--- a/docs/commercial-plan.xlsx
+++ b/docs/commercial-plan.xlsx
@@ -16,7 +16,8 @@
     <sheet name="الإكسسوارات" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="تكلفة اللتر" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="تجريبي — ثلاث محطات" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="البيانات" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="تشخيص فقدان الحركة" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="البيانات" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="614">
   <si>
     <t xml:space="preserve">الخطة التجارية — ثلاثة منافذ بيع</t>
   </si>
@@ -1474,6 +1475,192 @@
   </si>
   <si>
     <t xml:space="preserve">•  بن درويش 4 مضخات لـ807 زيارة — أقل من نصف طاقة عرفات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تشخيص فقدان الحركة — مكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بيانات يناير – 4 أغسطس 2026 · السبب مؤكَّد ميدانياً لكل حالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاكتشاف: التراجع في عدد الزيارات لا في سلة العميل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيارات يناير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيارات يونيو–يوليو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التغيّر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السبب المؤكَّد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK002 المعيصم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.51 ← 20.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تغيّر مسار الطريق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.10 ← 23.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منافس فتح قبلنا على المسار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK072 العزيزية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— ← 20.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تراجع موسمي · تعافت من يونيو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK007 العمرة الجديدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.72 ← 28.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تراجع موسمي · عادت لمستوى يناير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK017 عرفات الشوقية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.44 ← 20.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمو — المرجع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أثر الحدثين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المجموع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الزيارات المفقودة يومياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العميل لم يعد يمرّ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللترات المفقودة سنوياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بسلة ثابتة لكل زيارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهامش المفقود سنوياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بهامش 13.36 هللة لكل لتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الردّ — مختلف لكل حالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طبيعة الفقد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل يُسترد؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK002 — تغيّر المسار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دائم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا يُسترد بالسعر ولا بالخدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحويل المحطة من ممرّ إلى وجهة: مغسلة وسوبرماركت ومطعم · وإعادة تحجيم العمالة والمصاريف على الحركة الجديدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيراد غير وقودي لكل زيارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK019 — منافس قبلنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قابل للاسترداد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنافس يعترض العميل قبل وصوله</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سبب للتجاوز: عرض سعري أو خدمة لا توجد عنده · ولافتات مبكرة قبل نقطة اعتراضه · وتعاقد مع الأساطيل المارّة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الزيارات اليومية مقابل خط الأساس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عام — كل الشبكة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مخاطرة قائمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اكتُشف بعد شهور من وقوعه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إنذار مبكر: تنبيه آلي عند انخفاض الزيارات أسبوعياً بأكثر من 15% مقابل المتوسط · ومسح ربعي للمنافسين وأعمال الطرق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمن اكتشاف الحدث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما تثبته البيانات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  سلة العميل ثابتة في كل المحطات — فالفقد في عدد العملاء لا في سلوكهم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  المعيصم والشرايع سقطتا في فبراير بنسبة 60% و53% في شهر واحد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  العمرة والعزيزية تراجعتا موسمياً في أبريل–مايو ثم تعافتا في يونيو–يوليو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما ينفيه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  الخدمة ليست السبب — لو كانت لانخفضت السلة أو لتدرّج الأثر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  المضخات ليست السبب — الطاقة لم تتغيّر والزيارات هي التي اختفت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  التسعير ليس السبب — السعر مقنَّن وموحّد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الدرس الأهم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  حدثان خارجيان كلّفانا 2.1 مليون ريال هامش سنوياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  واكتُشفا بعد شهور — لا بنظام إنذار بل بتحليل لاحق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  الأولوية: نظام تنبيه أسبوعي على مستوى المحطة قبل أي مبادرة أخرى</t>
   </si>
   <si>
     <t xml:space="preserve">بيانات المحطات</t>
@@ -1690,7 +1877,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
@@ -1702,7 +1889,8 @@
     <numFmt numFmtId="172" formatCode="\+0.00;\-0.00"/>
     <numFmt numFmtId="173" formatCode="#,##0.##"/>
     <numFmt numFmtId="174" formatCode="\+#,##0.##;\-#,##0.##"/>
-    <numFmt numFmtId="175" formatCode="\+0.0%;\-0.0%;\—"/>
+    <numFmt numFmtId="175" formatCode="\+0.0%;\-0.0%"/>
+    <numFmt numFmtId="176" formatCode="\+0.0%;\-0.0%;\—"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1834,8 +2022,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFE699"/>
+        <bgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -1846,8 +2034,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
-        <bgColor rgb="FFF8CBAD"/>
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -1913,7 +2101,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2078,7 +2266,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2544,6 +2752,2282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M59"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>34063312</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>13312643</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>4236</v>
+      </c>
+      <c r="I4" s="43" t="n">
+        <v>-0.223</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="M4" s="23" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>35464924</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>3561</v>
+      </c>
+      <c r="I5" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>10864480</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>19344811</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>1892</v>
+      </c>
+      <c r="I6" s="45" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>19648510</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>10303487</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>2137</v>
+      </c>
+      <c r="I7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>13354076</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>5980304</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>1694</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>16732843</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>2589147</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>2359</v>
+      </c>
+      <c r="I9" s="43" t="n">
+        <v>-0.211</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="M9" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>12654914</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>4848425</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>1702</v>
+      </c>
+      <c r="I10" s="43" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>16280701</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>2041</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>16309064</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>98445</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>1726</v>
+      </c>
+      <c r="I12" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>8548346</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>7210207</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I13" s="43" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>14309768</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>1278215</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>1414</v>
+      </c>
+      <c r="I14" s="43" t="n">
+        <v>-0.119</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" s="4"/>
+      <c r="M14" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>11988986</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>3596696</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>1566</v>
+      </c>
+      <c r="I15" s="46" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="23" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>13247588</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>1088450</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>1169</v>
+      </c>
+      <c r="I16" s="45" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L16" s="4"/>
+      <c r="M16" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>13311973</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>1483</v>
+      </c>
+      <c r="I17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="4"/>
+      <c r="M17" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>13248903</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>1872</v>
+      </c>
+      <c r="I18" s="46" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="4"/>
+      <c r="M18" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>11882308</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>599108</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>1807</v>
+      </c>
+      <c r="I19" s="45" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>7867941</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>3857753</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>1328</v>
+      </c>
+      <c r="I20" s="45" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>11625662</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>1643</v>
+      </c>
+      <c r="I21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" s="4"/>
+      <c r="M21" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>11101203</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>1573</v>
+      </c>
+      <c r="I22" s="43" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L22" s="4"/>
+      <c r="M22" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>7193020</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>2745883</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>1112</v>
+      </c>
+      <c r="I23" s="46" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="4"/>
+      <c r="M23" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>9931491</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>1290</v>
+      </c>
+      <c r="I24" s="45" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>9064151</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>558090</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I25" s="45" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L25" s="4"/>
+      <c r="M25" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>9558604</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>1363</v>
+      </c>
+      <c r="I26" s="46" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>6835043</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>2528030</v>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>823</v>
+      </c>
+      <c r="I27" s="45" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="4"/>
+      <c r="M27" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>6066855</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>3252431</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>680</v>
+      </c>
+      <c r="I28" s="44" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L28" s="4"/>
+      <c r="M28" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>6241831</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>2950851</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>816</v>
+      </c>
+      <c r="I29" s="46" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="4"/>
+      <c r="M29" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>3791200</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>4805625</v>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>423</v>
+      </c>
+      <c r="I30" s="43" t="n">
+        <v>-0.084</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="4"/>
+      <c r="M30" s="23" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>6955614</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>1485665</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>1025</v>
+      </c>
+      <c r="I31" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="4"/>
+      <c r="M31" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>7191456</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>642374</v>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>864</v>
+      </c>
+      <c r="I32" s="45" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L32" s="4"/>
+      <c r="M32" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>6980426</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>801543</v>
+      </c>
+      <c r="H33" s="16" t="n">
+        <v>952</v>
+      </c>
+      <c r="I33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L33" s="4"/>
+      <c r="M33" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>7444371</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>175072</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>922</v>
+      </c>
+      <c r="I34" s="45" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L34" s="4"/>
+      <c r="M34" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>6267957</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>814480</v>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>931</v>
+      </c>
+      <c r="I35" s="43" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="4"/>
+      <c r="M35" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>6999984</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>913</v>
+      </c>
+      <c r="I36" s="43" t="n">
+        <v>-0.533</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>5722940</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>1147336</v>
+      </c>
+      <c r="H37" s="16" t="n">
+        <v>938</v>
+      </c>
+      <c r="I37" s="45" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" s="4"/>
+      <c r="M37" s="23" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>6046920</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>778046</v>
+      </c>
+      <c r="H38" s="16" t="n">
+        <v>1227</v>
+      </c>
+      <c r="I38" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>4191108</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>2493275</v>
+      </c>
+      <c r="H39" s="16" t="n">
+        <v>538</v>
+      </c>
+      <c r="I39" s="46" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" s="4"/>
+      <c r="M39" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <v>5545862</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>657563</v>
+      </c>
+      <c r="H40" s="16" t="n">
+        <v>537</v>
+      </c>
+      <c r="I40" s="43" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L40" s="4"/>
+      <c r="M40" s="23" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>5647921</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>335046</v>
+      </c>
+      <c r="H41" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="I41" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="4"/>
+      <c r="M41" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>3599745</v>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>2324712</v>
+      </c>
+      <c r="H42" s="16" t="n">
+        <v>441</v>
+      </c>
+      <c r="I42" s="46" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" s="4"/>
+      <c r="M42" s="23" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>5899223</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="16" t="n">
+        <v>807</v>
+      </c>
+      <c r="I43" s="43" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L43" s="4"/>
+      <c r="M43" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>5284855</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>440882</v>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>685</v>
+      </c>
+      <c r="I44" s="45" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" s="4"/>
+      <c r="M44" s="23" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>5197774</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>367295</v>
+      </c>
+      <c r="H45" s="16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I45" s="45" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" s="4"/>
+      <c r="M45" s="23" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>4156161</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>1282162</v>
+      </c>
+      <c r="H46" s="16" t="n">
+        <v>586</v>
+      </c>
+      <c r="I46" s="43" t="n">
+        <v>-0.123</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L46" s="4"/>
+      <c r="M46" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>4362115</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>983614</v>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>650</v>
+      </c>
+      <c r="I47" s="46" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L47" s="4"/>
+      <c r="M47" s="23" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>4341977</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="16" t="n">
+        <v>469</v>
+      </c>
+      <c r="I48" s="45" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L48" s="4"/>
+      <c r="M48" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>3433425</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>864810</v>
+      </c>
+      <c r="H49" s="16" t="n">
+        <v>402</v>
+      </c>
+      <c r="I49" s="45" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L49" s="4"/>
+      <c r="M49" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>3857645</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>456</v>
+      </c>
+      <c r="I50" s="43" t="n">
+        <v>-0.249</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>3708152</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>451</v>
+      </c>
+      <c r="I51" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>3315559</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>57339</v>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>455</v>
+      </c>
+      <c r="I52" s="45" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" s="4"/>
+      <c r="M52" s="23" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>2286567</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>943048</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>333</v>
+      </c>
+      <c r="I53" s="46" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" s="4"/>
+      <c r="M53" s="23" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>2663618</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>222209</v>
+      </c>
+      <c r="H54" s="16" t="n">
+        <v>327</v>
+      </c>
+      <c r="I54" s="46" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L54" s="4"/>
+      <c r="M54" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>2086987</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>458119</v>
+      </c>
+      <c r="H55" s="16" t="n">
+        <v>281</v>
+      </c>
+      <c r="I55" s="45" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L55" s="4"/>
+      <c r="M55" s="23" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="F56" s="16" t="n">
+        <v>1960098</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>471201</v>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>408</v>
+      </c>
+      <c r="I56" s="45" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L56" s="4"/>
+      <c r="M56" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>1451309</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>480553</v>
+      </c>
+      <c r="H57" s="16" t="n">
+        <v>196</v>
+      </c>
+      <c r="I57" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" s="16" t="n">
+        <v>1099275</v>
+      </c>
+      <c r="G58" s="16" t="n">
+        <v>220383</v>
+      </c>
+      <c r="H58" s="16" t="n">
+        <v>154</v>
+      </c>
+      <c r="I58" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L58" s="4"/>
+      <c r="M58" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="19"/>
+      <c r="B59" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="20" t="n">
+        <f aca="false">SUM(F4:F58)</f>
+        <v>478886741</v>
+      </c>
+      <c r="G59" s="20" t="n">
+        <f aca="false">SUM(G4:G58)</f>
+        <v>109395328</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <f aca="false">SUM(H4:H58)</f>
+        <v>61573</v>
+      </c>
+      <c r="I59" s="19"/>
+      <c r="J59" s="20" t="n">
+        <f aca="false">SUM(J4:J58)</f>
+        <v>482</v>
+      </c>
+      <c r="K59" s="20" t="n">
+        <f aca="false">SUM(K4:K58)</f>
+        <v>399</v>
+      </c>
+      <c r="L59" s="20" t="n">
+        <f aca="false">SUM(L4:L58)</f>
+        <v>103</v>
+      </c>
+      <c r="M59" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -7713,19 +10197,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7738,12 +10216,6 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -7755,2224 +10227,472 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K3" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="L3" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>489</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="C5" s="16" t="n">
+        <v>2163</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>601</v>
+      </c>
+      <c r="E5" s="38" t="n">
+        <f aca="false">IFERROR(D5/C5-1,"")</f>
+        <v>-0.722145168747111</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>830</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <f aca="false">IFERROR(D6/C6-1,"")</f>
+        <v>-0.542168674698795</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>34063312</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>13312643</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>4236</v>
-      </c>
-      <c r="I4" s="38" t="n">
-        <v>-0.223</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="M4" s="23" t="n">
-        <v>0.006</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="4" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>35464924</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>3561</v>
-      </c>
-      <c r="I5" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="C7" s="16" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>2488</v>
+      </c>
+      <c r="E7" s="39" t="n">
+        <f aca="false">IFERROR(D7/C7-1,"")</f>
+        <v>-0.104391648668107</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>176</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>10864480</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>19344811</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>1892</v>
-      </c>
-      <c r="I6" s="40" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>19648510</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>10303487</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>2137</v>
-      </c>
-      <c r="I7" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="16" t="n">
+        <v>4322</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>4266</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <f aca="false">IFERROR(D8/C8-1,"")</f>
+        <v>-0.012956964368348</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>13354076</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>5980304</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>1694</v>
-      </c>
-      <c r="I8" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>16732843</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>2589147</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>2359</v>
-      </c>
-      <c r="I9" s="38" t="n">
-        <v>-0.211</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="M9" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>12654914</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>4848425</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>1702</v>
-      </c>
-      <c r="I10" s="38" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="C9" s="16" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>1391</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <f aca="false">IFERROR(D9/C9-1,"")</f>
+        <v>0.149586776859504</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>16280701</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>2041</v>
-      </c>
-      <c r="I11" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>16309064</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>98445</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>1726</v>
-      </c>
-      <c r="I12" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>8548346</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>7210207</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>1380</v>
-      </c>
-      <c r="I13" s="38" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>14309768</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>1278215</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <v>1414</v>
-      </c>
-      <c r="I14" s="38" t="n">
-        <v>-0.119</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>505</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>11988986</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>3596696</v>
-      </c>
-      <c r="H15" s="16" t="n">
-        <v>1566</v>
-      </c>
-      <c r="I15" s="41" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="23" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="C13" s="16" t="n">
+        <v>1562</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>451</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">C13+D13</f>
+        <v>2013</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>13247588</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>1088450</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>1169</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>13311973</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>1483</v>
-      </c>
-      <c r="I17" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>508</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>13248903</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>1872</v>
-      </c>
-      <c r="I18" s="41" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="C14" s="16" t="n">
+        <v>11920000</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>3810000</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <f aca="false">C14+D14</f>
+        <v>15730000</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>11882308</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>599108</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>1807</v>
-      </c>
-      <c r="I19" s="40" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>511</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>7867941</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>3857753</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>1328</v>
-      </c>
-      <c r="I20" s="40" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="C15" s="24" t="n">
+        <v>1590000</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>510000</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <f aca="false">C15+D15</f>
+        <v>2100000</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="4" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>11625662</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>1643</v>
-      </c>
-      <c r="I21" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>11101203</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>1573</v>
-      </c>
-      <c r="I22" s="38" t="n">
-        <v>-0.112</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>7193020</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>2745883</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>1112</v>
-      </c>
-      <c r="I23" s="41" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>9931491</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>1290</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>0.069</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M24" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="E18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>517</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>9064151</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>558090</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>1144</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L25" s="4"/>
-      <c r="M25" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="C19" s="18" t="s">
         <v>518</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>9558604</v>
-      </c>
-      <c r="G26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="16" t="n">
-        <v>1363</v>
-      </c>
-      <c r="I26" s="41" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L26" s="4"/>
-      <c r="M26" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>6835043</v>
-      </c>
-      <c r="G27" s="16" t="n">
-        <v>2528030</v>
-      </c>
-      <c r="H27" s="16" t="n">
-        <v>823</v>
-      </c>
-      <c r="I27" s="40" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="4"/>
-      <c r="M27" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="E19" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>6066855</v>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>3252431</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>680</v>
-      </c>
-      <c r="I28" s="39" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="L28" s="4"/>
-      <c r="M28" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="F19" s="4"/>
+      <c r="G19" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>6241831</v>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>2950851</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>816</v>
-      </c>
-      <c r="I29" s="41" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" s="4"/>
-      <c r="M29" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>3791200</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>4805625</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>423</v>
-      </c>
-      <c r="I30" s="38" t="n">
-        <v>-0.084</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L30" s="4"/>
-      <c r="M30" s="23" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="C20" s="41" t="s">
         <v>523</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>6955614</v>
-      </c>
-      <c r="G31" s="16" t="n">
-        <v>1485665</v>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>1025</v>
-      </c>
-      <c r="I31" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>7191456</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <v>642374</v>
-      </c>
-      <c r="H32" s="16" t="n">
-        <v>864</v>
-      </c>
-      <c r="I32" s="40" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L32" s="4"/>
-      <c r="M32" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>6980426</v>
-      </c>
-      <c r="G33" s="16" t="n">
-        <v>801543</v>
-      </c>
-      <c r="H33" s="16" t="n">
-        <v>952</v>
-      </c>
-      <c r="I33" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="F20" s="4"/>
+      <c r="G20" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>7444371</v>
-      </c>
-      <c r="G34" s="16" t="n">
-        <v>175072</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>922</v>
-      </c>
-      <c r="I34" s="40" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>6267957</v>
-      </c>
-      <c r="G35" s="16" t="n">
-        <v>814480</v>
-      </c>
-      <c r="H35" s="16" t="n">
-        <v>931</v>
-      </c>
-      <c r="I35" s="38" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" s="4"/>
-      <c r="M35" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="C21" s="42" t="s">
         <v>528</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>6999984</v>
-      </c>
-      <c r="G36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="16" t="n">
-        <v>913</v>
-      </c>
-      <c r="I36" s="38" t="n">
-        <v>-0.533</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>5722940</v>
-      </c>
-      <c r="G37" s="16" t="n">
-        <v>1147336</v>
-      </c>
-      <c r="H37" s="16" t="n">
-        <v>938</v>
-      </c>
-      <c r="I37" s="40" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="23" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="E21" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>6046920</v>
-      </c>
-      <c r="G38" s="16" t="n">
-        <v>778046</v>
-      </c>
-      <c r="H38" s="16" t="n">
-        <v>1227</v>
-      </c>
-      <c r="I38" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="F21" s="4"/>
+      <c r="G21" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>4191108</v>
-      </c>
-      <c r="G39" s="16" t="n">
-        <v>2493275</v>
-      </c>
-      <c r="H39" s="16" t="n">
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="7" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C24" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C25" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C26" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C29" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C30" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="I39" s="41" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>5545862</v>
-      </c>
-      <c r="G40" s="16" t="n">
-        <v>657563</v>
-      </c>
-      <c r="H40" s="16" t="n">
-        <v>537</v>
-      </c>
-      <c r="I40" s="38" t="n">
-        <v>-0.126</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="23" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>5647921</v>
-      </c>
-      <c r="G41" s="16" t="n">
-        <v>335046</v>
-      </c>
-      <c r="H41" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="I41" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="4"/>
-      <c r="M41" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>3599745</v>
-      </c>
-      <c r="G42" s="16" t="n">
-        <v>2324712</v>
-      </c>
-      <c r="H42" s="16" t="n">
-        <v>441</v>
-      </c>
-      <c r="I42" s="41" t="n">
-        <v>-0.029</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L42" s="4"/>
-      <c r="M42" s="23" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>5899223</v>
-      </c>
-      <c r="G43" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="16" t="n">
-        <v>807</v>
-      </c>
-      <c r="I43" s="38" t="n">
-        <v>-0.121</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L43" s="4"/>
-      <c r="M43" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>5284855</v>
-      </c>
-      <c r="G44" s="16" t="n">
-        <v>440882</v>
-      </c>
-      <c r="H44" s="16" t="n">
-        <v>685</v>
-      </c>
-      <c r="I44" s="40" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L44" s="4"/>
-      <c r="M44" s="23" t="n">
-        <v>0.007</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>5197774</v>
-      </c>
-      <c r="G45" s="16" t="n">
-        <v>367295</v>
-      </c>
-      <c r="H45" s="16" t="n">
-        <v>591</v>
-      </c>
-      <c r="I45" s="40" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L45" s="4"/>
-      <c r="M45" s="23" t="n">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>4156161</v>
-      </c>
-      <c r="G46" s="16" t="n">
-        <v>1282162</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>586</v>
-      </c>
-      <c r="I46" s="38" t="n">
-        <v>-0.123</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L46" s="4"/>
-      <c r="M46" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C31" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="E47" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>4362115</v>
-      </c>
-      <c r="G47" s="16" t="n">
-        <v>983614</v>
-      </c>
-      <c r="H47" s="16" t="n">
-        <v>650</v>
-      </c>
-      <c r="I47" s="41" t="n">
-        <v>-0.009</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L47" s="4"/>
-      <c r="M47" s="23" t="n">
-        <v>0.007</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>4341977</v>
-      </c>
-      <c r="G48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="16" t="n">
-        <v>469</v>
-      </c>
-      <c r="I48" s="40" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L48" s="4"/>
-      <c r="M48" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F49" s="16" t="n">
-        <v>3433425</v>
-      </c>
-      <c r="G49" s="16" t="n">
-        <v>864810</v>
-      </c>
-      <c r="H49" s="16" t="n">
-        <v>402</v>
-      </c>
-      <c r="I49" s="40" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" s="4"/>
-      <c r="M49" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>3857645</v>
-      </c>
-      <c r="G50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="16" t="n">
-        <v>456</v>
-      </c>
-      <c r="I50" s="38" t="n">
-        <v>-0.249</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M50" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>3708152</v>
-      </c>
-      <c r="G51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="16" t="n">
-        <v>451</v>
-      </c>
-      <c r="I51" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F52" s="16" t="n">
-        <v>3315559</v>
-      </c>
-      <c r="G52" s="16" t="n">
-        <v>57339</v>
-      </c>
-      <c r="H52" s="16" t="n">
-        <v>455</v>
-      </c>
-      <c r="I52" s="40" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K52" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L52" s="4"/>
-      <c r="M52" s="23" t="n">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>2286567</v>
-      </c>
-      <c r="G53" s="16" t="n">
-        <v>943048</v>
-      </c>
-      <c r="H53" s="16" t="n">
-        <v>333</v>
-      </c>
-      <c r="I53" s="41" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L53" s="4"/>
-      <c r="M53" s="23" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>2663618</v>
-      </c>
-      <c r="G54" s="16" t="n">
-        <v>222209</v>
-      </c>
-      <c r="H54" s="16" t="n">
-        <v>327</v>
-      </c>
-      <c r="I54" s="41" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L54" s="4"/>
-      <c r="M54" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>2086987</v>
-      </c>
-      <c r="G55" s="16" t="n">
-        <v>458119</v>
-      </c>
-      <c r="H55" s="16" t="n">
-        <v>281</v>
-      </c>
-      <c r="I55" s="40" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L55" s="4"/>
-      <c r="M55" s="23" t="n">
-        <v>0.005</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>1960098</v>
-      </c>
-      <c r="G56" s="16" t="n">
-        <v>471201</v>
-      </c>
-      <c r="H56" s="16" t="n">
-        <v>408</v>
-      </c>
-      <c r="I56" s="40" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L56" s="4"/>
-      <c r="M56" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>1451309</v>
-      </c>
-      <c r="G57" s="16" t="n">
-        <v>480553</v>
-      </c>
-      <c r="H57" s="16" t="n">
-        <v>196</v>
-      </c>
-      <c r="I57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>1099275</v>
-      </c>
-      <c r="G58" s="16" t="n">
-        <v>220383</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="I58" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L58" s="4"/>
-      <c r="M58" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="19"/>
-      <c r="B59" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="20" t="n">
-        <f aca="false">SUM(F4:F58)</f>
-        <v>478886741</v>
-      </c>
-      <c r="G59" s="20" t="n">
-        <f aca="false">SUM(G4:G58)</f>
-        <v>109395328</v>
-      </c>
-      <c r="H59" s="20" t="n">
-        <f aca="false">SUM(H4:H58)</f>
-        <v>61573</v>
-      </c>
-      <c r="I59" s="19"/>
-      <c r="J59" s="20" t="n">
-        <f aca="false">SUM(J4:J58)</f>
-        <v>482</v>
-      </c>
-      <c r="K59" s="20" t="n">
-        <f aca="false">SUM(K4:K58)</f>
-        <v>399</v>
-      </c>
-      <c r="L59" s="20" t="n">
-        <f aca="false">SUM(L4:L58)</f>
-        <v>103</v>
-      </c>
-      <c r="M59" s="19"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+  <mergeCells count="14">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/commercial-plan.xlsx
+++ b/docs/commercial-plan.xlsx
@@ -17,7 +17,9 @@
     <sheet name="تكلفة اللتر" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="تجريبي — ثلاث محطات" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="تشخيص فقدان الحركة" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="البيانات" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="نموذج العامل" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="تجربة الشرايع" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="البيانات" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="742">
   <si>
     <t xml:space="preserve">الخطة التجارية — ثلاثة منافذ بيع</t>
   </si>
@@ -1661,6 +1663,390 @@
   </si>
   <si>
     <t xml:space="preserve">•  الأولوية: نظام تنبيه أسبوعي على مستوى المحطة قبل أي مبادرة أخرى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نموذج مبيعات العامل — مستهدف وحافز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لكل عامل مستهدف وردية · والحافز مرتبط بالزيادة وبجودة الخدمة معاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لتر لكل زيارة (المحطة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هامش المساهمة (هللة/لتر)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عدد الورديات في اليوم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سقف الحافز الشهري للعامل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بطاقة العامل — تُعبّأ لكل عامل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العامل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوردية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خط الأساس (زيارة/وردية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفعلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحافز (ريال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بوابة الجودة — الحافز لا يُصرف بدونها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشرط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المقياس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لماذا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا شكوى مثبتة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شكاوى العامل في الشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحافز مكافأة أداء لا مكافأة حجم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمن الخدمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متوسط زمن التعبئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤ الحد المعتمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سرعة الخدمة هي ما يطلبه العميل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الانضباط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحضور في وردية الذروة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الذروة هي حيث تُكسب الزيارة أو تُفقد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النظافة والمظهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تقييم المشرف الأسبوعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مقبول فأعلى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أول ما يراه العميل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قواعد الحافز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  يُحتسب على الزيادة فوق خط الأساس فقط — لا على الحجم الكلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  لا يُصرف إذا سقط أي شرط من بوابة الجودة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  سقف شهري يمنع المبالغة في شهر استثنائي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  خط الأساس يُراجع كل ربع حتى لا يصبح الحافز دائماً على نفس المستوى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ما يجب تفاديه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  ربط الحافز بالحجم وحده يحوّله إلى مكافأة على الموسم لا على الأداء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  خط أساس متساهل يجعل الحافز تكلفة ثابتة بلا مقابل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  غياب قياس زمن الخدمة يفرّغ البوابة من معناها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تجربة الشرايع MK019 — خدمة ممتازة وتوزيع مناديل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنافس يعترض العميل قبلنا · والعميل ما زال يمرّ — فالتجربة اختبار لسبب التجاوز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خط الأساس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفترة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يونيو – 4 أغسطس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يناير كان 830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثابت طوال الفترة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السلة لم تتأثر — الفقد في العدد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هامش المساهمة لكل زيارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.15 لتر × 13.36 هللة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المتفق 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نقص عامل واحد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الطاقة غير مقيِّدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ساعة الذروة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توقيت التوزيع الأمثل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اقتصاديات التدخل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكلفة الوحدة الموزّعة (ريال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة الزيارات التي تُوزَّع عليها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكلفة إضافية أخرى شهرياً (تدريب · مشرف)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مدة التجربة (أسبوع)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكلفة التوزيع يومياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قبل أي نمو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الزيارات الإضافية للتعادل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهامش لكل زيارة 3.09 ريال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دون هذه النسبة التجربة خاسرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سقف الاسترداد الممكن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العودة الكاملة لمستوى يناير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أقصى نمو ممكن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحد الأعلى لما يمكن استرداده</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المتابعة — ما يُسجَّل يومياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التكرار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لماذا هذا المؤشر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الزيارات اليومية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نظام المحطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يومي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مدير المحطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المؤشر الرئيسي — الفقد كان في العدد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اللترات اليومية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">للتأكد أن السلة لم تنخفض</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محسوب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إن انخفض فالنمو من عملاء أصغر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوحدات الموزّعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سجل يدوي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المشرف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لربط التكلفة بالأثر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمن التعبئة في الذروة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قياس عيّنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخدمة الممتازة يجب أن تُقاس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خدمة العملاء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مؤشر عكسي للجودة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيارات المحطة المرجع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التحليل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لعزل أثر الموسم عن أثر التدخل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سجل المتابعة الأسبوعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسبوع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وحدات موزّعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التكلفة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفارق عن الأساس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحكم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسبوع 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لماذا الشرايع تحديداً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  الفقد سببه اعتراض منافس — والعميل ما زال يمرّ على الطريق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  فالتدخل يختبر سؤالاً واحداً: هل يعطي سبباً كافياً لتجاوز المنافس؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  بخلاف المعيصم حيث الطريق نفسه تغيّر — ولا تدخّل يعيد سيارة لا تمرّ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحذير من الأرقام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  الهامش لكل زيارة 3.09 ريال فقط — فتكلفة التوزيع تلتهمه بسرعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  توزيع بريال واحد على كل الزيارات يحتاج نمواً 32% لمجرد التعادل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  وبريال على نصف الزيارات يحتاج 16% — وهو الأقرب للواقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  ابدأ بالنسبة الأقل والتكلفة الأدنى ثم ارفع إن ثبت الأثر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرط صحة القياس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  محطة مرجع تُقاس بالتوازي — عرفات الشوقية أو أي محطة مستقرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  بدونها لا يمكن التفريق بين أثر التدخل وأثر الموسم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  والخدمة الممتازة يجب أن تُقاس بزمن التعبئة لا بالانطباع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قرار الاستمرار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  بعد 8 أسابيع: إن تجاوز النمو نقطة التعادل يُعمَّم التدخل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  إن كان دون التعادل لكن الاتجاه صاعد يُمدَّد 4 أسابيع بتكلفة أقل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  إن لم يتحرك شيء فالسبب ليس الخدمة — والملف يعود لمعالجة الموقع</t>
   </si>
   <si>
     <t xml:space="preserve">بيانات المحطات</t>
@@ -1877,7 +2263,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
@@ -1890,7 +2276,9 @@
     <numFmt numFmtId="173" formatCode="#,##0.##"/>
     <numFmt numFmtId="174" formatCode="\+#,##0.##;\-#,##0.##"/>
     <numFmt numFmtId="175" formatCode="\+0.0%;\-0.0%"/>
-    <numFmt numFmtId="176" formatCode="\+0.0%;\-0.0%;\—"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="0%"/>
+    <numFmt numFmtId="178" formatCode="\+0.0%;\-0.0%;\—"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -2101,7 +2489,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2274,19 +2662,47 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2757,6 +3173,1496 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="C4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>13.36</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="C8" s="21"/>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="17" t="str">
+        <f aca="false">IF(OR(G12="",F12=""),"",G12-F12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="24" t="str">
+        <f aca="false">IFERROR(IF(H12&lt;=0,0,MIN(H12*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="44"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="17" t="str">
+        <f aca="false">IF(OR(G13="",F13=""),"",G13-F13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="24" t="str">
+        <f aca="false">IFERROR(IF(H13&lt;=0,0,MIN(H13*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="44"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="17" t="str">
+        <f aca="false">IF(OR(G14="",F14=""),"",G14-F14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="24" t="str">
+        <f aca="false">IFERROR(IF(H14&lt;=0,0,MIN(H14*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="17" t="str">
+        <f aca="false">IF(OR(G15="",F15=""),"",G15-F15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="24" t="str">
+        <f aca="false">IFERROR(IF(H15&lt;=0,0,MIN(H15*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="44"/>
+    </row>
+    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="17" t="str">
+        <f aca="false">IF(OR(G16="",F16=""),"",G16-F16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="24" t="str">
+        <f aca="false">IFERROR(IF(H16&lt;=0,0,MIN(H16*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="17" t="str">
+        <f aca="false">IF(OR(G17="",F17=""),"",G17-F17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="24" t="str">
+        <f aca="false">IFERROR(IF(H17&lt;=0,0,MIN(H17*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="44"/>
+    </row>
+    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="17" t="str">
+        <f aca="false">IF(OR(G18="",F18=""),"",G18-F18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="24" t="str">
+        <f aca="false">IFERROR(IF(H18&lt;=0,0,MIN(H18*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="44"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="17" t="str">
+        <f aca="false">IF(OR(G19="",F19=""),"",G19-F19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="24" t="str">
+        <f aca="false">IFERROR(IF(H19&lt;=0,0,MIN(H19*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="44"/>
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="17" t="str">
+        <f aca="false">IF(OR(G20="",F20=""),"",G20-F20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="24" t="str">
+        <f aca="false">IFERROR(IF(H20&lt;=0,0,MIN(H20*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="44"/>
+    </row>
+    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="17" t="str">
+        <f aca="false">IF(OR(G21="",F21=""),"",G21-F21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="24" t="str">
+        <f aca="false">IFERROR(IF(H21&lt;=0,0,MIN(H21*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="44"/>
+    </row>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="17" t="str">
+        <f aca="false">IF(OR(G22="",F22=""),"",G22-F22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="24" t="str">
+        <f aca="false">IFERROR(IF(H22&lt;=0,0,MIN(H22*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="44"/>
+    </row>
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="17" t="str">
+        <f aca="false">IF(OR(G23="",F23=""),"",G23-F23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="24" t="str">
+        <f aca="false">IFERROR(IF(H23&lt;=0,0,MIN(H23*$C$4*$C$5/100*$C$6*30,$C$8)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="44"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20" t="n">
+        <f aca="false">SUM(E12:E23)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <f aca="false">SUM(F12:F23)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <f aca="false">SUM(G12:G23)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <f aca="false">SUM(H12:H23)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="20" t="n">
+        <f aca="false">SUM(I12:I23)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>561</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="45" t="s">
+        <v>565</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="45" t="s">
+        <v>569</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="6" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>573</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="7" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C37" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="9" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C40" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C41" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C42" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="C40:J40"/>
+    <mergeCell ref="C41:J41"/>
+    <mergeCell ref="C42:J42"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G66"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>378</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="6" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="6" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="6" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="6" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>599</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="C13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="C14" s="47"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="C15" s="21"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">378*C14*C13</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="6" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <f aca="false">IFERROR(C19/3.09,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <f aca="false">IFERROR(C20/378,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="6" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>611</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <f aca="false">830-378</f>
+        <v>452</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <f aca="false">IFERROR(C22/378,"")</f>
+        <v>1.1957671957672</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="6" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>623</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="6" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="6" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="6" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="6" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>638</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="6" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="45" t="s">
+        <v>647</v>
+      </c>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="17" t="str">
+        <f aca="false">IF(B37="","",B37-378)</f>
+        <v/>
+      </c>
+      <c r="G37" s="4" t="str">
+        <f aca="false">IF(B37="","",IF(F37*3.09&gt;E37/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="45" t="s">
+        <v>648</v>
+      </c>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="17" t="str">
+        <f aca="false">IF(B38="","",B38-378)</f>
+        <v/>
+      </c>
+      <c r="G38" s="4" t="str">
+        <f aca="false">IF(B38="","",IF(F38*3.09&gt;E38/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="45" t="s">
+        <v>649</v>
+      </c>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="17" t="str">
+        <f aca="false">IF(B39="","",B39-378)</f>
+        <v/>
+      </c>
+      <c r="G39" s="4" t="str">
+        <f aca="false">IF(B39="","",IF(F39*3.09&gt;E39/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="45" t="s">
+        <v>650</v>
+      </c>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="17" t="str">
+        <f aca="false">IF(B40="","",B40-378)</f>
+        <v/>
+      </c>
+      <c r="G40" s="4" t="str">
+        <f aca="false">IF(B40="","",IF(F40*3.09&gt;E40/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="45" t="s">
+        <v>651</v>
+      </c>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="17" t="str">
+        <f aca="false">IF(B41="","",B41-378)</f>
+        <v/>
+      </c>
+      <c r="G41" s="4" t="str">
+        <f aca="false">IF(B41="","",IF(F41*3.09&gt;E41/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="45" t="s">
+        <v>652</v>
+      </c>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="17" t="str">
+        <f aca="false">IF(B42="","",B42-378)</f>
+        <v/>
+      </c>
+      <c r="G42" s="4" t="str">
+        <f aca="false">IF(B42="","",IF(F42*3.09&gt;E42/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="45" t="s">
+        <v>653</v>
+      </c>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="17" t="str">
+        <f aca="false">IF(B43="","",B43-378)</f>
+        <v/>
+      </c>
+      <c r="G43" s="4" t="str">
+        <f aca="false">IF(B43="","",IF(F43*3.09&gt;E43/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="45" t="s">
+        <v>654</v>
+      </c>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="17" t="str">
+        <f aca="false">IF(B44="","",B44-378)</f>
+        <v/>
+      </c>
+      <c r="G44" s="4" t="str">
+        <f aca="false">IF(B44="","",IF(F44*3.09&gt;E44/7,"مربح","دون التعادل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="7" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C48" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C49" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C50" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="9" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C53" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C54" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C55" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C56" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="9" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C59" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+    </row>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C60" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C61" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="7" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C64" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C65" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C66" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:M59"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2774,7 +4680,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>544</v>
+        <v>672</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2791,7 +4697,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>545</v>
+        <v>673</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2808,7 +4714,7 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>546</v>
+        <v>674</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>111</v>
@@ -2817,16 +4723,16 @@
         <v>112</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>547</v>
+        <v>675</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>548</v>
+        <v>676</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>113</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>549</v>
+        <v>677</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>114</v>
@@ -2838,18 +4744,18 @@
         <v>115</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>550</v>
+        <v>678</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>551</v>
+        <v>679</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>552</v>
+        <v>680</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>553</v>
+        <v>681</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>122</v>
@@ -2858,7 +4764,7 @@
         <v>121</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>181</v>
@@ -2872,7 +4778,7 @@
       <c r="H4" s="16" t="n">
         <v>4236</v>
       </c>
-      <c r="I4" s="43" t="n">
+      <c r="I4" s="50" t="n">
         <v>-0.223</v>
       </c>
       <c r="J4" s="4" t="n">
@@ -2890,7 +4796,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>555</v>
+        <v>683</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>120</v>
@@ -2899,7 +4805,7 @@
         <v>121</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>556</v>
+        <v>684</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>91</v>
@@ -2913,7 +4819,7 @@
       <c r="H5" s="16" t="n">
         <v>3561</v>
       </c>
-      <c r="I5" s="44" t="n">
+      <c r="I5" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
@@ -2929,7 +4835,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>557</v>
+        <v>685</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>141</v>
@@ -2938,7 +4844,7 @@
         <v>128</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>556</v>
+        <v>684</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>176</v>
@@ -2952,7 +4858,7 @@
       <c r="H6" s="16" t="n">
         <v>1892</v>
       </c>
-      <c r="I6" s="45" t="n">
+      <c r="I6" s="52" t="n">
         <v>0.273</v>
       </c>
       <c r="J6" s="4"/>
@@ -2964,7 +4870,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>558</v>
+        <v>686</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>123</v>
@@ -2973,7 +4879,7 @@
         <v>124</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>91</v>
@@ -2987,7 +4893,7 @@
       <c r="H7" s="16" t="n">
         <v>2137</v>
       </c>
-      <c r="I7" s="44" t="n">
+      <c r="I7" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
@@ -3003,7 +4909,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>559</v>
+        <v>687</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>130</v>
@@ -3012,7 +4918,7 @@
         <v>124</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>560</v>
+        <v>688</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>55</v>
@@ -3026,7 +4932,7 @@
       <c r="H8" s="16" t="n">
         <v>1694</v>
       </c>
-      <c r="I8" s="44" t="n">
+      <c r="I8" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
@@ -3042,7 +4948,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>561</v>
+        <v>689</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>125</v>
@@ -3051,7 +4957,7 @@
         <v>121</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>180</v>
@@ -3065,7 +4971,7 @@
       <c r="H9" s="16" t="n">
         <v>2359</v>
       </c>
-      <c r="I9" s="43" t="n">
+      <c r="I9" s="50" t="n">
         <v>-0.211</v>
       </c>
       <c r="J9" s="4" t="n">
@@ -3083,7 +4989,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>562</v>
+        <v>690</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>135</v>
@@ -3092,7 +4998,7 @@
         <v>121</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>181</v>
@@ -3106,7 +5012,7 @@
       <c r="H10" s="16" t="n">
         <v>1702</v>
       </c>
-      <c r="I10" s="43" t="n">
+      <c r="I10" s="50" t="n">
         <v>-0.09</v>
       </c>
       <c r="J10" s="4" t="n">
@@ -3122,7 +5028,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>563</v>
+        <v>691</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>127</v>
@@ -3131,7 +5037,7 @@
         <v>128</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>65</v>
@@ -3145,7 +5051,7 @@
       <c r="H11" s="16" t="n">
         <v>2041</v>
       </c>
-      <c r="I11" s="44" t="n">
+      <c r="I11" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
@@ -3161,7 +5067,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>564</v>
+        <v>692</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>126</v>
@@ -3170,7 +5076,7 @@
         <v>124</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>63</v>
@@ -3184,7 +5090,7 @@
       <c r="H12" s="16" t="n">
         <v>1726</v>
       </c>
-      <c r="I12" s="44" t="n">
+      <c r="I12" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
@@ -3200,7 +5106,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>565</v>
+        <v>693</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>145</v>
@@ -3209,7 +5115,7 @@
         <v>121</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>556</v>
+        <v>684</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>181</v>
@@ -3223,7 +5129,7 @@
       <c r="H13" s="16" t="n">
         <v>1380</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="50" t="n">
         <v>-0.217</v>
       </c>
       <c r="J13" s="4" t="n">
@@ -3239,7 +5145,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>566</v>
+        <v>694</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>129</v>
@@ -3248,7 +5154,7 @@
         <v>124</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>560</v>
+        <v>688</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>181</v>
@@ -3262,7 +5168,7 @@
       <c r="H14" s="16" t="n">
         <v>1414</v>
       </c>
-      <c r="I14" s="43" t="n">
+      <c r="I14" s="50" t="n">
         <v>-0.119</v>
       </c>
       <c r="J14" s="4" t="n">
@@ -3278,7 +5184,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>567</v>
+        <v>695</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>136</v>
@@ -3287,7 +5193,7 @@
         <v>121</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>181</v>
@@ -3301,7 +5207,7 @@
       <c r="H15" s="16" t="n">
         <v>1566</v>
       </c>
-      <c r="I15" s="46" t="n">
+      <c r="I15" s="53" t="n">
         <v>-0.034</v>
       </c>
       <c r="J15" s="4" t="n">
@@ -3317,7 +5223,7 @@
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>568</v>
+        <v>696</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>133</v>
@@ -3326,7 +5232,7 @@
         <v>134</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>181</v>
@@ -3340,7 +5246,7 @@
       <c r="H16" s="16" t="n">
         <v>1169</v>
       </c>
-      <c r="I16" s="45" t="n">
+      <c r="I16" s="52" t="n">
         <v>0.151</v>
       </c>
       <c r="J16" s="4" t="n">
@@ -3356,7 +5262,7 @@
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>569</v>
+        <v>697</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>131</v>
@@ -3365,7 +5271,7 @@
         <v>124</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>57</v>
@@ -3379,7 +5285,7 @@
       <c r="H17" s="16" t="n">
         <v>1483</v>
       </c>
-      <c r="I17" s="44" t="n">
+      <c r="I17" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
@@ -3395,7 +5301,7 @@
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>570</v>
+        <v>698</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>132</v>
@@ -3404,7 +5310,7 @@
         <v>121</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>181</v>
@@ -3418,7 +5324,7 @@
       <c r="H18" s="16" t="n">
         <v>1872</v>
       </c>
-      <c r="I18" s="46" t="n">
+      <c r="I18" s="53" t="n">
         <v>-0.03</v>
       </c>
       <c r="J18" s="4" t="n">
@@ -3434,7 +5340,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>571</v>
+        <v>699</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>137</v>
@@ -3443,7 +5349,7 @@
         <v>138</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>130</v>
@@ -3457,7 +5363,7 @@
       <c r="H19" s="16" t="n">
         <v>1807</v>
       </c>
-      <c r="I19" s="45" t="n">
+      <c r="I19" s="52" t="n">
         <v>0.275</v>
       </c>
       <c r="J19" s="4"/>
@@ -3469,7 +5375,7 @@
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>573</v>
+        <v>701</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>146</v>
@@ -3478,7 +5384,7 @@
         <v>128</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>147</v>
@@ -3492,7 +5398,7 @@
       <c r="H20" s="16" t="n">
         <v>1328</v>
       </c>
-      <c r="I20" s="45" t="n">
+      <c r="I20" s="52" t="n">
         <v>0.068</v>
       </c>
       <c r="J20" s="4"/>
@@ -3504,7 +5410,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>574</v>
+        <v>702</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>139</v>
@@ -3513,7 +5419,7 @@
         <v>121</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>70</v>
@@ -3527,7 +5433,7 @@
       <c r="H21" s="16" t="n">
         <v>1643</v>
       </c>
-      <c r="I21" s="44" t="n">
+      <c r="I21" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="4" t="n">
@@ -3543,7 +5449,7 @@
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>576</v>
+        <v>704</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>140</v>
@@ -3552,7 +5458,7 @@
         <v>121</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>181</v>
@@ -3566,7 +5472,7 @@
       <c r="H22" s="16" t="n">
         <v>1573</v>
       </c>
-      <c r="I22" s="43" t="n">
+      <c r="I22" s="50" t="n">
         <v>-0.112</v>
       </c>
       <c r="J22" s="4" t="n">
@@ -3582,7 +5488,7 @@
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>577</v>
+        <v>705</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>148</v>
@@ -3591,7 +5497,7 @@
         <v>121</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>181</v>
@@ -3605,7 +5511,7 @@
       <c r="H23" s="16" t="n">
         <v>1112</v>
       </c>
-      <c r="I23" s="46" t="n">
+      <c r="I23" s="53" t="n">
         <v>-0.033</v>
       </c>
       <c r="J23" s="4" t="n">
@@ -3621,7 +5527,7 @@
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>578</v>
+        <v>706</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>142</v>
@@ -3630,7 +5536,7 @@
         <v>121</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>181</v>
@@ -3644,7 +5550,7 @@
       <c r="H24" s="16" t="n">
         <v>1290</v>
       </c>
-      <c r="I24" s="45" t="n">
+      <c r="I24" s="52" t="n">
         <v>0.069</v>
       </c>
       <c r="J24" s="4" t="n">
@@ -3662,7 +5568,7 @@
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>579</v>
+        <v>707</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>144</v>
@@ -3671,7 +5577,7 @@
         <v>124</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>560</v>
+        <v>688</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>181</v>
@@ -3685,7 +5591,7 @@
       <c r="H25" s="16" t="n">
         <v>1144</v>
       </c>
-      <c r="I25" s="45" t="n">
+      <c r="I25" s="52" t="n">
         <v>0.177</v>
       </c>
       <c r="J25" s="4" t="n">
@@ -3701,7 +5607,7 @@
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>580</v>
+        <v>708</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>143</v>
@@ -3710,7 +5616,7 @@
         <v>121</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>181</v>
@@ -3724,7 +5630,7 @@
       <c r="H26" s="16" t="n">
         <v>1363</v>
       </c>
-      <c r="I26" s="46" t="n">
+      <c r="I26" s="53" t="n">
         <v>0.042</v>
       </c>
       <c r="J26" s="4" t="n">
@@ -3740,7 +5646,7 @@
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>581</v>
+        <v>709</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>155</v>
@@ -3749,7 +5655,7 @@
         <v>124</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>560</v>
+        <v>688</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>181</v>
@@ -3763,7 +5669,7 @@
       <c r="H27" s="16" t="n">
         <v>823</v>
       </c>
-      <c r="I27" s="45" t="n">
+      <c r="I27" s="52" t="n">
         <v>0.083</v>
       </c>
       <c r="J27" s="4" t="n">
@@ -3779,7 +5685,7 @@
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>582</v>
+        <v>710</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>158</v>
@@ -3788,7 +5694,7 @@
         <v>121</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>556</v>
+        <v>684</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>111</v>
@@ -3802,7 +5708,7 @@
       <c r="H28" s="16" t="n">
         <v>680</v>
       </c>
-      <c r="I28" s="44" t="n">
+      <c r="I28" s="51" t="n">
         <v>-0.033</v>
       </c>
       <c r="J28" s="4" t="n">
@@ -3818,7 +5724,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>583</v>
+        <v>711</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>157</v>
@@ -3827,7 +5733,7 @@
         <v>121</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>181</v>
@@ -3841,7 +5747,7 @@
       <c r="H29" s="16" t="n">
         <v>816</v>
       </c>
-      <c r="I29" s="46" t="n">
+      <c r="I29" s="53" t="n">
         <v>-0.045</v>
       </c>
       <c r="J29" s="4" t="n">
@@ -3857,7 +5763,7 @@
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>584</v>
+        <v>712</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>172</v>
@@ -3866,7 +5772,7 @@
         <v>121</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>556</v>
+        <v>684</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>181</v>
@@ -3880,7 +5786,7 @@
       <c r="H30" s="16" t="n">
         <v>423</v>
       </c>
-      <c r="I30" s="43" t="n">
+      <c r="I30" s="50" t="n">
         <v>-0.084</v>
       </c>
       <c r="J30" s="4" t="n">
@@ -3896,7 +5802,7 @@
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>585</v>
+        <v>713</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>154</v>
@@ -3905,7 +5811,7 @@
         <v>121</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>92</v>
@@ -3919,7 +5825,7 @@
       <c r="H31" s="16" t="n">
         <v>1025</v>
       </c>
-      <c r="I31" s="44" t="n">
+      <c r="I31" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="4" t="n">
@@ -3935,7 +5841,7 @@
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>586</v>
+        <v>714</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>149</v>
@@ -3944,7 +5850,7 @@
         <v>150</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>181</v>
@@ -3958,7 +5864,7 @@
       <c r="H32" s="16" t="n">
         <v>864</v>
       </c>
-      <c r="I32" s="45" t="n">
+      <c r="I32" s="52" t="n">
         <v>0.186</v>
       </c>
       <c r="J32" s="4" t="n">
@@ -3974,7 +5880,7 @@
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>587</v>
+        <v>715</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>152</v>
@@ -3983,7 +5889,7 @@
         <v>153</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>69</v>
@@ -3997,7 +5903,7 @@
       <c r="H33" s="16" t="n">
         <v>952</v>
       </c>
-      <c r="I33" s="44" t="n">
+      <c r="I33" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
@@ -4013,7 +5919,7 @@
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>588</v>
+        <v>716</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>147</v>
@@ -4022,7 +5928,7 @@
         <v>138</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>181</v>
@@ -4036,7 +5942,7 @@
       <c r="H34" s="16" t="n">
         <v>922</v>
       </c>
-      <c r="I34" s="45" t="n">
+      <c r="I34" s="52" t="n">
         <v>0.18</v>
       </c>
       <c r="J34" s="4" t="n">
@@ -4052,7 +5958,7 @@
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>589</v>
+        <v>717</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>156</v>
@@ -4061,7 +5967,7 @@
         <v>121</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>560</v>
+        <v>688</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>181</v>
@@ -4075,7 +5981,7 @@
       <c r="H35" s="16" t="n">
         <v>931</v>
       </c>
-      <c r="I35" s="43" t="n">
+      <c r="I35" s="50" t="n">
         <v>-0.068</v>
       </c>
       <c r="J35" s="4" t="n">
@@ -4091,7 +5997,7 @@
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>590</v>
+        <v>718</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>151</v>
@@ -4100,7 +6006,7 @@
         <v>121</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>181</v>
@@ -4114,7 +6020,7 @@
       <c r="H36" s="16" t="n">
         <v>913</v>
       </c>
-      <c r="I36" s="43" t="n">
+      <c r="I36" s="50" t="n">
         <v>-0.533</v>
       </c>
       <c r="J36" s="4" t="n">
@@ -4132,7 +6038,7 @@
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>591</v>
+        <v>719</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>161</v>
@@ -4141,7 +6047,7 @@
         <v>128</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>181</v>
@@ -4155,7 +6061,7 @@
       <c r="H37" s="16" t="n">
         <v>938</v>
       </c>
-      <c r="I37" s="45" t="n">
+      <c r="I37" s="52" t="n">
         <v>0.083</v>
       </c>
       <c r="J37" s="4" t="n">
@@ -4171,7 +6077,7 @@
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>592</v>
+        <v>720</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>159</v>
@@ -4180,7 +6086,7 @@
         <v>138</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E38" s="4" t="n">
         <v>26</v>
@@ -4194,7 +6100,7 @@
       <c r="H38" s="16" t="n">
         <v>1227</v>
       </c>
-      <c r="I38" s="44" t="n">
+      <c r="I38" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="4"/>
@@ -4206,7 +6112,7 @@
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>593</v>
+        <v>721</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>169</v>
@@ -4215,7 +6121,7 @@
         <v>138</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>181</v>
@@ -4229,7 +6135,7 @@
       <c r="H39" s="16" t="n">
         <v>538</v>
       </c>
-      <c r="I39" s="46" t="n">
+      <c r="I39" s="53" t="n">
         <v>-0.044</v>
       </c>
       <c r="J39" s="4" t="n">
@@ -4245,7 +6151,7 @@
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>594</v>
+        <v>722</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>163</v>
@@ -4254,7 +6160,7 @@
         <v>121</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>556</v>
+        <v>684</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>181</v>
@@ -4268,7 +6174,7 @@
       <c r="H40" s="16" t="n">
         <v>537</v>
       </c>
-      <c r="I40" s="43" t="n">
+      <c r="I40" s="50" t="n">
         <v>-0.126</v>
       </c>
       <c r="J40" s="4" t="n">
@@ -4284,7 +6190,7 @@
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>595</v>
+        <v>723</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>162</v>
@@ -4293,7 +6199,7 @@
         <v>138</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E41" s="4" t="n">
         <v>68</v>
@@ -4307,7 +6213,7 @@
       <c r="H41" s="16" t="n">
         <v>800</v>
       </c>
-      <c r="I41" s="44" t="n">
+      <c r="I41" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="4" t="n">
@@ -4323,7 +6229,7 @@
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>596</v>
+        <v>724</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>174</v>
@@ -4332,7 +6238,7 @@
         <v>175</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E42" s="4" t="n">
         <v>181</v>
@@ -4346,7 +6252,7 @@
       <c r="H42" s="16" t="n">
         <v>441</v>
       </c>
-      <c r="I42" s="46" t="n">
+      <c r="I42" s="53" t="n">
         <v>-0.029</v>
       </c>
       <c r="J42" s="4" t="n">
@@ -4362,7 +6268,7 @@
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>597</v>
+        <v>725</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>160</v>
@@ -4371,7 +6277,7 @@
         <v>121</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>181</v>
@@ -4385,7 +6291,7 @@
       <c r="H43" s="16" t="n">
         <v>807</v>
       </c>
-      <c r="I43" s="43" t="n">
+      <c r="I43" s="50" t="n">
         <v>-0.121</v>
       </c>
       <c r="J43" s="4" t="n">
@@ -4401,7 +6307,7 @@
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>598</v>
+        <v>726</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>164</v>
@@ -4410,7 +6316,7 @@
         <v>124</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="E44" s="4" t="n">
         <v>181</v>
@@ -4424,7 +6330,7 @@
       <c r="H44" s="16" t="n">
         <v>685</v>
       </c>
-      <c r="I44" s="45" t="n">
+      <c r="I44" s="52" t="n">
         <v>0.082</v>
       </c>
       <c r="J44" s="4" t="n">
@@ -4440,7 +6346,7 @@
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>599</v>
+        <v>727</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>165</v>
@@ -4449,7 +6355,7 @@
         <v>166</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>181</v>
@@ -4463,7 +6369,7 @@
       <c r="H45" s="16" t="n">
         <v>591</v>
       </c>
-      <c r="I45" s="45" t="n">
+      <c r="I45" s="52" t="n">
         <v>0.327</v>
       </c>
       <c r="J45" s="4" t="n">
@@ -4479,7 +6385,7 @@
     </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>600</v>
+        <v>728</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>170</v>
@@ -4488,7 +6394,7 @@
         <v>121</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E46" s="4" t="n">
         <v>181</v>
@@ -4502,7 +6408,7 @@
       <c r="H46" s="16" t="n">
         <v>586</v>
       </c>
-      <c r="I46" s="43" t="n">
+      <c r="I46" s="50" t="n">
         <v>-0.123</v>
       </c>
       <c r="J46" s="4" t="n">
@@ -4518,7 +6424,7 @@
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>601</v>
+        <v>729</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>167</v>
@@ -4527,7 +6433,7 @@
         <v>138</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>602</v>
+        <v>730</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>181</v>
@@ -4541,7 +6447,7 @@
       <c r="H47" s="16" t="n">
         <v>650</v>
       </c>
-      <c r="I47" s="46" t="n">
+      <c r="I47" s="53" t="n">
         <v>-0.009</v>
       </c>
       <c r="J47" s="4" t="n">
@@ -4557,7 +6463,7 @@
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>603</v>
+        <v>731</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>168</v>
@@ -4566,7 +6472,7 @@
         <v>150</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E48" s="4" t="n">
         <v>181</v>
@@ -4580,7 +6486,7 @@
       <c r="H48" s="16" t="n">
         <v>469</v>
       </c>
-      <c r="I48" s="45" t="n">
+      <c r="I48" s="52" t="n">
         <v>0.064</v>
       </c>
       <c r="J48" s="4" t="n">
@@ -4596,7 +6502,7 @@
     </row>
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>604</v>
+        <v>732</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>176</v>
@@ -4605,7 +6511,7 @@
         <v>150</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>181</v>
@@ -4619,7 +6525,7 @@
       <c r="H49" s="16" t="n">
         <v>402</v>
       </c>
-      <c r="I49" s="45" t="n">
+      <c r="I49" s="52" t="n">
         <v>0.256</v>
       </c>
       <c r="J49" s="4" t="n">
@@ -4635,7 +6541,7 @@
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>605</v>
+        <v>733</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>171</v>
@@ -4644,7 +6550,7 @@
         <v>121</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>181</v>
@@ -4658,7 +6564,7 @@
       <c r="H50" s="16" t="n">
         <v>456</v>
       </c>
-      <c r="I50" s="43" t="n">
+      <c r="I50" s="50" t="n">
         <v>-0.249</v>
       </c>
       <c r="J50" s="4" t="n">
@@ -4676,7 +6582,7 @@
     </row>
     <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>606</v>
+        <v>734</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>173</v>
@@ -4685,7 +6591,7 @@
         <v>121</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>56</v>
@@ -4699,7 +6605,7 @@
       <c r="H51" s="16" t="n">
         <v>451</v>
       </c>
-      <c r="I51" s="44" t="n">
+      <c r="I51" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="4"/>
@@ -4711,7 +6617,7 @@
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>607</v>
+        <v>735</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>177</v>
@@ -4720,7 +6626,7 @@
         <v>124</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>181</v>
@@ -4734,7 +6640,7 @@
       <c r="H52" s="16" t="n">
         <v>455</v>
       </c>
-      <c r="I52" s="45" t="n">
+      <c r="I52" s="52" t="n">
         <v>0.137</v>
       </c>
       <c r="J52" s="4" t="n">
@@ -4750,7 +6656,7 @@
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>608</v>
+        <v>736</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>180</v>
@@ -4759,7 +6665,7 @@
         <v>128</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E53" s="4" t="n">
         <v>181</v>
@@ -4773,7 +6679,7 @@
       <c r="H53" s="16" t="n">
         <v>333</v>
       </c>
-      <c r="I53" s="46" t="n">
+      <c r="I53" s="53" t="n">
         <v>0.045</v>
       </c>
       <c r="J53" s="4" t="n">
@@ -4789,7 +6695,7 @@
     </row>
     <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>609</v>
+        <v>737</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>178</v>
@@ -4798,7 +6704,7 @@
         <v>179</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>181</v>
@@ -4812,7 +6718,7 @@
       <c r="H54" s="16" t="n">
         <v>327</v>
       </c>
-      <c r="I54" s="46" t="n">
+      <c r="I54" s="53" t="n">
         <v>-0.028</v>
       </c>
       <c r="J54" s="4" t="n">
@@ -4828,7 +6734,7 @@
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>610</v>
+        <v>738</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>181</v>
@@ -4837,7 +6743,7 @@
         <v>138</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>181</v>
@@ -4851,7 +6757,7 @@
       <c r="H55" s="16" t="n">
         <v>281</v>
       </c>
-      <c r="I55" s="45" t="n">
+      <c r="I55" s="52" t="n">
         <v>0.188</v>
       </c>
       <c r="J55" s="4" t="n">
@@ -4867,7 +6773,7 @@
     </row>
     <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>611</v>
+        <v>739</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>182</v>
@@ -4876,7 +6782,7 @@
         <v>138</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>554</v>
+        <v>682</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>181</v>
@@ -4890,7 +6796,7 @@
       <c r="H56" s="16" t="n">
         <v>408</v>
       </c>
-      <c r="I56" s="45" t="n">
+      <c r="I56" s="52" t="n">
         <v>0.06</v>
       </c>
       <c r="J56" s="4" t="n">
@@ -4906,7 +6812,7 @@
     </row>
     <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>612</v>
+        <v>740</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>183</v>
@@ -4915,7 +6821,7 @@
         <v>184</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>39</v>
@@ -4929,7 +6835,7 @@
       <c r="H57" s="16" t="n">
         <v>196</v>
       </c>
-      <c r="I57" s="44" t="n">
+      <c r="I57" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="4"/>
@@ -4941,7 +6847,7 @@
     </row>
     <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>613</v>
+        <v>741</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>185</v>
@@ -4950,7 +6856,7 @@
         <v>186</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>572</v>
+        <v>700</v>
       </c>
       <c r="E58" s="4" t="n">
         <v>6</v>
@@ -4964,7 +6870,7 @@
       <c r="H58" s="16" t="n">
         <v>154</v>
       </c>
-      <c r="I58" s="44" t="n">
+      <c r="I58" s="51" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="4" t="n">

--- a/docs/commercial-plan.xlsx
+++ b/docs/commercial-plan.xlsx
@@ -8,20 +8,21 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإطار" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنافسون" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="السيطرة الميدانية" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="وقود · أفراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="وقود · شركات" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العقار والتأجير" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإكسسوارات" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تكلفة اللتر" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجريبي — ثلاث محطات" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تشخيص فقدان الحركة" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج العامل" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مطابقة الوردية مع الطلب" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجربة الشرايع" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="البيانات" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بيانات الورديات" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأداء المالي — يوليو ٢٠٢٦" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="وقود · أفراد" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنافسون" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="السيطرة الميدانية" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="وقود · شركات" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العقار والتأجير" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإكسسوارات" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تكلفة اللتر" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجريبي — ثلاث محطات" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تشخيص فقدان الحركة" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج العامل" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مطابقة الوردية مع الطلب" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجربة الشرايع" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="البيانات" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بيانات الورديات" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -30,7 +31,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="23">
+  <numFmts count="28">
     <numFmt numFmtId="164" formatCode="#,##0&quot; م&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="\+0.0;\-0.0"/>
@@ -54,6 +55,11 @@
     <numFmt numFmtId="184" formatCode="0.00;-0.00;&quot;&quot;"/>
     <numFmt numFmtId="185" formatCode="+#,##0;-#,##0"/>
     <numFmt numFmtId="186" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="187" formatCode="#,##0;(#,##0)"/>
+    <numFmt numFmtId="188" formatCode="+#,##0;(#,##0)"/>
+    <numFmt numFmtId="189" formatCode="#,##0.0"/>
+    <numFmt numFmtId="190" formatCode="(#,##0)"/>
+    <numFmt numFmtId="191" formatCode="0.00;;&quot;&quot;"/>
   </numFmts>
   <fonts count="44">
     <font>
@@ -342,7 +348,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -468,8 +474,13 @@
         <fgColor rgb="00D6E9E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5831F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -609,6 +620,50 @@
         <color rgb="00E3DCD1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E3DCD1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E3DCD1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E3DCD1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E3DCD1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E3DCD1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E3DCD1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E3DCD1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E3DCD1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -620,7 +675,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1251,6 +1306,63 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="187" fontId="30" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="188" fontId="30" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="187" fontId="30" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="188" fontId="30" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="189" fontId="30" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="190" fontId="30" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="189" fontId="31" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="188" fontId="31" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="190" fontId="31" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="30" fillId="20" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="189" fontId="30" fillId="20" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="191" fontId="39" fillId="20" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -1684,7 +1796,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>الخطة التجارية — ثلاثة منافذ بيع</t>
         </is>
@@ -1696,7 +1808,7 @@
       <c r="F1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>الوقود (شركات · أفراد) · العقار والتأجير · الإكسسوارات</t>
         </is>
@@ -1877,7 +1989,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="107">
       <c r="A10" s="109" t="n"/>
-      <c r="B10" s="115" t="inlineStr">
+      <c r="B10" s="128" t="inlineStr">
         <is>
           <t>المبدأ</t>
         </is>
@@ -1890,7 +2002,7 @@
     <row r="11" ht="15.75" customHeight="1" s="107">
       <c r="A11" s="109" t="n"/>
       <c r="B11" s="109" t="n"/>
-      <c r="C11" s="116" t="inlineStr">
+      <c r="C11" s="129" t="inlineStr">
         <is>
           <t>•  ثلاثة منافذ فقط — وكل ما عداها يخدمها أو يتبعها</t>
         </is>
@@ -1902,7 +2014,7 @@
     <row r="12" ht="15.75" customHeight="1" s="107">
       <c r="A12" s="109" t="n"/>
       <c r="B12" s="109" t="n"/>
-      <c r="C12" s="116" t="inlineStr">
+      <c r="C12" s="129" t="inlineStr">
         <is>
           <t>•  الوقود قناتان مختلفتان تماماً في العميل وأداة البيع والمنافس</t>
         </is>
@@ -1914,7 +2026,7 @@
     <row r="13" ht="15.75" customHeight="1" s="107">
       <c r="A13" s="109" t="n"/>
       <c r="B13" s="109" t="n"/>
-      <c r="C13" s="116" t="inlineStr">
+      <c r="C13" s="129" t="inlineStr">
         <is>
           <t>•  في العقار والإكسسوارات لا مسيطر — وهما أضعف منافذنا وأقلّها منافسة</t>
         </is>
@@ -1946,7 +2058,7 @@
     <row r="16" ht="15.75" customHeight="1" s="107">
       <c r="A16" s="109" t="n"/>
       <c r="B16" s="109" t="n"/>
-      <c r="C16" s="116" t="inlineStr">
+      <c r="C16" s="129" t="inlineStr">
         <is>
           <t>•  الوحدة الشاغرة تُحسب تكلفة لا فرصة ضائعة — التمويل والإهلاك مدفوعان</t>
         </is>
@@ -1958,7 +2070,7 @@
     <row r="17" ht="15.75" customHeight="1" s="107">
       <c r="A17" s="109" t="n"/>
       <c r="B17" s="109" t="n"/>
-      <c r="C17" s="116" t="inlineStr">
+      <c r="C17" s="129" t="inlineStr">
         <is>
           <t>•  فعمولة الوسيط أرخص من بقاء الوحدة شاغرة</t>
         </is>
@@ -1970,7 +2082,7 @@
     <row r="18" ht="15.75" customHeight="1" s="107">
       <c r="A18" s="109" t="n"/>
       <c r="B18" s="109" t="n"/>
-      <c r="C18" s="116" t="inlineStr">
+      <c r="C18" s="129" t="inlineStr">
         <is>
           <t>•  وسعر الوقود مقنَّن — فالربح من الحجم والخدمة لا من السعر</t>
         </is>
@@ -2002,6 +2114,618 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="106" min="1" max="1"/>
+    <col width="26" customWidth="1" style="106" min="2" max="2"/>
+    <col width="16" customWidth="1" style="106" min="3" max="5"/>
+    <col width="38" customWidth="1" style="106" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="107">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>النموذج التجريبي</t>
+        </is>
+      </c>
+      <c r="B1" s="109" t="n"/>
+      <c r="C1" s="109" t="n"/>
+      <c r="D1" s="109" t="n"/>
+      <c r="E1" s="109" t="n"/>
+      <c r="F1" s="109" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="107">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>محطتان للوقود ومحطة للمستأجرين</t>
+        </is>
+      </c>
+      <c r="B2" s="109" t="n"/>
+      <c r="C2" s="109" t="n"/>
+      <c r="D2" s="109" t="n"/>
+      <c r="E2" s="109" t="n"/>
+      <c r="F2" s="109" t="n"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="107">
+      <c r="A3" s="142" t="inlineStr">
+        <is>
+          <t>التصميم</t>
+        </is>
+      </c>
+      <c r="B3" s="143" t="n"/>
+      <c r="C3" s="143" t="n"/>
+      <c r="D3" s="143" t="n"/>
+      <c r="E3" s="143" t="n"/>
+      <c r="F3" s="143" t="n"/>
+    </row>
+    <row r="4" ht="21.75" customHeight="1" s="107">
+      <c r="A4" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="113" t="inlineStr">
+        <is>
+          <t>عرفات الشوقية MK017</t>
+        </is>
+      </c>
+      <c r="C4" s="112" t="inlineStr">
+        <is>
+          <t>وقود</t>
+        </is>
+      </c>
+      <c r="D4" s="114" t="inlineStr">
+        <is>
+          <t>نامية +6.9%</t>
+        </is>
+      </c>
+      <c r="E4" s="114" t="n"/>
+      <c r="F4" s="114" t="inlineStr">
+        <is>
+          <t>المرجع — ماذا تفعل الناجحة</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.75" customHeight="1" s="107">
+      <c r="A5" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="113" t="inlineStr">
+        <is>
+          <t>بن درويش MK023</t>
+        </is>
+      </c>
+      <c r="C5" s="112" t="inlineStr">
+        <is>
+          <t>وقود</t>
+        </is>
+      </c>
+      <c r="D5" s="114" t="inlineStr">
+        <is>
+          <t>هابطة −12.1%</t>
+        </is>
+      </c>
+      <c r="E5" s="114" t="n"/>
+      <c r="F5" s="114" t="inlineStr">
+        <is>
+          <t>الهدف — ما الذي يمكن تغييره</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="107">
+      <c r="A6" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="113" t="inlineStr">
+        <is>
+          <t>النورية MK007</t>
+        </is>
+      </c>
+      <c r="C6" s="112" t="inlineStr">
+        <is>
+          <t>مستأجرون</t>
+        </is>
+      </c>
+      <c r="D6" s="114" t="inlineStr">
+        <is>
+          <t>أعلى حركة 4,236 زيارة/يوم</t>
+        </is>
+      </c>
+      <c r="E6" s="114" t="n"/>
+      <c r="F6" s="114" t="inlineStr">
+        <is>
+          <t>حملات المستأجرين وقياس أثرها</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="109" t="n"/>
+      <c r="B7" s="109" t="n"/>
+      <c r="C7" s="109" t="n"/>
+      <c r="D7" s="109" t="n"/>
+      <c r="E7" s="109" t="n"/>
+      <c r="F7" s="109" t="n"/>
+    </row>
+    <row r="8" ht="21.75" customHeight="1" s="107">
+      <c r="A8" s="142" t="inlineStr">
+        <is>
+          <t>مقارنة محطتَي الوقود</t>
+        </is>
+      </c>
+      <c r="B8" s="143" t="n"/>
+      <c r="C8" s="143" t="n"/>
+      <c r="D8" s="143" t="n"/>
+      <c r="E8" s="143" t="n"/>
+      <c r="F8" s="143" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="107">
+      <c r="A9" s="111" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="111" t="inlineStr">
+        <is>
+          <t>المؤشر</t>
+        </is>
+      </c>
+      <c r="C9" s="111" t="inlineStr">
+        <is>
+          <t>عرفات الشوقية</t>
+        </is>
+      </c>
+      <c r="D9" s="111" t="inlineStr">
+        <is>
+          <t>بن درويش</t>
+        </is>
+      </c>
+      <c r="E9" s="111" t="inlineStr">
+        <is>
+          <t>الفارق</t>
+        </is>
+      </c>
+      <c r="F9" s="111" t="inlineStr">
+        <is>
+          <t>الدلالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" s="107">
+      <c r="A10" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="148" t="inlineStr">
+        <is>
+          <t>النمو</t>
+        </is>
+      </c>
+      <c r="C10" s="112" t="inlineStr">
+        <is>
+          <t>+6.9%</t>
+        </is>
+      </c>
+      <c r="D10" s="112" t="inlineStr">
+        <is>
+          <t>-12.1%</t>
+        </is>
+      </c>
+      <c r="E10" s="112" t="n"/>
+      <c r="F10" s="114" t="inlineStr">
+        <is>
+          <t>المتغيّر المراد تفسيره</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" s="107">
+      <c r="A11" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="148" t="inlineStr">
+        <is>
+          <t>المنطقة والنمط</t>
+        </is>
+      </c>
+      <c r="C11" s="112" t="inlineStr">
+        <is>
+          <t>مكة · حيوية</t>
+        </is>
+      </c>
+      <c r="D11" s="112" t="inlineStr">
+        <is>
+          <t>مكة · حيوية</t>
+        </is>
+      </c>
+      <c r="E11" s="112" t="n"/>
+      <c r="F11" s="114" t="inlineStr">
+        <is>
+          <t>متطابق</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1" s="107">
+      <c r="A12" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="148" t="inlineStr">
+        <is>
+          <t>المزيج</t>
+        </is>
+      </c>
+      <c r="C12" s="112" t="inlineStr">
+        <is>
+          <t>51.7 / 48.3</t>
+        </is>
+      </c>
+      <c r="D12" s="112" t="inlineStr">
+        <is>
+          <t>54.0 / 46.0</t>
+        </is>
+      </c>
+      <c r="E12" s="112" t="n"/>
+      <c r="F12" s="114" t="inlineStr">
+        <is>
+          <t>متطابق · بلا ديزل</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1" s="107">
+      <c r="A13" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="148" t="inlineStr">
+        <is>
+          <t>طريقة الدفع</t>
+        </is>
+      </c>
+      <c r="C13" s="112" t="inlineStr">
+        <is>
+          <t>نقد 100%</t>
+        </is>
+      </c>
+      <c r="D13" s="112" t="inlineStr">
+        <is>
+          <t>نقد 100%</t>
+        </is>
+      </c>
+      <c r="E13" s="112" t="n"/>
+      <c r="F13" s="114" t="inlineStr">
+        <is>
+          <t>صفر شبكة وصفر تطبيق</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18.75" customHeight="1" s="107">
+      <c r="A14" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="148" t="inlineStr">
+        <is>
+          <t>الزيارات يومياً</t>
+        </is>
+      </c>
+      <c r="C14" s="169" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D14" s="169" t="n">
+        <v>807</v>
+      </c>
+      <c r="E14" s="170">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="114" t="n"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1" s="107">
+      <c r="A15" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="148" t="inlineStr">
+        <is>
+          <t>اللترات يومياً</t>
+        </is>
+      </c>
+      <c r="C15" s="169" t="n">
+        <v>27210</v>
+      </c>
+      <c r="D15" s="169" t="n">
+        <v>16162</v>
+      </c>
+      <c r="E15" s="170">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="114" t="n"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1" s="107">
+      <c r="A16" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="148" t="inlineStr">
+        <is>
+          <t>لتر لكل زيارة</t>
+        </is>
+      </c>
+      <c r="C16" s="169" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D16" s="169" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="E16" s="170">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="114" t="inlineStr">
+        <is>
+          <t>سلة أكبر في عرفات</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" s="107">
+      <c r="A17" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="148" t="inlineStr">
+        <is>
+          <t>المضخات</t>
+        </is>
+      </c>
+      <c r="C17" s="169" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="169" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="170">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="114" t="n"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" s="107">
+      <c r="A18" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="148" t="inlineStr">
+        <is>
+          <t>زيارة لكل مضخة</t>
+        </is>
+      </c>
+      <c r="C18" s="169" t="n">
+        <v>143</v>
+      </c>
+      <c r="D18" s="169" t="n">
+        <v>202</v>
+      </c>
+      <c r="E18" s="170">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="114" t="inlineStr">
+        <is>
+          <t>بن درويش أزحم رغم أنها أصغر</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" s="107">
+      <c r="A19" s="112" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="148" t="inlineStr">
+        <is>
+          <t>العمال</t>
+        </is>
+      </c>
+      <c r="C19" s="169" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" s="169" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="170">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="114" t="inlineStr">
+        <is>
+          <t>مطابق للمتفق عليه</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18.75" customHeight="1" s="107">
+      <c r="A20" s="112" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="148" t="inlineStr">
+        <is>
+          <t>الشكاوى</t>
+        </is>
+      </c>
+      <c r="C20" s="169" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="170">
+        <f>C20-D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="114" t="inlineStr">
+        <is>
+          <t>بن درويش بلا شكاوى رغم تراجعها</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="109" t="n"/>
+      <c r="B21" s="109" t="n"/>
+      <c r="C21" s="109" t="n"/>
+      <c r="D21" s="109" t="n"/>
+      <c r="E21" s="109" t="n"/>
+      <c r="F21" s="109" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="107">
+      <c r="A22" s="109" t="n"/>
+      <c r="B22" s="128" t="inlineStr">
+        <is>
+          <t>ما يعزله التصميم</t>
+        </is>
+      </c>
+      <c r="C22" s="109" t="n"/>
+      <c r="D22" s="109" t="n"/>
+      <c r="E22" s="109" t="n"/>
+      <c r="F22" s="109" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="107">
+      <c r="A23" s="109" t="n"/>
+      <c r="B23" s="109" t="n"/>
+      <c r="C23" s="129" t="inlineStr">
+        <is>
+          <t>•  نفس المنطقة والنمط والمزيج وطريقة الدفع</t>
+        </is>
+      </c>
+      <c r="D23" s="109" t="n"/>
+      <c r="E23" s="109" t="n"/>
+      <c r="F23" s="109" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="107">
+      <c r="A24" s="109" t="n"/>
+      <c r="B24" s="109" t="n"/>
+      <c r="C24" s="129" t="inlineStr">
+        <is>
+          <t>•  فالفارق لا يُفسَّر بالموقع ولا المنتج ولا نوع العميل</t>
+        </is>
+      </c>
+      <c r="D24" s="109" t="n"/>
+      <c r="E24" s="109" t="n"/>
+      <c r="F24" s="109" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="109" t="n"/>
+      <c r="B25" s="109" t="n"/>
+      <c r="C25" s="109" t="n"/>
+      <c r="D25" s="109" t="n"/>
+      <c r="E25" s="109" t="n"/>
+      <c r="F25" s="109" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="107">
+      <c r="A26" s="109" t="n"/>
+      <c r="B26" s="128" t="inlineStr">
+        <is>
+          <t>ما يُقاس ميدانياً</t>
+        </is>
+      </c>
+      <c r="C26" s="109" t="n"/>
+      <c r="D26" s="109" t="n"/>
+      <c r="E26" s="109" t="n"/>
+      <c r="F26" s="109" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="107">
+      <c r="A27" s="109" t="n"/>
+      <c r="B27" s="109" t="n"/>
+      <c r="C27" s="129" t="inlineStr">
+        <is>
+          <t>•  زمن الخدمة لكل تعبئة في ساعة الذروة (21)</t>
+        </is>
+      </c>
+      <c r="D27" s="109" t="n"/>
+      <c r="E27" s="109" t="n"/>
+      <c r="F27" s="109" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="107">
+      <c r="A28" s="109" t="n"/>
+      <c r="B28" s="109" t="n"/>
+      <c r="C28" s="129" t="inlineStr">
+        <is>
+          <t>•  عدد المركبات التي تدخل ولا تعبّئ</t>
+        </is>
+      </c>
+      <c r="D28" s="109" t="n"/>
+      <c r="E28" s="109" t="n"/>
+      <c r="F28" s="109" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="107">
+      <c r="A29" s="109" t="n"/>
+      <c r="B29" s="109" t="n"/>
+      <c r="C29" s="129" t="inlineStr">
+        <is>
+          <t>•  المنافس الأقرب والمسافة إليه · وتغيّرات المسار</t>
+        </is>
+      </c>
+      <c r="D29" s="109" t="n"/>
+      <c r="E29" s="109" t="n"/>
+      <c r="F29" s="109" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="109" t="n"/>
+      <c r="B30" s="109" t="n"/>
+      <c r="C30" s="109" t="n"/>
+      <c r="D30" s="109" t="n"/>
+      <c r="E30" s="109" t="n"/>
+      <c r="F30" s="109" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="107">
+      <c r="A31" s="109" t="n"/>
+      <c r="B31" s="117" t="inlineStr">
+        <is>
+          <t>فرصة فورية مشتركة</t>
+        </is>
+      </c>
+      <c r="C31" s="109" t="n"/>
+      <c r="D31" s="109" t="n"/>
+      <c r="E31" s="109" t="n"/>
+      <c r="F31" s="109" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="107">
+      <c r="A32" s="109" t="n"/>
+      <c r="B32" s="109" t="n"/>
+      <c r="C32" s="129" t="inlineStr">
+        <is>
+          <t>•  الدفع نقد 100% في المحطتين — تفعيل الشبكة والتطبيق يبني قاعدة تعريف من الصفر</t>
+        </is>
+      </c>
+      <c r="D32" s="109" t="n"/>
+      <c r="E32" s="109" t="n"/>
+      <c r="F32" s="109" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="107">
+      <c r="A33" s="109" t="n"/>
+      <c r="B33" s="109" t="n"/>
+      <c r="C33" s="129" t="inlineStr">
+        <is>
+          <t>•  بن درويش 4 مضخات لـ807 زيارة — أقل من نصف طاقة عرفات</t>
+        </is>
+      </c>
+      <c r="D33" s="109" t="n"/>
+      <c r="E33" s="109" t="n"/>
+      <c r="F33" s="109" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -2012,7 +2736,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>تشخيص فقدان الحركة — مكة</t>
         </is>
@@ -2025,7 +2749,7 @@
       <c r="G1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>بيانات يناير – 4 أغسطس 2026 · السبب مؤكَّد ميدانياً لكل حالة</t>
         </is>
@@ -2541,7 +3265,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" s="107">
       <c r="A23" s="109" t="n"/>
-      <c r="B23" s="115" t="inlineStr">
+      <c r="B23" s="128" t="inlineStr">
         <is>
           <t>ما تثبته البيانات</t>
         </is>
@@ -2555,7 +3279,7 @@
     <row r="24" ht="15.75" customHeight="1" s="107">
       <c r="A24" s="109" t="n"/>
       <c r="B24" s="109" t="n"/>
-      <c r="C24" s="116" t="inlineStr">
+      <c r="C24" s="129" t="inlineStr">
         <is>
           <t>•  سلة العميل ثابتة في كل المحطات — فالفقد في عدد العملاء لا في سلوكهم</t>
         </is>
@@ -2568,7 +3292,7 @@
     <row r="25" ht="15.75" customHeight="1" s="107">
       <c r="A25" s="109" t="n"/>
       <c r="B25" s="109" t="n"/>
-      <c r="C25" s="116" t="inlineStr">
+      <c r="C25" s="129" t="inlineStr">
         <is>
           <t>•  المعيصم والشرايع سقطتا في فبراير بنسبة 60% و53% في شهر واحد</t>
         </is>
@@ -2581,7 +3305,7 @@
     <row r="26" ht="15.75" customHeight="1" s="107">
       <c r="A26" s="109" t="n"/>
       <c r="B26" s="109" t="n"/>
-      <c r="C26" s="116" t="inlineStr">
+      <c r="C26" s="129" t="inlineStr">
         <is>
           <t>•  العمرة والعزيزية تراجعتا موسمياً في أبريل–مايو ثم تعافتا في يونيو–يوليو</t>
         </is>
@@ -2616,7 +3340,7 @@
     <row r="29" ht="15.75" customHeight="1" s="107">
       <c r="A29" s="109" t="n"/>
       <c r="B29" s="109" t="n"/>
-      <c r="C29" s="116" t="inlineStr">
+      <c r="C29" s="129" t="inlineStr">
         <is>
           <t>•  الخدمة ليست السبب — لو كانت لانخفضت السلة أو لتدرّج الأثر</t>
         </is>
@@ -2629,7 +3353,7 @@
     <row r="30" ht="15.75" customHeight="1" s="107">
       <c r="A30" s="109" t="n"/>
       <c r="B30" s="109" t="n"/>
-      <c r="C30" s="116" t="inlineStr">
+      <c r="C30" s="129" t="inlineStr">
         <is>
           <t>•  المضخات ليست السبب — الطاقة لم تتغيّر والزيارات هي التي اختفت</t>
         </is>
@@ -2642,7 +3366,7 @@
     <row r="31" ht="15.75" customHeight="1" s="107">
       <c r="A31" s="109" t="n"/>
       <c r="B31" s="109" t="n"/>
-      <c r="C31" s="116" t="inlineStr">
+      <c r="C31" s="129" t="inlineStr">
         <is>
           <t>•  التسعير ليس السبب — السعر مقنَّن وموحّد</t>
         </is>
@@ -2677,7 +3401,7 @@
     <row r="34" ht="15.75" customHeight="1" s="107">
       <c r="A34" s="109" t="n"/>
       <c r="B34" s="109" t="n"/>
-      <c r="C34" s="116" t="inlineStr">
+      <c r="C34" s="129" t="inlineStr">
         <is>
           <t>•  حدثان خارجيان كلّفانا 2.1 مليون ريال هامش سنوياً</t>
         </is>
@@ -2690,7 +3414,7 @@
     <row r="35" ht="15.75" customHeight="1" s="107">
       <c r="A35" s="109" t="n"/>
       <c r="B35" s="109" t="n"/>
-      <c r="C35" s="116" t="inlineStr">
+      <c r="C35" s="129" t="inlineStr">
         <is>
           <t>•  واكتُشفا بعد شهور — لا بنظام إنذار بل بتحليل لاحق</t>
         </is>
@@ -2703,7 +3427,7 @@
     <row r="36" ht="15.75" customHeight="1" s="107">
       <c r="A36" s="109" t="n"/>
       <c r="B36" s="109" t="n"/>
-      <c r="C36" s="116" t="inlineStr">
+      <c r="C36" s="129" t="inlineStr">
         <is>
           <t>•  الأولوية: نظام تنبيه أسبوعي على مستوى المحطة قبل أي مبادرة أخرى</t>
         </is>
@@ -2736,7 +3460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2912,12 +3636,13 @@
           <t>هامش المساهمة (هللة/لتر)</t>
         </is>
       </c>
-      <c r="C12" s="183" t="n">
-        <v>13.36</v>
+      <c r="C12" s="234">
+        <f>IFERROR(INDEX('بيانات الورديات'!$P$4:$P$8,MATCH($C$4,'بيانات الورديات'!$B$4:$B$8,0)),0)</f>
+        <v/>
       </c>
       <c r="E12" s="137" t="inlineStr">
         <is>
-          <t>من قائمة الدخل</t>
+          <t>من تقرير يوليو ٢٠٢٦</t>
         </is>
       </c>
     </row>
@@ -4573,10 +5298,10 @@
       <formula1>"نعم,لا"</formula1>
     </dataValidation>
     <dataValidation sqref="C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='بيانات الورديات'!$Q$4:$Q$5</formula1>
+      <formula1>='بيانات الورديات'!$T$4:$T$5</formula1>
     </dataValidation>
     <dataValidation sqref="J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="قيمة غير معتمدة" error="اكتب: مستوفاة أو غير مستوفاة" type="list">
-      <formula1>='بيانات الورديات'!$R$4:$R$5</formula1>
+      <formula1>='بيانات الورديات'!$U$4:$U$5</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -4585,7 +5310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5013,7 +5738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5029,7 +5754,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>تجربة الشرايع MK019 — خدمة ممتازة وتوزيع مناديل</t>
         </is>
@@ -5042,7 +5767,7 @@
       <c r="G1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>المنافس يعترض العميل قبلنا · والعميل ما زال يمرّ — فالتجربة اختبار لسبب التجاوز</t>
         </is>
@@ -5267,7 +5992,7 @@
           <t>تكلفة الوحدة الموزّعة (ريال)</t>
         </is>
       </c>
-      <c r="C13" s="146" t="n"/>
+      <c r="C13" s="183" t="n"/>
       <c r="D13" s="109" t="n"/>
       <c r="E13" s="109" t="n"/>
       <c r="F13" s="109" t="n"/>
@@ -5293,7 +6018,7 @@
           <t>تكلفة إضافية أخرى شهرياً (تدريب · مشرف)</t>
         </is>
       </c>
-      <c r="C15" s="154" t="n"/>
+      <c r="C15" s="185" t="n"/>
       <c r="D15" s="109" t="n"/>
       <c r="E15" s="109" t="n"/>
       <c r="F15" s="109" t="n"/>
@@ -5306,7 +6031,7 @@
           <t>مدة التجربة (أسبوع)</t>
         </is>
       </c>
-      <c r="C16" s="160" t="n">
+      <c r="C16" s="186" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="109" t="n"/>
@@ -5961,7 +6686,7 @@
     </row>
     <row r="47" ht="15" customHeight="1" s="107">
       <c r="A47" s="109" t="n"/>
-      <c r="B47" s="115" t="inlineStr">
+      <c r="B47" s="128" t="inlineStr">
         <is>
           <t>لماذا الشرايع تحديداً</t>
         </is>
@@ -5975,7 +6700,7 @@
     <row r="48" ht="15.75" customHeight="1" s="107">
       <c r="A48" s="109" t="n"/>
       <c r="B48" s="109" t="n"/>
-      <c r="C48" s="116" t="inlineStr">
+      <c r="C48" s="129" t="inlineStr">
         <is>
           <t>•  الفقد سببه اعتراض منافس — والعميل ما زال يمرّ على الطريق</t>
         </is>
@@ -5988,7 +6713,7 @@
     <row r="49" ht="15.75" customHeight="1" s="107">
       <c r="A49" s="109" t="n"/>
       <c r="B49" s="109" t="n"/>
-      <c r="C49" s="116" t="inlineStr">
+      <c r="C49" s="129" t="inlineStr">
         <is>
           <t>•  فالتدخل يختبر سؤالاً واحداً: هل يعطي سبباً كافياً لتجاوز المنافس؟</t>
         </is>
@@ -6001,7 +6726,7 @@
     <row r="50" ht="15.75" customHeight="1" s="107">
       <c r="A50" s="109" t="n"/>
       <c r="B50" s="109" t="n"/>
-      <c r="C50" s="116" t="inlineStr">
+      <c r="C50" s="129" t="inlineStr">
         <is>
           <t>•  بخلاف المعيصم حيث الطريق نفسه تغيّر — ولا تدخّل يعيد سيارة لا تمرّ</t>
         </is>
@@ -6036,7 +6761,7 @@
     <row r="53" ht="15.75" customHeight="1" s="107">
       <c r="A53" s="109" t="n"/>
       <c r="B53" s="109" t="n"/>
-      <c r="C53" s="116" t="inlineStr">
+      <c r="C53" s="129" t="inlineStr">
         <is>
           <t>•  الهامش لكل زيارة 3.09 ريال فقط — فتكلفة التوزيع تلتهمه بسرعة</t>
         </is>
@@ -6049,7 +6774,7 @@
     <row r="54" ht="15.75" customHeight="1" s="107">
       <c r="A54" s="109" t="n"/>
       <c r="B54" s="109" t="n"/>
-      <c r="C54" s="116" t="inlineStr">
+      <c r="C54" s="129" t="inlineStr">
         <is>
           <t>•  توزيع بريال واحد على كل الزيارات يحتاج نمواً 32% لمجرد التعادل</t>
         </is>
@@ -6062,7 +6787,7 @@
     <row r="55" ht="15.75" customHeight="1" s="107">
       <c r="A55" s="109" t="n"/>
       <c r="B55" s="109" t="n"/>
-      <c r="C55" s="116" t="inlineStr">
+      <c r="C55" s="129" t="inlineStr">
         <is>
           <t>•  وبريال على نصف الزيارات يحتاج 16% — وهو الأقرب للواقع</t>
         </is>
@@ -6075,7 +6800,7 @@
     <row r="56" ht="15.75" customHeight="1" s="107">
       <c r="A56" s="109" t="n"/>
       <c r="B56" s="109" t="n"/>
-      <c r="C56" s="116" t="inlineStr">
+      <c r="C56" s="129" t="inlineStr">
         <is>
           <t>•  ابدأ بالنسبة الأقل والتكلفة الأدنى ثم ارفع إن ثبت الأثر</t>
         </is>
@@ -6110,7 +6835,7 @@
     <row r="59" ht="15.75" customHeight="1" s="107">
       <c r="A59" s="109" t="n"/>
       <c r="B59" s="109" t="n"/>
-      <c r="C59" s="116" t="inlineStr">
+      <c r="C59" s="129" t="inlineStr">
         <is>
           <t>•  محطة مرجع تُقاس بالتوازي — عرفات الشوقية أو أي محطة مستقرة</t>
         </is>
@@ -6123,7 +6848,7 @@
     <row r="60" ht="15.75" customHeight="1" s="107">
       <c r="A60" s="109" t="n"/>
       <c r="B60" s="109" t="n"/>
-      <c r="C60" s="116" t="inlineStr">
+      <c r="C60" s="129" t="inlineStr">
         <is>
           <t>•  بدونها لا يمكن التفريق بين أثر التدخل وأثر الموسم</t>
         </is>
@@ -6136,7 +6861,7 @@
     <row r="61" ht="15.75" customHeight="1" s="107">
       <c r="A61" s="109" t="n"/>
       <c r="B61" s="109" t="n"/>
-      <c r="C61" s="116" t="inlineStr">
+      <c r="C61" s="129" t="inlineStr">
         <is>
           <t>•  والخدمة الممتازة يجب أن تُقاس بزمن التعبئة لا بالانطباع</t>
         </is>
@@ -6157,7 +6882,7 @@
     </row>
     <row r="63" ht="15" customHeight="1" s="107">
       <c r="A63" s="109" t="n"/>
-      <c r="B63" s="115" t="inlineStr">
+      <c r="B63" s="128" t="inlineStr">
         <is>
           <t>قرار الاستمرار</t>
         </is>
@@ -6171,7 +6896,7 @@
     <row r="64" ht="15.75" customHeight="1" s="107">
       <c r="A64" s="109" t="n"/>
       <c r="B64" s="109" t="n"/>
-      <c r="C64" s="116" t="inlineStr">
+      <c r="C64" s="129" t="inlineStr">
         <is>
           <t>•  بعد 8 أسابيع: إن تجاوز النمو نقطة التعادل يُعمَّم التدخل</t>
         </is>
@@ -6184,7 +6909,7 @@
     <row r="65" ht="15.75" customHeight="1" s="107">
       <c r="A65" s="109" t="n"/>
       <c r="B65" s="109" t="n"/>
-      <c r="C65" s="116" t="inlineStr">
+      <c r="C65" s="129" t="inlineStr">
         <is>
           <t>•  إن كان دون التعادل لكن الاتجاه صاعد يُمدَّد 4 أسابيع بتكلفة أقل</t>
         </is>
@@ -6197,7 +6922,7 @@
     <row r="66" ht="15.75" customHeight="1" s="107">
       <c r="A66" s="109" t="n"/>
       <c r="B66" s="109" t="n"/>
-      <c r="C66" s="116" t="inlineStr">
+      <c r="C66" s="129" t="inlineStr">
         <is>
           <t>•  إن لم يتحرك شيء فالسبب ليس الخدمة — والملف يعود لمعالجة الموقع</t>
         </is>
@@ -6235,7 +6960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6257,7 +6982,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>بيانات المحطات</t>
         </is>
@@ -6276,7 +7001,7 @@
       <c r="M1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>55 محطة · 1 يناير – 30 يونيو 2026 · 181 يوماً</t>
         </is>
@@ -8980,13 +9705,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="107" min="1" max="1"/>
@@ -9004,8 +9729,10 @@
     <col width="15" customWidth="1" style="107" min="13" max="13"/>
     <col width="9" customWidth="1" style="107" min="14" max="14"/>
     <col width="9" customWidth="1" style="107" min="15" max="15"/>
-    <col width="12" customWidth="1" style="107" min="17" max="17"/>
-    <col width="14" customWidth="1" style="107" min="18" max="18"/>
+    <col width="16" customWidth="1" style="107" min="16" max="16"/>
+    <col width="11" customWidth="1" style="107" min="17" max="17"/>
+    <col width="12" customWidth="1" style="107" min="20" max="20"/>
+    <col width="14" customWidth="1" style="107" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="107">
@@ -9098,12 +9825,22 @@
           <t>المضخات</t>
         </is>
       </c>
-      <c r="Q3" s="211" t="inlineStr">
+      <c r="P3" s="120" t="inlineStr">
+        <is>
+          <t>هامش المساهمة (هللة/لتر)</t>
+        </is>
+      </c>
+      <c r="Q3" s="120" t="inlineStr">
+        <is>
+          <t>نموذج العمل</t>
+        </is>
+      </c>
+      <c r="T3" s="211" t="inlineStr">
         <is>
           <t>الورديات</t>
         </is>
       </c>
-      <c r="R3" s="211" t="inlineStr">
+      <c r="U3" s="211" t="inlineStr">
         <is>
           <t>بوابة الجودة</t>
         </is>
@@ -9165,12 +9902,20 @@
       <c r="O4" s="200" t="n">
         <v>18</v>
       </c>
-      <c r="Q4" s="213" t="inlineStr">
+      <c r="P4" s="212" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="Q4" s="121" t="inlineStr">
+        <is>
+          <t>استثماري</t>
+        </is>
+      </c>
+      <c r="T4" s="213" t="inlineStr">
         <is>
           <t>صباحية</t>
         </is>
       </c>
-      <c r="R4" s="213" t="inlineStr">
+      <c r="U4" s="213" t="inlineStr">
         <is>
           <t>مستوفاة</t>
         </is>
@@ -9232,12 +9977,20 @@
       <c r="O5" s="200" t="n">
         <v>9</v>
       </c>
-      <c r="Q5" s="213" t="inlineStr">
+      <c r="P5" s="212" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="Q5" s="121" t="inlineStr">
+        <is>
+          <t>إيجاري</t>
+        </is>
+      </c>
+      <c r="T5" s="213" t="inlineStr">
         <is>
           <t>مسائية</t>
         </is>
       </c>
-      <c r="R5" s="213" t="inlineStr">
+      <c r="U5" s="213" t="inlineStr">
         <is>
           <t>غير مستوفاة</t>
         </is>
@@ -9299,6 +10052,14 @@
       <c r="O6" s="200" t="n">
         <v>10</v>
       </c>
+      <c r="P6" s="212" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="Q6" s="121" t="inlineStr">
+        <is>
+          <t>إيجاري</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="107">
       <c r="A7" s="121" t="n">
@@ -9356,6 +10117,14 @@
       <c r="O7" s="200" t="n">
         <v>4</v>
       </c>
+      <c r="P7" s="212" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="Q7" s="121" t="inlineStr">
+        <is>
+          <t>تشغيلي</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="107">
       <c r="A8" s="121" t="n">
@@ -9413,6 +10182,14 @@
       <c r="O8" s="200" t="n">
         <v>6</v>
       </c>
+      <c r="P8" s="212" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q8" s="121" t="inlineStr">
+        <is>
+          <t>إيجاري</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="137" t="inlineStr">
@@ -9430,8 +10207,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -9440,6 +10217,4147 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="107" min="1" max="1"/>
+    <col width="30" customWidth="1" style="107" min="2" max="2"/>
+    <col width="14" customWidth="1" style="107" min="3" max="3"/>
+    <col width="14" customWidth="1" style="107" min="4" max="4"/>
+    <col width="13" customWidth="1" style="107" min="5" max="5"/>
+    <col width="14" customWidth="1" style="107" min="6" max="6"/>
+    <col width="12" customWidth="1" style="107" min="7" max="7"/>
+    <col width="12" customWidth="1" style="107" min="8" max="8"/>
+    <col width="12" customWidth="1" style="107" min="9" max="9"/>
+    <col width="12" customWidth="1" style="107" min="10" max="10"/>
+    <col width="40" customWidth="1" style="107" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="107">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>الأداء المالي — يناير إلى يوليو ٢٠٢٦</t>
+        </is>
+      </c>
+      <c r="B1" s="109" t="n"/>
+      <c r="C1" s="109" t="n"/>
+      <c r="D1" s="109" t="n"/>
+      <c r="E1" s="109" t="n"/>
+      <c r="F1" s="109" t="n"/>
+      <c r="G1" s="109" t="n"/>
+      <c r="H1" s="109" t="n"/>
+      <c r="I1" s="109" t="n"/>
+      <c r="J1" s="109" t="n"/>
+      <c r="K1" s="109" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="107">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>من تقرير درب التجاري (النسخة المصححة) · ألف ريال سعودي</t>
+        </is>
+      </c>
+      <c r="B2" s="109" t="n"/>
+      <c r="C2" s="109" t="n"/>
+      <c r="D2" s="109" t="n"/>
+      <c r="E2" s="109" t="n"/>
+      <c r="F2" s="109" t="n"/>
+      <c r="G2" s="109" t="n"/>
+      <c r="H2" s="109" t="n"/>
+      <c r="I2" s="109" t="n"/>
+      <c r="J2" s="109" t="n"/>
+      <c r="K2" s="109" t="n"/>
+    </row>
+    <row r="3" ht="3.5" customHeight="1" s="107">
+      <c r="A3" s="214" t="n"/>
+      <c r="B3" s="214" t="n"/>
+      <c r="C3" s="214" t="n"/>
+      <c r="D3" s="214" t="n"/>
+      <c r="E3" s="214" t="n"/>
+      <c r="F3" s="214" t="n"/>
+      <c r="G3" s="214" t="n"/>
+      <c r="H3" s="214" t="n"/>
+      <c r="I3" s="214" t="n"/>
+      <c r="J3" s="214" t="n"/>
+      <c r="K3" s="214" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="107">
+      <c r="A4" s="131" t="inlineStr">
+        <is>
+          <t>① قائمة الدخل التراكمية</t>
+        </is>
+      </c>
+      <c r="B4" s="109" t="n"/>
+      <c r="C4" s="109" t="n"/>
+      <c r="D4" s="109" t="n"/>
+      <c r="E4" s="109" t="n"/>
+      <c r="F4" s="109" t="n"/>
+      <c r="G4" s="109" t="n"/>
+      <c r="H4" s="109" t="n"/>
+      <c r="I4" s="109" t="n"/>
+      <c r="J4" s="109" t="n"/>
+      <c r="K4" s="109" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="107">
+      <c r="A5" s="120" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="120" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="C5" s="120" t="inlineStr">
+        <is>
+          <t>الفعلي</t>
+        </is>
+      </c>
+      <c r="D5" s="120" t="inlineStr">
+        <is>
+          <t>الموازنة</t>
+        </is>
+      </c>
+      <c r="E5" s="120" t="inlineStr">
+        <is>
+          <t>الفرق</t>
+        </is>
+      </c>
+      <c r="F5" s="120" t="inlineStr">
+        <is>
+          <t>العام الماضي</t>
+        </is>
+      </c>
+      <c r="G5" s="120" t="inlineStr"/>
+      <c r="H5" s="120" t="inlineStr"/>
+      <c r="I5" s="120" t="inlineStr"/>
+      <c r="J5" s="120" t="inlineStr"/>
+      <c r="K5" s="120" t="inlineStr">
+        <is>
+          <t>ملاحظة</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" s="107">
+      <c r="A6" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="121" t="inlineStr">
+        <is>
+          <t>إيرادات الوقود</t>
+        </is>
+      </c>
+      <c r="C6" s="215" t="n">
+        <v>1173578</v>
+      </c>
+      <c r="D6" s="215" t="n">
+        <v>1219570</v>
+      </c>
+      <c r="E6" s="216" t="n">
+        <v>-45992</v>
+      </c>
+      <c r="F6" s="215" t="n">
+        <v>411451</v>
+      </c>
+      <c r="G6" s="121" t="n"/>
+      <c r="H6" s="121" t="n"/>
+      <c r="I6" s="121" t="n"/>
+      <c r="J6" s="121" t="n"/>
+      <c r="K6" s="217" t="n"/>
+    </row>
+    <row r="7" ht="19" customHeight="1" s="107">
+      <c r="A7" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="121" t="inlineStr">
+        <is>
+          <t>تكلفة المبيعات</t>
+        </is>
+      </c>
+      <c r="C7" s="215" t="n">
+        <v>-1133905</v>
+      </c>
+      <c r="D7" s="215" t="n">
+        <v>-1177404</v>
+      </c>
+      <c r="E7" s="216" t="n">
+        <v>43499</v>
+      </c>
+      <c r="F7" s="215" t="n">
+        <v>-391474</v>
+      </c>
+      <c r="G7" s="121" t="n"/>
+      <c r="H7" s="121" t="n"/>
+      <c r="I7" s="121" t="n"/>
+      <c r="J7" s="121" t="n"/>
+      <c r="K7" s="217" t="n"/>
+    </row>
+    <row r="8" ht="19" customHeight="1" s="107">
+      <c r="A8" s="218" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="194" t="inlineStr">
+        <is>
+          <t>هامش المساهمة — الوقود</t>
+        </is>
+      </c>
+      <c r="C8" s="219" t="n">
+        <v>39673</v>
+      </c>
+      <c r="D8" s="219" t="n">
+        <v>42166</v>
+      </c>
+      <c r="E8" s="220" t="n">
+        <v>-2493</v>
+      </c>
+      <c r="F8" s="219" t="n">
+        <v>19976</v>
+      </c>
+      <c r="G8" s="218" t="n"/>
+      <c r="H8" s="218" t="n"/>
+      <c r="I8" s="218" t="n"/>
+      <c r="J8" s="218" t="n"/>
+      <c r="K8" s="221" t="n"/>
+    </row>
+    <row r="9" ht="19" customHeight="1" s="107">
+      <c r="A9" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="121" t="inlineStr">
+        <is>
+          <t>صافي الإيراد العقاري</t>
+        </is>
+      </c>
+      <c r="C9" s="215" t="n">
+        <v>31465</v>
+      </c>
+      <c r="D9" s="215" t="n">
+        <v>33138</v>
+      </c>
+      <c r="E9" s="216" t="n">
+        <v>-1673</v>
+      </c>
+      <c r="F9" s="215" t="n">
+        <v>24887</v>
+      </c>
+      <c r="G9" s="121" t="n"/>
+      <c r="H9" s="121" t="n"/>
+      <c r="I9" s="121" t="n"/>
+      <c r="J9" s="121" t="n"/>
+      <c r="K9" s="217" t="n"/>
+    </row>
+    <row r="10" ht="19" customHeight="1" s="107">
+      <c r="A10" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="121" t="inlineStr">
+        <is>
+          <t>إهلاك أصول حق الاستخدام</t>
+        </is>
+      </c>
+      <c r="C10" s="215" t="n">
+        <v>-15347</v>
+      </c>
+      <c r="D10" s="215" t="n">
+        <v>-15999</v>
+      </c>
+      <c r="E10" s="216" t="n">
+        <v>652</v>
+      </c>
+      <c r="F10" s="215" t="n">
+        <v>-12391</v>
+      </c>
+      <c r="G10" s="121" t="n"/>
+      <c r="H10" s="121" t="n"/>
+      <c r="I10" s="121" t="n"/>
+      <c r="J10" s="121" t="n"/>
+      <c r="K10" s="217" t="n"/>
+    </row>
+    <row r="11" ht="19" customHeight="1" s="107">
+      <c r="A11" s="121" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="121" t="inlineStr">
+        <is>
+          <t>تكلفة التمويل</t>
+        </is>
+      </c>
+      <c r="C11" s="215" t="n">
+        <v>-15525</v>
+      </c>
+      <c r="D11" s="215" t="n">
+        <v>-14569</v>
+      </c>
+      <c r="E11" s="216" t="n">
+        <v>-956</v>
+      </c>
+      <c r="F11" s="215" t="n">
+        <v>-9828</v>
+      </c>
+      <c r="G11" s="121" t="n"/>
+      <c r="H11" s="121" t="n"/>
+      <c r="I11" s="121" t="n"/>
+      <c r="J11" s="121" t="n"/>
+      <c r="K11" s="217" t="n"/>
+    </row>
+    <row r="12" ht="19" customHeight="1" s="107">
+      <c r="A12" s="121" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="121" t="inlineStr">
+        <is>
+          <t>هامش المساهمة — العقارات</t>
+        </is>
+      </c>
+      <c r="C12" s="215" t="n">
+        <v>593</v>
+      </c>
+      <c r="D12" s="215" t="n">
+        <v>2570</v>
+      </c>
+      <c r="E12" s="216" t="n">
+        <v>-1977</v>
+      </c>
+      <c r="F12" s="215" t="n">
+        <v>2669</v>
+      </c>
+      <c r="G12" s="121" t="n"/>
+      <c r="H12" s="121" t="n"/>
+      <c r="I12" s="121" t="n"/>
+      <c r="J12" s="121" t="n"/>
+      <c r="K12" s="217" t="n"/>
+    </row>
+    <row r="13" ht="19" customHeight="1" s="107">
+      <c r="A13" s="121" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="121" t="inlineStr">
+        <is>
+          <t>مصاريف التشغيل</t>
+        </is>
+      </c>
+      <c r="C13" s="215" t="n">
+        <v>-28704</v>
+      </c>
+      <c r="D13" s="215" t="n">
+        <v>-27760</v>
+      </c>
+      <c r="E13" s="216" t="n">
+        <v>-944</v>
+      </c>
+      <c r="F13" s="215" t="n">
+        <v>-13962</v>
+      </c>
+      <c r="G13" s="121" t="n"/>
+      <c r="H13" s="121" t="n"/>
+      <c r="I13" s="121" t="n"/>
+      <c r="J13" s="121" t="n"/>
+      <c r="K13" s="217" t="n"/>
+    </row>
+    <row r="14" ht="19" customHeight="1" s="107">
+      <c r="A14" s="218" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="194" t="inlineStr">
+        <is>
+          <t>مجمل الربح</t>
+        </is>
+      </c>
+      <c r="C14" s="219" t="n">
+        <v>11563</v>
+      </c>
+      <c r="D14" s="219" t="n">
+        <v>16976</v>
+      </c>
+      <c r="E14" s="220" t="n">
+        <v>-5413</v>
+      </c>
+      <c r="F14" s="219" t="n">
+        <v>8683</v>
+      </c>
+      <c r="G14" s="218" t="n"/>
+      <c r="H14" s="218" t="n"/>
+      <c r="I14" s="218" t="n"/>
+      <c r="J14" s="218" t="n"/>
+      <c r="K14" s="221" t="n"/>
+    </row>
+    <row r="15" ht="19" customHeight="1" s="107">
+      <c r="A15" s="121" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="121" t="inlineStr">
+        <is>
+          <t>عمومية وإدارية + بيع وتوزيع</t>
+        </is>
+      </c>
+      <c r="C15" s="215" t="n">
+        <v>-13958</v>
+      </c>
+      <c r="D15" s="215" t="n">
+        <v>-10927</v>
+      </c>
+      <c r="E15" s="216" t="n">
+        <v>-3031</v>
+      </c>
+      <c r="F15" s="215" t="n">
+        <v>-12063</v>
+      </c>
+      <c r="G15" s="121" t="n"/>
+      <c r="H15" s="121" t="n"/>
+      <c r="I15" s="121" t="n"/>
+      <c r="J15" s="121" t="n"/>
+      <c r="K15" s="217" t="n"/>
+    </row>
+    <row r="16" ht="19" customHeight="1" s="107">
+      <c r="A16" s="121" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="121" t="inlineStr">
+        <is>
+          <t>فوائد القروض</t>
+        </is>
+      </c>
+      <c r="C16" s="215" t="n">
+        <v>-3043</v>
+      </c>
+      <c r="D16" s="215" t="n">
+        <v>-1653</v>
+      </c>
+      <c r="E16" s="216" t="n">
+        <v>-1390</v>
+      </c>
+      <c r="F16" s="215" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G16" s="121" t="n"/>
+      <c r="H16" s="121" t="n"/>
+      <c r="I16" s="121" t="n"/>
+      <c r="J16" s="121" t="n"/>
+      <c r="K16" s="217" t="n"/>
+    </row>
+    <row r="17" ht="19" customHeight="1" s="107">
+      <c r="A17" s="121" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="121" t="inlineStr">
+        <is>
+          <t>الزكاة</t>
+        </is>
+      </c>
+      <c r="C17" s="215" t="n">
+        <v>-120</v>
+      </c>
+      <c r="D17" s="215" t="n">
+        <v>-110</v>
+      </c>
+      <c r="E17" s="216" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F17" s="215" t="n">
+        <v>-101</v>
+      </c>
+      <c r="G17" s="121" t="n"/>
+      <c r="H17" s="121" t="n"/>
+      <c r="I17" s="121" t="n"/>
+      <c r="J17" s="121" t="n"/>
+      <c r="K17" s="217" t="n"/>
+    </row>
+    <row r="18" ht="19" customHeight="1" s="107">
+      <c r="A18" s="218" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="194" t="inlineStr">
+        <is>
+          <t>صافي الدخل</t>
+        </is>
+      </c>
+      <c r="C18" s="219" t="n">
+        <v>-5535</v>
+      </c>
+      <c r="D18" s="219" t="n">
+        <v>4285</v>
+      </c>
+      <c r="E18" s="220" t="n">
+        <v>-9820</v>
+      </c>
+      <c r="F18" s="219" t="n">
+        <v>-3941</v>
+      </c>
+      <c r="G18" s="218" t="n"/>
+      <c r="H18" s="218" t="n"/>
+      <c r="I18" s="218" t="n"/>
+      <c r="J18" s="218" t="n"/>
+      <c r="K18" s="221" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="109" t="n"/>
+      <c r="B19" s="109" t="n"/>
+      <c r="C19" s="109" t="n"/>
+      <c r="D19" s="109" t="n"/>
+      <c r="E19" s="109" t="n"/>
+      <c r="F19" s="109" t="n"/>
+      <c r="G19" s="109" t="n"/>
+      <c r="H19" s="109" t="n"/>
+      <c r="I19" s="109" t="n"/>
+      <c r="J19" s="109" t="n"/>
+      <c r="K19" s="109" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="107">
+      <c r="A20" s="131" t="inlineStr">
+        <is>
+          <t>② أداء نماذج العمل — قبل التحميل المركزي وبعده</t>
+        </is>
+      </c>
+      <c r="B20" s="109" t="n"/>
+      <c r="C20" s="109" t="n"/>
+      <c r="D20" s="109" t="n"/>
+      <c r="E20" s="109" t="n"/>
+      <c r="F20" s="109" t="n"/>
+      <c r="G20" s="109" t="n"/>
+      <c r="H20" s="109" t="n"/>
+      <c r="I20" s="109" t="n"/>
+      <c r="J20" s="109" t="n"/>
+      <c r="K20" s="109" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="107">
+      <c r="A21" s="120" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B21" s="120" t="inlineStr">
+        <is>
+          <t>النموذج</t>
+        </is>
+      </c>
+      <c r="C21" s="120" t="inlineStr">
+        <is>
+          <t>محطات</t>
+        </is>
+      </c>
+      <c r="D21" s="120" t="inlineStr">
+        <is>
+          <t>لتر (مليون)</t>
+        </is>
+      </c>
+      <c r="E21" s="120" t="inlineStr">
+        <is>
+          <t>الإيراد</t>
+        </is>
+      </c>
+      <c r="F21" s="120" t="inlineStr">
+        <is>
+          <t>هامش الوقود</t>
+        </is>
+      </c>
+      <c r="G21" s="120" t="inlineStr">
+        <is>
+          <t>هللة/لتر</t>
+        </is>
+      </c>
+      <c r="H21" s="120" t="inlineStr">
+        <is>
+          <t>قبل التحميل</t>
+        </is>
+      </c>
+      <c r="I21" s="120" t="inlineStr">
+        <is>
+          <t>التحميل</t>
+        </is>
+      </c>
+      <c r="J21" s="120" t="inlineStr">
+        <is>
+          <t>صافي الربح</t>
+        </is>
+      </c>
+      <c r="K21" s="120" t="inlineStr">
+        <is>
+          <t>القراءة</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" s="107">
+      <c r="A22" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="122" t="inlineStr">
+        <is>
+          <t>استثماري</t>
+        </is>
+      </c>
+      <c r="C22" s="200" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="222" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E22" s="132" t="n">
+        <v>174309</v>
+      </c>
+      <c r="F22" s="132" t="n">
+        <v>10765</v>
+      </c>
+      <c r="G22" s="212" t="n">
+        <v>11.72657952069717</v>
+      </c>
+      <c r="H22" s="216" t="n">
+        <v>9505</v>
+      </c>
+      <c r="I22" s="223" t="n">
+        <v>-4279</v>
+      </c>
+      <c r="J22" s="216" t="n">
+        <v>2722</v>
+      </c>
+      <c r="K22" s="224" t="inlineStr">
+        <is>
+          <t>الوحيد الرابح — وأعلى هامش لكل لتر</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" s="107">
+      <c r="A23" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="122" t="inlineStr">
+        <is>
+          <t>إيجاري</t>
+        </is>
+      </c>
+      <c r="C23" s="200" t="n">
+        <v>17</v>
+      </c>
+      <c r="D23" s="222" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="E23" s="132" t="n">
+        <v>146564</v>
+      </c>
+      <c r="F23" s="132" t="n">
+        <v>8787</v>
+      </c>
+      <c r="G23" s="212" t="n">
+        <v>11.30888030888031</v>
+      </c>
+      <c r="H23" s="216" t="n">
+        <v>-1290</v>
+      </c>
+      <c r="I23" s="223" t="n">
+        <v>-4279</v>
+      </c>
+      <c r="J23" s="216" t="n">
+        <v>-7038</v>
+      </c>
+      <c r="K23" s="224" t="inlineStr">
+        <is>
+          <t>الخسارة من إهلاك حق الاستخدام والتمويل لا من التشغيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="107">
+      <c r="A24" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="122" t="inlineStr">
+        <is>
+          <t>تشغيلي</t>
+        </is>
+      </c>
+      <c r="C24" s="200" t="n">
+        <v>26</v>
+      </c>
+      <c r="D24" s="222" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="E24" s="132" t="n">
+        <v>268915</v>
+      </c>
+      <c r="F24" s="132" t="n">
+        <v>15984</v>
+      </c>
+      <c r="G24" s="212" t="n">
+        <v>11.32011331444759</v>
+      </c>
+      <c r="H24" s="216" t="n">
+        <v>6864</v>
+      </c>
+      <c r="I24" s="223" t="n">
+        <v>-5135</v>
+      </c>
+      <c r="J24" s="216" t="n">
+        <v>-1869</v>
+      </c>
+      <c r="K24" s="224" t="inlineStr">
+        <is>
+          <t>يربح قبل التحميل ويخسر بعده</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" s="107">
+      <c r="A25" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="122" t="inlineStr">
+        <is>
+          <t>امتياز</t>
+        </is>
+      </c>
+      <c r="C25" s="200" t="n">
+        <v>92</v>
+      </c>
+      <c r="D25" s="222" t="n">
+        <v>350.8</v>
+      </c>
+      <c r="E25" s="132" t="n">
+        <v>583790</v>
+      </c>
+      <c r="F25" s="132" t="n">
+        <v>4136</v>
+      </c>
+      <c r="G25" s="212" t="n">
+        <v>1.179019384264538</v>
+      </c>
+      <c r="H25" s="216" t="n">
+        <v>3296</v>
+      </c>
+      <c r="I25" s="223" t="n">
+        <v>-3424</v>
+      </c>
+      <c r="J25" s="216" t="n">
+        <v>609</v>
+      </c>
+      <c r="K25" s="224" t="inlineStr">
+        <is>
+          <t>نصف اللترات وعُشر الهامش — ١٫١٨ هللة/لتر</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="194" t="n"/>
+      <c r="B26" s="194" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="C26" s="225">
+        <f>SUM(C22:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="226">
+        <f>SUM(D22:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="195">
+        <f>SUM(E22:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="195">
+        <f>SUM(F22:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="227">
+        <f>IFERROR(F26*1000/(D26*1000000)*100,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="228">
+        <f>SUM(H22:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="229">
+        <f>SUM(I22:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="228">
+        <f>SUM(J22:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="194" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="109" t="n"/>
+      <c r="B27" s="109" t="n"/>
+      <c r="C27" s="109" t="n"/>
+      <c r="D27" s="109" t="n"/>
+      <c r="E27" s="109" t="n"/>
+      <c r="F27" s="109" t="n"/>
+      <c r="G27" s="109" t="n"/>
+      <c r="H27" s="109" t="n"/>
+      <c r="I27" s="109" t="n"/>
+      <c r="J27" s="109" t="n"/>
+      <c r="K27" s="109" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1" s="107">
+      <c r="A28" s="131" t="inlineStr">
+        <is>
+          <t>③ نقطة التعادل — أين تقف الشركة</t>
+        </is>
+      </c>
+      <c r="B28" s="109" t="n"/>
+      <c r="C28" s="109" t="n"/>
+      <c r="D28" s="109" t="n"/>
+      <c r="E28" s="109" t="n"/>
+      <c r="F28" s="109" t="n"/>
+      <c r="G28" s="109" t="n"/>
+      <c r="H28" s="109" t="n"/>
+      <c r="I28" s="109" t="n"/>
+      <c r="J28" s="109" t="n"/>
+      <c r="K28" s="109" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="107">
+      <c r="A29" s="109" t="n"/>
+      <c r="B29" s="230" t="inlineStr">
+        <is>
+          <t>مجمل الربح</t>
+        </is>
+      </c>
+      <c r="C29" s="190">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="D29" s="109" t="n"/>
+      <c r="E29" s="109" t="n"/>
+      <c r="F29" s="109" t="n"/>
+      <c r="G29" s="109" t="n"/>
+      <c r="H29" s="109" t="n"/>
+      <c r="I29" s="109" t="n"/>
+      <c r="J29" s="109" t="n"/>
+      <c r="K29" s="231" t="inlineStr">
+        <is>
+          <t>من قائمة الدخل أعلاه</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="107">
+      <c r="A30" s="109" t="n"/>
+      <c r="B30" s="230" t="inlineStr">
+        <is>
+          <t>التحميل المركزي</t>
+        </is>
+      </c>
+      <c r="C30" s="190">
+        <f>-I26</f>
+        <v/>
+      </c>
+      <c r="D30" s="109" t="n"/>
+      <c r="E30" s="109" t="n"/>
+      <c r="F30" s="109" t="n"/>
+      <c r="G30" s="109" t="n"/>
+      <c r="H30" s="109" t="n"/>
+      <c r="I30" s="109" t="n"/>
+      <c r="J30" s="109" t="n"/>
+      <c r="K30" s="231" t="inlineStr">
+        <is>
+          <t>بيع وتوزيع + عمومية + فوائد محمّلة</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="107">
+      <c r="A31" s="109" t="n"/>
+      <c r="B31" s="230" t="inlineStr">
+        <is>
+          <t>التحميل ÷ مجمل الربح</t>
+        </is>
+      </c>
+      <c r="C31" s="192">
+        <f>C30/C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="109" t="n"/>
+      <c r="E31" s="109" t="n"/>
+      <c r="F31" s="109" t="n"/>
+      <c r="G31" s="109" t="n"/>
+      <c r="H31" s="109" t="n"/>
+      <c r="I31" s="109" t="n"/>
+      <c r="J31" s="109" t="n"/>
+      <c r="K31" s="231" t="inlineStr">
+        <is>
+          <t>التحميل يتجاوز مجمل الربح — هنا أصل الخسارة</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="107">
+      <c r="A32" s="109" t="n"/>
+      <c r="B32" s="230" t="inlineStr">
+        <is>
+          <t>المحطات النشطة</t>
+        </is>
+      </c>
+      <c r="C32" s="232" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D32" s="109" t="n"/>
+      <c r="E32" s="109" t="n"/>
+      <c r="F32" s="109" t="n"/>
+      <c r="G32" s="109" t="n"/>
+      <c r="H32" s="109" t="n"/>
+      <c r="I32" s="109" t="n"/>
+      <c r="J32" s="109" t="n"/>
+      <c r="K32" s="231" t="inlineStr">
+        <is>
+          <t>خطة يوليو ١٩٨ · هدف ديسمبر ٢٣٢</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="107">
+      <c r="A33" s="109" t="n"/>
+      <c r="B33" s="230" t="inlineStr">
+        <is>
+          <t>مجمل الربح لكل محطة</t>
+        </is>
+      </c>
+      <c r="C33" s="233">
+        <f>C29/C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="109" t="n"/>
+      <c r="E33" s="109" t="n"/>
+      <c r="F33" s="109" t="n"/>
+      <c r="G33" s="109" t="n"/>
+      <c r="H33" s="109" t="n"/>
+      <c r="I33" s="109" t="n"/>
+      <c r="J33" s="109" t="n"/>
+      <c r="K33" s="231" t="inlineStr">
+        <is>
+          <t>ألف ريال / ٧ أشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" s="107">
+      <c r="A34" s="109" t="n"/>
+      <c r="B34" s="230" t="inlineStr">
+        <is>
+          <t>محطات التعادل المطلوبة</t>
+        </is>
+      </c>
+      <c r="C34" s="232">
+        <f>ROUND(C30/C33,0)</f>
+        <v/>
+      </c>
+      <c r="D34" s="109" t="n"/>
+      <c r="E34" s="109" t="n"/>
+      <c r="F34" s="109" t="n"/>
+      <c r="G34" s="109" t="n"/>
+      <c r="H34" s="109" t="n"/>
+      <c r="I34" s="109" t="n"/>
+      <c r="J34" s="109" t="n"/>
+      <c r="K34" s="231" t="inlineStr">
+        <is>
+          <t>عند مجمل الربح الحالي لكل محطة — الموازنة نفسها (١٩٨) كانت دون التعادل</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="109" t="n"/>
+      <c r="B35" s="109" t="n"/>
+      <c r="C35" s="109" t="n"/>
+      <c r="D35" s="109" t="n"/>
+      <c r="E35" s="109" t="n"/>
+      <c r="F35" s="109" t="n"/>
+      <c r="G35" s="109" t="n"/>
+      <c r="H35" s="109" t="n"/>
+      <c r="I35" s="109" t="n"/>
+      <c r="J35" s="109" t="n"/>
+      <c r="K35" s="109" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="109" t="n"/>
+      <c r="B36" s="109" t="n"/>
+      <c r="C36" s="109" t="n"/>
+      <c r="D36" s="109" t="n"/>
+      <c r="E36" s="109" t="n"/>
+      <c r="F36" s="109" t="n"/>
+      <c r="G36" s="109" t="n"/>
+      <c r="H36" s="109" t="n"/>
+      <c r="I36" s="109" t="n"/>
+      <c r="J36" s="109" t="n"/>
+      <c r="K36" s="109" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="109" t="n"/>
+      <c r="B37" s="128" t="inlineStr">
+        <is>
+          <t>ما تقوله الأرقام</t>
+        </is>
+      </c>
+      <c r="C37" s="109" t="n"/>
+      <c r="D37" s="109" t="n"/>
+      <c r="E37" s="109" t="n"/>
+      <c r="F37" s="109" t="n"/>
+      <c r="G37" s="109" t="n"/>
+      <c r="H37" s="109" t="n"/>
+      <c r="I37" s="109" t="n"/>
+      <c r="J37" s="109" t="n"/>
+      <c r="K37" s="109" t="n"/>
+    </row>
+    <row r="38" ht="16" customHeight="1" s="107">
+      <c r="A38" s="109" t="n"/>
+      <c r="B38" s="109" t="n"/>
+      <c r="C38" s="129" t="inlineStr">
+        <is>
+          <t>•  المحطات تربح +١٨٫٤ مليون قبل التحميل المركزي — والشركة تخسر (٥٫٥) بعده</t>
+        </is>
+      </c>
+      <c r="D38" s="109" t="n"/>
+      <c r="E38" s="109" t="n"/>
+      <c r="F38" s="109" t="n"/>
+      <c r="G38" s="109" t="n"/>
+      <c r="H38" s="109" t="n"/>
+      <c r="I38" s="109" t="n"/>
+      <c r="J38" s="109" t="n"/>
+      <c r="K38" s="109" t="n"/>
+    </row>
+    <row r="39" ht="16" customHeight="1" s="107">
+      <c r="A39" s="109" t="n"/>
+      <c r="B39" s="109" t="n"/>
+      <c r="C39" s="129" t="inlineStr">
+        <is>
+          <t>•  الامتياز ٥٣٪ من اللترات و١٠٪ من الهامش: ١٫١٨ هللة/لتر مقابل ١١٫٣ لبقية النماذج</t>
+        </is>
+      </c>
+      <c r="D39" s="109" t="n"/>
+      <c r="E39" s="109" t="n"/>
+      <c r="F39" s="109" t="n"/>
+      <c r="G39" s="109" t="n"/>
+      <c r="H39" s="109" t="n"/>
+      <c r="I39" s="109" t="n"/>
+      <c r="J39" s="109" t="n"/>
+      <c r="K39" s="109" t="n"/>
+    </row>
+    <row r="40" ht="16" customHeight="1" s="107">
+      <c r="A40" s="109" t="n"/>
+      <c r="B40" s="109" t="n"/>
+      <c r="C40" s="129" t="inlineStr">
+        <is>
+          <t>•  محطة استثمارية واحدة تعادل ٦٩ محطة امتياز في صافي الربح</t>
+        </is>
+      </c>
+      <c r="D40" s="109" t="n"/>
+      <c r="E40" s="109" t="n"/>
+      <c r="F40" s="109" t="n"/>
+      <c r="G40" s="109" t="n"/>
+      <c r="H40" s="109" t="n"/>
+      <c r="I40" s="109" t="n"/>
+      <c r="J40" s="109" t="n"/>
+      <c r="K40" s="109" t="n"/>
+    </row>
+    <row r="41" ht="16" customHeight="1" s="107">
+      <c r="A41" s="109" t="n"/>
+      <c r="B41" s="109" t="n"/>
+      <c r="C41" s="129" t="inlineStr">
+        <is>
+          <t>•  الفوائد ٦٫٦ أضعاف العام الماضي وتجاوز الموازنة ٨٤٪ — أسرع بند نمواً</t>
+        </is>
+      </c>
+      <c r="D41" s="109" t="n"/>
+      <c r="E41" s="109" t="n"/>
+      <c r="F41" s="109" t="n"/>
+      <c r="G41" s="109" t="n"/>
+      <c r="H41" s="109" t="n"/>
+      <c r="I41" s="109" t="n"/>
+      <c r="J41" s="109" t="n"/>
+      <c r="K41" s="109" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="109" t="n"/>
+      <c r="B42" s="109" t="n"/>
+      <c r="C42" s="109" t="n"/>
+      <c r="D42" s="109" t="n"/>
+      <c r="E42" s="109" t="n"/>
+      <c r="F42" s="109" t="n"/>
+      <c r="G42" s="109" t="n"/>
+      <c r="H42" s="109" t="n"/>
+      <c r="I42" s="109" t="n"/>
+      <c r="J42" s="109" t="n"/>
+      <c r="K42" s="109" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="109" t="n"/>
+      <c r="B43" s="117" t="inlineStr">
+        <is>
+          <t>ما يحتاج تحققاً قبل أي قرار</t>
+        </is>
+      </c>
+      <c r="C43" s="109" t="n"/>
+      <c r="D43" s="109" t="n"/>
+      <c r="E43" s="109" t="n"/>
+      <c r="F43" s="109" t="n"/>
+      <c r="G43" s="109" t="n"/>
+      <c r="H43" s="109" t="n"/>
+      <c r="I43" s="109" t="n"/>
+      <c r="J43" s="109" t="n"/>
+      <c r="K43" s="109" t="n"/>
+    </row>
+    <row r="44" ht="16" customHeight="1" s="107">
+      <c r="A44" s="109" t="n"/>
+      <c r="B44" s="109" t="n"/>
+      <c r="C44" s="129" t="inlineStr">
+        <is>
+          <t>•  مفتاح توزيع العمومية غير مُفسَّر: ٦ محطات استثمارية تحمل ما تحمله ١٧ إيجارية</t>
+        </is>
+      </c>
+      <c r="D44" s="109" t="n"/>
+      <c r="E44" s="109" t="n"/>
+      <c r="F44" s="109" t="n"/>
+      <c r="G44" s="109" t="n"/>
+      <c r="H44" s="109" t="n"/>
+      <c r="I44" s="109" t="n"/>
+      <c r="J44" s="109" t="n"/>
+      <c r="K44" s="109" t="n"/>
+    </row>
+    <row r="45" ht="16" customHeight="1" s="107">
+      <c r="A45" s="109" t="n"/>
+      <c r="B45" s="109" t="n"/>
+      <c r="C45" s="129" t="inlineStr">
+        <is>
+          <t>•  خسارة العقار قد تكون محاسبية لا نقدية — تمويل IFRS 16 مُقدَّم التحميل والعقود جديدة</t>
+        </is>
+      </c>
+      <c r="D45" s="109" t="n"/>
+      <c r="E45" s="109" t="n"/>
+      <c r="F45" s="109" t="n"/>
+      <c r="G45" s="109" t="n"/>
+      <c r="H45" s="109" t="n"/>
+      <c r="I45" s="109" t="n"/>
+      <c r="J45" s="109" t="n"/>
+      <c r="K45" s="109" t="n"/>
+    </row>
+    <row r="46" ht="16" customHeight="1" s="107">
+      <c r="A46" s="109" t="n"/>
+      <c r="B46" s="109" t="n"/>
+      <c r="C46" s="129" t="inlineStr">
+        <is>
+          <t>•  رفع هامش الامتياز نقطة يعطي ٥٫٨ مليون، لكن هامش المُمتاز نفسه غير معروض</t>
+        </is>
+      </c>
+      <c r="D46" s="109" t="n"/>
+      <c r="E46" s="109" t="n"/>
+      <c r="F46" s="109" t="n"/>
+      <c r="G46" s="109" t="n"/>
+      <c r="H46" s="109" t="n"/>
+      <c r="I46" s="109" t="n"/>
+      <c r="J46" s="109" t="n"/>
+      <c r="K46" s="109" t="n"/>
+    </row>
+    <row r="47" ht="16" customHeight="1" s="107">
+      <c r="A47" s="109" t="n"/>
+      <c r="B47" s="109" t="n"/>
+      <c r="C47" s="129" t="inlineStr">
+        <is>
+          <t>•  فجوة ٦٬٧٣٨ بين صافي المحطات ومجمل الربح ما زالت مفتوحة في التقرير</t>
+        </is>
+      </c>
+      <c r="D47" s="109" t="n"/>
+      <c r="E47" s="109" t="n"/>
+      <c r="F47" s="109" t="n"/>
+      <c r="G47" s="109" t="n"/>
+      <c r="H47" s="109" t="n"/>
+      <c r="I47" s="109" t="n"/>
+      <c r="J47" s="109" t="n"/>
+      <c r="K47" s="109" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C38:K38"/>
+    <mergeCell ref="C47:K47"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="C41:K41"/>
+    <mergeCell ref="C44:K44"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="C40:K40"/>
+    <mergeCell ref="C45:K45"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C46:K46"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E6:E18">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="9">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="10">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22:J25">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="7">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="8">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="7">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:K87"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="106" min="1" max="1"/>
+    <col width="24" customWidth="1" style="106" min="2" max="2"/>
+    <col width="13" customWidth="1" style="106" min="3" max="4"/>
+    <col width="12" customWidth="1" style="106" min="5" max="7"/>
+    <col width="13" customWidth="1" style="106" min="8" max="10"/>
+    <col width="34" customWidth="1" style="106" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="107">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>الوقود — قناة الأفراد</t>
+        </is>
+      </c>
+      <c r="B1" s="109" t="n"/>
+      <c r="C1" s="109" t="n"/>
+      <c r="D1" s="109" t="n"/>
+      <c r="E1" s="109" t="n"/>
+      <c r="F1" s="109" t="n"/>
+      <c r="G1" s="109" t="n"/>
+      <c r="H1" s="109" t="n"/>
+      <c r="I1" s="109" t="n"/>
+      <c r="J1" s="109" t="n"/>
+      <c r="K1" s="109" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="107">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>المنافس: كل مشغّلي المحطات · السلاح: سرعة الخدمة · الأداة: مستهدف لكل محطة وحافز لكل عامل</t>
+        </is>
+      </c>
+      <c r="B2" s="109" t="n"/>
+      <c r="C2" s="109" t="n"/>
+      <c r="D2" s="109" t="n"/>
+      <c r="E2" s="109" t="n"/>
+      <c r="F2" s="109" t="n"/>
+      <c r="G2" s="109" t="n"/>
+      <c r="H2" s="109" t="n"/>
+      <c r="I2" s="109" t="n"/>
+      <c r="J2" s="109" t="n"/>
+      <c r="K2" s="109" t="n"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="107">
+      <c r="A3" s="142" t="inlineStr">
+        <is>
+          <t>محاور الخطة الأربعة</t>
+        </is>
+      </c>
+      <c r="B3" s="143" t="n"/>
+      <c r="C3" s="143" t="n"/>
+      <c r="D3" s="143" t="n"/>
+      <c r="E3" s="143" t="n"/>
+      <c r="F3" s="143" t="n"/>
+      <c r="G3" s="143" t="n"/>
+      <c r="H3" s="143" t="n"/>
+      <c r="I3" s="143" t="n"/>
+      <c r="J3" s="143" t="n"/>
+      <c r="K3" s="143" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="107">
+      <c r="A4" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="113" t="inlineStr">
+        <is>
+          <t>تدريب العمالة</t>
+        </is>
+      </c>
+      <c r="C4" s="114" t="inlineStr">
+        <is>
+          <t>الشكاوى</t>
+        </is>
+      </c>
+      <c r="D4" s="114" t="inlineStr">
+        <is>
+          <t>56% من الشكاوى عن العامل: بطء الخدمة وسلوك</t>
+        </is>
+      </c>
+      <c r="E4" s="114" t="inlineStr">
+        <is>
+          <t>برنامج تدريب على زمن الخدمة والتعامل</t>
+        </is>
+      </c>
+      <c r="F4" s="114" t="n"/>
+      <c r="G4" s="114" t="n"/>
+      <c r="H4" s="114" t="n"/>
+      <c r="I4" s="114" t="n"/>
+      <c r="J4" s="114" t="n"/>
+      <c r="K4" s="114" t="inlineStr">
+        <is>
+          <t>يُقاس بانخفاض الشكاوى وزمن التعبئة</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="107">
+      <c r="A5" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="113" t="inlineStr">
+        <is>
+          <t>فهم مشاكل العملاء</t>
+        </is>
+      </c>
+      <c r="C5" s="114" t="inlineStr">
+        <is>
+          <t>الشكاوى + قوقل ماب</t>
+        </is>
+      </c>
+      <c r="D5" s="114" t="inlineStr">
+        <is>
+          <t>41 من 103 شكوى منشورة على قوقل ماب</t>
+        </is>
+      </c>
+      <c r="E5" s="114" t="inlineStr">
+        <is>
+          <t>تصنيف أسبوعي للشكاوى وإغلاقها بإجراء لا بتنبيه</t>
+        </is>
+      </c>
+      <c r="F5" s="114" t="n"/>
+      <c r="G5" s="114" t="n"/>
+      <c r="H5" s="114" t="n"/>
+      <c r="I5" s="114" t="n"/>
+      <c r="J5" s="114" t="n"/>
+      <c r="K5" s="114" t="inlineStr">
+        <is>
+          <t>من 58 شكوى: 31 انتهت بتنبيه وصفر إجراء</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="107">
+      <c r="A6" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="113" t="inlineStr">
+        <is>
+          <t>مستهدف وحافز</t>
+        </is>
+      </c>
+      <c r="C6" s="114" t="inlineStr">
+        <is>
+          <t>الجدول أدناه</t>
+        </is>
+      </c>
+      <c r="D6" s="114" t="inlineStr">
+        <is>
+          <t>مستهدف لكل محطة وحافز مرتبط به</t>
+        </is>
+      </c>
+      <c r="E6" s="114" t="inlineStr">
+        <is>
+          <t>الحافز نسبة من هامش اللتر الإضافي</t>
+        </is>
+      </c>
+      <c r="F6" s="114" t="n"/>
+      <c r="G6" s="114" t="n"/>
+      <c r="H6" s="114" t="n"/>
+      <c r="I6" s="114" t="n"/>
+      <c r="J6" s="114" t="n"/>
+      <c r="K6" s="114" t="inlineStr">
+        <is>
+          <t>يربط أجر العامل بنتيجة المحطة</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="107">
+      <c r="A7" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="113" t="inlineStr">
+        <is>
+          <t>خفض مصاريف المحطة</t>
+        </is>
+      </c>
+      <c r="C7" s="114" t="inlineStr">
+        <is>
+          <t>قائمة الدخل</t>
+        </is>
+      </c>
+      <c r="D7" s="114" t="inlineStr">
+        <is>
+          <t>المصاريف النقدية 0.94 هللة لكل لتر فقط</t>
+        </is>
+      </c>
+      <c r="E7" s="114" t="inlineStr">
+        <is>
+          <t>المجال ضيق — الأولوية للحجم لا للخفض</t>
+        </is>
+      </c>
+      <c r="F7" s="114" t="n"/>
+      <c r="G7" s="114" t="n"/>
+      <c r="H7" s="114" t="n"/>
+      <c r="I7" s="114" t="n"/>
+      <c r="J7" s="114" t="n"/>
+      <c r="K7" s="114" t="inlineStr">
+        <is>
+          <t>88% من المصاريف إهلاك غير قابل للخفض</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="109" t="n"/>
+      <c r="B8" s="109" t="n"/>
+      <c r="C8" s="109" t="n"/>
+      <c r="D8" s="109" t="n"/>
+      <c r="E8" s="109" t="n"/>
+      <c r="F8" s="109" t="n"/>
+      <c r="G8" s="109" t="n"/>
+      <c r="H8" s="109" t="n"/>
+      <c r="I8" s="109" t="n"/>
+      <c r="J8" s="109" t="n"/>
+      <c r="K8" s="109" t="n"/>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="107">
+      <c r="A9" s="142" t="inlineStr">
+        <is>
+          <t>مُدخلات النموذج</t>
+        </is>
+      </c>
+      <c r="B9" s="143" t="n"/>
+      <c r="C9" s="143" t="n"/>
+      <c r="D9" s="143" t="n"/>
+      <c r="E9" s="143" t="n"/>
+      <c r="F9" s="143" t="n"/>
+      <c r="G9" s="143" t="n"/>
+      <c r="H9" s="143" t="n"/>
+      <c r="I9" s="143" t="n"/>
+      <c r="J9" s="143" t="n"/>
+      <c r="K9" s="143" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="107">
+      <c r="A10" s="109" t="n"/>
+      <c r="B10" s="144" t="inlineStr">
+        <is>
+          <t>سعر البيع المرجّح (ريال/لتر)</t>
+        </is>
+      </c>
+      <c r="C10" s="145" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D10" s="109" t="n"/>
+      <c r="E10" s="109" t="n"/>
+      <c r="F10" s="109" t="n"/>
+      <c r="G10" s="109" t="n"/>
+      <c r="H10" s="109" t="n"/>
+      <c r="I10" s="109" t="n"/>
+      <c r="J10" s="109" t="n"/>
+      <c r="K10" s="109" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="107">
+      <c r="A11" s="109" t="n"/>
+      <c r="B11" s="144" t="inlineStr">
+        <is>
+          <t>هامش المساهمة لكل لتر (هللة)</t>
+        </is>
+      </c>
+      <c r="C11" s="183" t="n"/>
+      <c r="D11" s="109" t="n"/>
+      <c r="E11" s="109" t="n"/>
+      <c r="F11" s="109" t="n"/>
+      <c r="G11" s="109" t="n"/>
+      <c r="H11" s="109" t="n"/>
+      <c r="I11" s="109" t="n"/>
+      <c r="J11" s="109" t="n"/>
+      <c r="K11" s="109" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="107">
+      <c r="A12" s="109" t="n"/>
+      <c r="B12" s="144" t="inlineStr">
+        <is>
+          <t>نسبة الحافز من الهامش الإضافي</t>
+        </is>
+      </c>
+      <c r="C12" s="184" t="n"/>
+      <c r="D12" s="109" t="n"/>
+      <c r="E12" s="109" t="n"/>
+      <c r="F12" s="109" t="n"/>
+      <c r="G12" s="109" t="n"/>
+      <c r="H12" s="109" t="n"/>
+      <c r="I12" s="109" t="n"/>
+      <c r="J12" s="109" t="n"/>
+      <c r="K12" s="109" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="107">
+      <c r="A13" s="109" t="n"/>
+      <c r="B13" s="144" t="inlineStr">
+        <is>
+          <t>معدل النمو المستهدف للبنزين</t>
+        </is>
+      </c>
+      <c r="C13" s="184" t="n"/>
+      <c r="D13" s="109" t="n"/>
+      <c r="E13" s="109" t="n"/>
+      <c r="F13" s="109" t="n"/>
+      <c r="G13" s="109" t="n"/>
+      <c r="H13" s="109" t="n"/>
+      <c r="I13" s="109" t="n"/>
+      <c r="J13" s="109" t="n"/>
+      <c r="K13" s="109" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="109" t="n"/>
+      <c r="B14" s="109" t="n"/>
+      <c r="C14" s="109" t="n"/>
+      <c r="D14" s="109" t="n"/>
+      <c r="E14" s="109" t="n"/>
+      <c r="F14" s="109" t="n"/>
+      <c r="G14" s="109" t="n"/>
+      <c r="H14" s="109" t="n"/>
+      <c r="I14" s="109" t="n"/>
+      <c r="J14" s="109" t="n"/>
+      <c r="K14" s="109" t="n"/>
+    </row>
+    <row r="15" ht="21.75" customHeight="1" s="107">
+      <c r="A15" s="142" t="inlineStr">
+        <is>
+          <t>المستهدف والحافز لكل محطة</t>
+        </is>
+      </c>
+      <c r="B15" s="143" t="n"/>
+      <c r="C15" s="143" t="n"/>
+      <c r="D15" s="143" t="n"/>
+      <c r="E15" s="143" t="n"/>
+      <c r="F15" s="143" t="n"/>
+      <c r="G15" s="143" t="n"/>
+      <c r="H15" s="143" t="n"/>
+      <c r="I15" s="143" t="n"/>
+      <c r="J15" s="143" t="n"/>
+      <c r="K15" s="143" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="107">
+      <c r="A16" s="111" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B16" s="111" t="inlineStr">
+        <is>
+          <t>المحطة</t>
+        </is>
+      </c>
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>المنطقة</t>
+        </is>
+      </c>
+      <c r="D16" s="111" t="inlineStr">
+        <is>
+          <t>بنزين سنوي</t>
+        </is>
+      </c>
+      <c r="E16" s="111" t="inlineStr">
+        <is>
+          <t>زيارة/يوم</t>
+        </is>
+      </c>
+      <c r="F16" s="111" t="inlineStr">
+        <is>
+          <t>عمال</t>
+        </is>
+      </c>
+      <c r="G16" s="111" t="inlineStr">
+        <is>
+          <t>الشكاوى</t>
+        </is>
+      </c>
+      <c r="H16" s="111" t="inlineStr">
+        <is>
+          <t>المستهدف</t>
+        </is>
+      </c>
+      <c r="I16" s="111" t="inlineStr">
+        <is>
+          <t>الزيادة</t>
+        </is>
+      </c>
+      <c r="J16" s="111" t="inlineStr">
+        <is>
+          <t>الحافز (ريال/سنة)</t>
+        </is>
+      </c>
+      <c r="K16" s="111" t="inlineStr">
+        <is>
+          <t>لكل عامل شهرياً</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="107">
+      <c r="A17" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="148" t="inlineStr">
+        <is>
+          <t>العوالي</t>
+        </is>
+      </c>
+      <c r="C17" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D17" s="149" t="n">
+        <v>35464924</v>
+      </c>
+      <c r="E17" s="149" t="n">
+        <v>3561</v>
+      </c>
+      <c r="F17" s="112" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" s="112" t="n"/>
+      <c r="H17" s="149">
+        <f>IFERROR(D17*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="150">
+        <f>IFERROR(H17-D17,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="149">
+        <f>IFERROR(I17*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="149">
+        <f>IFERROR(J17/F17/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="107">
+      <c r="A18" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="148" t="inlineStr">
+        <is>
+          <t>العمرة الجديدة</t>
+        </is>
+      </c>
+      <c r="C18" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D18" s="149" t="n">
+        <v>34063312</v>
+      </c>
+      <c r="E18" s="149" t="n">
+        <v>4236</v>
+      </c>
+      <c r="F18" s="112" t="n">
+        <v>32</v>
+      </c>
+      <c r="G18" s="151" t="n">
+        <v>58</v>
+      </c>
+      <c r="H18" s="149">
+        <f>IFERROR(D18*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="150">
+        <f>IFERROR(H18-D18,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="149">
+        <f>IFERROR(I18*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="149">
+        <f>IFERROR(J18/F18/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="107">
+      <c r="A19" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="148" t="inlineStr">
+        <is>
+          <t>عاصفة الصحراء</t>
+        </is>
+      </c>
+      <c r="C19" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D19" s="149" t="n">
+        <v>19648510</v>
+      </c>
+      <c r="E19" s="149" t="n">
+        <v>2137</v>
+      </c>
+      <c r="F19" s="112" t="n">
+        <v>19</v>
+      </c>
+      <c r="G19" s="112" t="n"/>
+      <c r="H19" s="149">
+        <f>IFERROR(D19*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="150">
+        <f>IFERROR(H19-D19,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="149">
+        <f>IFERROR(I19*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="149">
+        <f>IFERROR(J19/F19/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="107">
+      <c r="A20" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="148" t="inlineStr">
+        <is>
+          <t>العزيزية</t>
+        </is>
+      </c>
+      <c r="C20" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D20" s="149" t="n">
+        <v>16732843</v>
+      </c>
+      <c r="E20" s="149" t="n">
+        <v>2359</v>
+      </c>
+      <c r="F20" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" s="151" t="n">
+        <v>28</v>
+      </c>
+      <c r="H20" s="149">
+        <f>IFERROR(D20*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="150">
+        <f>IFERROR(H20-D20,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="149">
+        <f>IFERROR(I20*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="149">
+        <f>IFERROR(J20/F20/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="107">
+      <c r="A21" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="148" t="inlineStr">
+        <is>
+          <t>الشيباني</t>
+        </is>
+      </c>
+      <c r="C21" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D21" s="149" t="n">
+        <v>16309064</v>
+      </c>
+      <c r="E21" s="149" t="n">
+        <v>1726</v>
+      </c>
+      <c r="F21" s="112" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" s="112" t="n"/>
+      <c r="H21" s="149">
+        <f>IFERROR(D21*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="150">
+        <f>IFERROR(H21-D21,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="149">
+        <f>IFERROR(I21*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="149">
+        <f>IFERROR(J21/F21/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="107">
+      <c r="A22" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="148" t="inlineStr">
+        <is>
+          <t>النسيم</t>
+        </is>
+      </c>
+      <c r="C22" s="112" t="inlineStr">
+        <is>
+          <t>جدة</t>
+        </is>
+      </c>
+      <c r="D22" s="149" t="n">
+        <v>16280701</v>
+      </c>
+      <c r="E22" s="149" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F22" s="112" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="112" t="n"/>
+      <c r="H22" s="149">
+        <f>IFERROR(D22*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="150">
+        <f>IFERROR(H22-D22,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="149">
+        <f>IFERROR(I22*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="149">
+        <f>IFERROR(J22/F22/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="107">
+      <c r="A23" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="148" t="inlineStr">
+        <is>
+          <t>أحلى مساء</t>
+        </is>
+      </c>
+      <c r="C23" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D23" s="149" t="n">
+        <v>14309768</v>
+      </c>
+      <c r="E23" s="149" t="n">
+        <v>1414</v>
+      </c>
+      <c r="F23" s="112" t="n">
+        <v>13</v>
+      </c>
+      <c r="G23" s="112" t="n"/>
+      <c r="H23" s="149">
+        <f>IFERROR(D23*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="150">
+        <f>IFERROR(H23-D23,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="149">
+        <f>IFERROR(I23*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="149">
+        <f>IFERROR(J23/F23/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="107">
+      <c r="A24" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="148" t="inlineStr">
+        <is>
+          <t>الحليس - طريق الجنوب</t>
+        </is>
+      </c>
+      <c r="C24" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D24" s="149" t="n">
+        <v>13354076</v>
+      </c>
+      <c r="E24" s="149" t="n">
+        <v>1694</v>
+      </c>
+      <c r="F24" s="112" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" s="112" t="n"/>
+      <c r="H24" s="149">
+        <f>IFERROR(D24*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="150">
+        <f>IFERROR(H24-D24,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="149">
+        <f>IFERROR(I24*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="149">
+        <f>IFERROR(J24/F24/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="107">
+      <c r="A25" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="B25" s="148" t="inlineStr">
+        <is>
+          <t>جنوب الطائف</t>
+        </is>
+      </c>
+      <c r="C25" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D25" s="149" t="n">
+        <v>13311973</v>
+      </c>
+      <c r="E25" s="149" t="n">
+        <v>1483</v>
+      </c>
+      <c r="F25" s="112" t="n">
+        <v>13</v>
+      </c>
+      <c r="G25" s="112" t="n"/>
+      <c r="H25" s="149">
+        <f>IFERROR(D25*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="150">
+        <f>IFERROR(H25-D25,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="149">
+        <f>IFERROR(I25*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="149">
+        <f>IFERROR(J25/F25/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="107">
+      <c r="A26" s="112" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="148" t="inlineStr">
+        <is>
+          <t>جبل النور</t>
+        </is>
+      </c>
+      <c r="C26" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D26" s="149" t="n">
+        <v>13248903</v>
+      </c>
+      <c r="E26" s="149" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F26" s="112" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="112" t="n"/>
+      <c r="H26" s="149">
+        <f>IFERROR(D26*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="150">
+        <f>IFERROR(H26-D26,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="149">
+        <f>IFERROR(I26*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="149">
+        <f>IFERROR(J26/F26/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="107">
+      <c r="A27" s="112" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="148" t="inlineStr">
+        <is>
+          <t>الدائري الشمالي</t>
+        </is>
+      </c>
+      <c r="C27" s="112" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+      <c r="D27" s="149" t="n">
+        <v>13247588</v>
+      </c>
+      <c r="E27" s="149" t="n">
+        <v>1169</v>
+      </c>
+      <c r="F27" s="112" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="112" t="n"/>
+      <c r="H27" s="149">
+        <f>IFERROR(D27*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="150">
+        <f>IFERROR(H27-D27,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="149">
+        <f>IFERROR(I27*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="149">
+        <f>IFERROR(J27/F27/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="107">
+      <c r="A28" s="112" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" s="148" t="inlineStr">
+        <is>
+          <t>القادسية</t>
+        </is>
+      </c>
+      <c r="C28" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D28" s="149" t="n">
+        <v>12654914</v>
+      </c>
+      <c r="E28" s="149" t="n">
+        <v>1702</v>
+      </c>
+      <c r="F28" s="112" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="112" t="n"/>
+      <c r="H28" s="149">
+        <f>IFERROR(D28*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="150">
+        <f>IFERROR(H28-D28,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="149">
+        <f>IFERROR(I28*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="149">
+        <f>IFERROR(J28/F28/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="107">
+      <c r="A29" s="112" t="n">
+        <v>13</v>
+      </c>
+      <c r="B29" s="148" t="inlineStr">
+        <is>
+          <t>الدائري الثالث - الذكرى</t>
+        </is>
+      </c>
+      <c r="C29" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D29" s="149" t="n">
+        <v>11988986</v>
+      </c>
+      <c r="E29" s="149" t="n">
+        <v>1566</v>
+      </c>
+      <c r="F29" s="112" t="n">
+        <v>12</v>
+      </c>
+      <c r="G29" s="112" t="n"/>
+      <c r="H29" s="149">
+        <f>IFERROR(D29*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="150">
+        <f>IFERROR(H29-D29,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="149">
+        <f>IFERROR(I29*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="149">
+        <f>IFERROR(J29/F29/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="107">
+      <c r="A30" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="B30" s="148" t="inlineStr">
+        <is>
+          <t>الصفا - أحد المسارحة</t>
+        </is>
+      </c>
+      <c r="C30" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D30" s="149" t="n">
+        <v>11882308</v>
+      </c>
+      <c r="E30" s="149" t="n">
+        <v>1807</v>
+      </c>
+      <c r="F30" s="112" t="n"/>
+      <c r="G30" s="112" t="n"/>
+      <c r="H30" s="149">
+        <f>IFERROR(D30*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="150">
+        <f>IFERROR(H30-D30,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="149">
+        <f>IFERROR(I30*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="149">
+        <f>IFERROR(J30/F30/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="107">
+      <c r="A31" s="112" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="148" t="inlineStr">
+        <is>
+          <t>الحسينية</t>
+        </is>
+      </c>
+      <c r="C31" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D31" s="149" t="n">
+        <v>11625662</v>
+      </c>
+      <c r="E31" s="149" t="n">
+        <v>1643</v>
+      </c>
+      <c r="F31" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="112" t="n"/>
+      <c r="H31" s="149">
+        <f>IFERROR(D31*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="150">
+        <f>IFERROR(H31-D31,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="149">
+        <f>IFERROR(I31*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="149">
+        <f>IFERROR(J31/F31/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="107">
+      <c r="A32" s="112" t="n">
+        <v>16</v>
+      </c>
+      <c r="B32" s="148" t="inlineStr">
+        <is>
+          <t>الرصيفة</t>
+        </is>
+      </c>
+      <c r="C32" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D32" s="149" t="n">
+        <v>11101203</v>
+      </c>
+      <c r="E32" s="149" t="n">
+        <v>1573</v>
+      </c>
+      <c r="F32" s="112" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" s="112" t="n"/>
+      <c r="H32" s="149">
+        <f>IFERROR(D32*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="150">
+        <f>IFERROR(H32-D32,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="149">
+        <f>IFERROR(I32*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="149">
+        <f>IFERROR(J32/F32/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="107">
+      <c r="A33" s="112" t="n">
+        <v>17</v>
+      </c>
+      <c r="B33" s="148" t="inlineStr">
+        <is>
+          <t>طريق الليث - الفضيلة</t>
+        </is>
+      </c>
+      <c r="C33" s="112" t="inlineStr">
+        <is>
+          <t>جدة</t>
+        </is>
+      </c>
+      <c r="D33" s="149" t="n">
+        <v>10864480</v>
+      </c>
+      <c r="E33" s="149" t="n">
+        <v>1892</v>
+      </c>
+      <c r="F33" s="112" t="n"/>
+      <c r="G33" s="112" t="n"/>
+      <c r="H33" s="149">
+        <f>IFERROR(D33*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="150">
+        <f>IFERROR(H33-D33,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="149">
+        <f>IFERROR(I33*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K33" s="149">
+        <f>IFERROR(J33/F33/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="107">
+      <c r="A34" s="112" t="n">
+        <v>18</v>
+      </c>
+      <c r="B34" s="148" t="inlineStr">
+        <is>
+          <t>عرفات الشوقية</t>
+        </is>
+      </c>
+      <c r="C34" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D34" s="149" t="n">
+        <v>9931491</v>
+      </c>
+      <c r="E34" s="149" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F34" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" s="149">
+        <f>IFERROR(D34*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="150">
+        <f>IFERROR(H34-D34,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="149">
+        <f>IFERROR(I34*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="149">
+        <f>IFERROR(J34/F34/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="107">
+      <c r="A35" s="112" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35" s="148" t="inlineStr">
+        <is>
+          <t>ممشى الشوقية</t>
+        </is>
+      </c>
+      <c r="C35" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D35" s="149" t="n">
+        <v>9558604</v>
+      </c>
+      <c r="E35" s="149" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F35" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" s="112" t="n"/>
+      <c r="H35" s="149">
+        <f>IFERROR(D35*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="150">
+        <f>IFERROR(H35-D35,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="149">
+        <f>IFERROR(I35*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="149">
+        <f>IFERROR(J35/F35/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="107">
+      <c r="A36" s="112" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" s="148" t="inlineStr">
+        <is>
+          <t>السواط - شهار</t>
+        </is>
+      </c>
+      <c r="C36" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D36" s="149" t="n">
+        <v>9064151</v>
+      </c>
+      <c r="E36" s="149" t="n">
+        <v>1144</v>
+      </c>
+      <c r="F36" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="G36" s="112" t="n"/>
+      <c r="H36" s="149">
+        <f>IFERROR(D36*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="150">
+        <f>IFERROR(H36-D36,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="149">
+        <f>IFERROR(I36*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="149">
+        <f>IFERROR(J36/F36/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="107">
+      <c r="A37" s="112" t="n">
+        <v>21</v>
+      </c>
+      <c r="B37" s="148" t="inlineStr">
+        <is>
+          <t>أبو وافي العمرة</t>
+        </is>
+      </c>
+      <c r="C37" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D37" s="149" t="n">
+        <v>8548346</v>
+      </c>
+      <c r="E37" s="149" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F37" s="112" t="n">
+        <v>13</v>
+      </c>
+      <c r="G37" s="112" t="n"/>
+      <c r="H37" s="149">
+        <f>IFERROR(D37*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="150">
+        <f>IFERROR(H37-D37,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="149">
+        <f>IFERROR(I37*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="149">
+        <f>IFERROR(J37/F37/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="107">
+      <c r="A38" s="112" t="n">
+        <v>22</v>
+      </c>
+      <c r="B38" s="148" t="inlineStr">
+        <is>
+          <t>الفلاح - فلسطين</t>
+        </is>
+      </c>
+      <c r="C38" s="112" t="inlineStr">
+        <is>
+          <t>جدة</t>
+        </is>
+      </c>
+      <c r="D38" s="149" t="n">
+        <v>7867941</v>
+      </c>
+      <c r="E38" s="149" t="n">
+        <v>1328</v>
+      </c>
+      <c r="F38" s="112" t="n"/>
+      <c r="G38" s="112" t="n"/>
+      <c r="H38" s="149">
+        <f>IFERROR(D38*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="150">
+        <f>IFERROR(H38-D38,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="149">
+        <f>IFERROR(I38*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="149">
+        <f>IFERROR(J38/F38/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="107">
+      <c r="A39" s="112" t="n">
+        <v>23</v>
+      </c>
+      <c r="B39" s="148" t="inlineStr">
+        <is>
+          <t>كورنيش جيزان</t>
+        </is>
+      </c>
+      <c r="C39" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D39" s="149" t="n">
+        <v>7444371</v>
+      </c>
+      <c r="E39" s="149" t="n">
+        <v>922</v>
+      </c>
+      <c r="F39" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="112" t="n"/>
+      <c r="H39" s="149">
+        <f>IFERROR(D39*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="150">
+        <f>IFERROR(H39-D39,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="149">
+        <f>IFERROR(I39*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="149">
+        <f>IFERROR(J39/F39/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="107">
+      <c r="A40" s="112" t="n">
+        <v>24</v>
+      </c>
+      <c r="B40" s="148" t="inlineStr">
+        <is>
+          <t>الجعرانة</t>
+        </is>
+      </c>
+      <c r="C40" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D40" s="149" t="n">
+        <v>7193020</v>
+      </c>
+      <c r="E40" s="149" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F40" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" s="112" t="n"/>
+      <c r="H40" s="149">
+        <f>IFERROR(D40*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="150">
+        <f>IFERROR(H40-D40,"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="149">
+        <f>IFERROR(I40*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K40" s="149">
+        <f>IFERROR(J40/F40/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="107">
+      <c r="A41" s="112" t="n">
+        <v>25</v>
+      </c>
+      <c r="B41" s="148" t="inlineStr">
+        <is>
+          <t>الحمرا - طريق الملك عبدالله</t>
+        </is>
+      </c>
+      <c r="C41" s="112" t="inlineStr">
+        <is>
+          <t>الخرج</t>
+        </is>
+      </c>
+      <c r="D41" s="149" t="n">
+        <v>7191456</v>
+      </c>
+      <c r="E41" s="149" t="n">
+        <v>864</v>
+      </c>
+      <c r="F41" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" s="112" t="n"/>
+      <c r="H41" s="149">
+        <f>IFERROR(D41*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="150">
+        <f>IFERROR(H41-D41,"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="149">
+        <f>IFERROR(I41*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K41" s="149">
+        <f>IFERROR(J41/F41/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="107">
+      <c r="A42" s="112" t="n">
+        <v>26</v>
+      </c>
+      <c r="B42" s="148" t="inlineStr">
+        <is>
+          <t>المعيصم</t>
+        </is>
+      </c>
+      <c r="C42" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D42" s="149" t="n">
+        <v>6999984</v>
+      </c>
+      <c r="E42" s="149" t="n">
+        <v>913</v>
+      </c>
+      <c r="F42" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" s="149">
+        <f>IFERROR(D42*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="150">
+        <f>IFERROR(H42-D42,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="149">
+        <f>IFERROR(I42*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="149">
+        <f>IFERROR(J42/F42/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="107">
+      <c r="A43" s="112" t="n">
+        <v>27</v>
+      </c>
+      <c r="B43" s="148" t="inlineStr">
+        <is>
+          <t>مدخل محايل</t>
+        </is>
+      </c>
+      <c r="C43" s="112" t="inlineStr">
+        <is>
+          <t>عسير</t>
+        </is>
+      </c>
+      <c r="D43" s="149" t="n">
+        <v>6980426</v>
+      </c>
+      <c r="E43" s="149" t="n">
+        <v>952</v>
+      </c>
+      <c r="F43" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" s="112" t="n"/>
+      <c r="H43" s="149">
+        <f>IFERROR(D43*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="150">
+        <f>IFERROR(H43-D43,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="149">
+        <f>IFERROR(I43*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="149">
+        <f>IFERROR(J43/F43/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="107">
+      <c r="A44" s="112" t="n">
+        <v>28</v>
+      </c>
+      <c r="B44" s="148" t="inlineStr">
+        <is>
+          <t>الرصيفة المسار</t>
+        </is>
+      </c>
+      <c r="C44" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D44" s="149" t="n">
+        <v>6955614</v>
+      </c>
+      <c r="E44" s="149" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F44" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" s="112" t="n"/>
+      <c r="H44" s="149">
+        <f>IFERROR(D44*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="150">
+        <f>IFERROR(H44-D44,"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="149">
+        <f>IFERROR(I44*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="149">
+        <f>IFERROR(J44/F44/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="107">
+      <c r="A45" s="112" t="n">
+        <v>29</v>
+      </c>
+      <c r="B45" s="148" t="inlineStr">
+        <is>
+          <t>الجمعية الوسام</t>
+        </is>
+      </c>
+      <c r="C45" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D45" s="149" t="n">
+        <v>6835043</v>
+      </c>
+      <c r="E45" s="149" t="n">
+        <v>823</v>
+      </c>
+      <c r="F45" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" s="112" t="n"/>
+      <c r="H45" s="149">
+        <f>IFERROR(D45*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="150">
+        <f>IFERROR(H45-D45,"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="149">
+        <f>IFERROR(I45*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K45" s="149">
+        <f>IFERROR(J45/F45/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="107">
+      <c r="A46" s="112" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" s="148" t="inlineStr">
+        <is>
+          <t>الجموم - الكنيدري</t>
+        </is>
+      </c>
+      <c r="C46" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D46" s="149" t="n">
+        <v>6267957</v>
+      </c>
+      <c r="E46" s="149" t="n">
+        <v>931</v>
+      </c>
+      <c r="F46" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="112" t="n"/>
+      <c r="H46" s="149">
+        <f>IFERROR(D46*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="150">
+        <f>IFERROR(H46-D46,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="149">
+        <f>IFERROR(I46*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="149">
+        <f>IFERROR(J46/F46/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="107">
+      <c r="A47" s="112" t="n">
+        <v>31</v>
+      </c>
+      <c r="B47" s="148" t="inlineStr">
+        <is>
+          <t>بطحاء قريش 1</t>
+        </is>
+      </c>
+      <c r="C47" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D47" s="149" t="n">
+        <v>6241831</v>
+      </c>
+      <c r="E47" s="149" t="n">
+        <v>816</v>
+      </c>
+      <c r="F47" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" s="112" t="n"/>
+      <c r="H47" s="149">
+        <f>IFERROR(D47*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="150">
+        <f>IFERROR(H47-D47,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="149">
+        <f>IFERROR(I47*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="149">
+        <f>IFERROR(J47/F47/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1" s="107">
+      <c r="A48" s="112" t="n">
+        <v>32</v>
+      </c>
+      <c r="B48" s="148" t="inlineStr">
+        <is>
+          <t>طريق السيل</t>
+        </is>
+      </c>
+      <c r="C48" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D48" s="149" t="n">
+        <v>6066855</v>
+      </c>
+      <c r="E48" s="149" t="n">
+        <v>680</v>
+      </c>
+      <c r="F48" s="112" t="n">
+        <v>11</v>
+      </c>
+      <c r="G48" s="112" t="n"/>
+      <c r="H48" s="149">
+        <f>IFERROR(D48*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="150">
+        <f>IFERROR(H48-D48,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="149">
+        <f>IFERROR(I48*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K48" s="149">
+        <f>IFERROR(J48/F48/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" s="107">
+      <c r="A49" s="112" t="n">
+        <v>33</v>
+      </c>
+      <c r="B49" s="148" t="inlineStr">
+        <is>
+          <t>جنوب صبيا</t>
+        </is>
+      </c>
+      <c r="C49" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D49" s="149" t="n">
+        <v>6046920</v>
+      </c>
+      <c r="E49" s="149" t="n">
+        <v>1227</v>
+      </c>
+      <c r="F49" s="112" t="n"/>
+      <c r="G49" s="112" t="n"/>
+      <c r="H49" s="149">
+        <f>IFERROR(D49*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="150">
+        <f>IFERROR(H49-D49,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="149">
+        <f>IFERROR(I49*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="149">
+        <f>IFERROR(J49/F49/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="107">
+      <c r="A50" s="112" t="n">
+        <v>34</v>
+      </c>
+      <c r="B50" s="148" t="inlineStr">
+        <is>
+          <t>بن درويش</t>
+        </is>
+      </c>
+      <c r="C50" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D50" s="149" t="n">
+        <v>5899223</v>
+      </c>
+      <c r="E50" s="149" t="n">
+        <v>807</v>
+      </c>
+      <c r="F50" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" s="112" t="n"/>
+      <c r="H50" s="149">
+        <f>IFERROR(D50*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="150">
+        <f>IFERROR(H50-D50,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="149">
+        <f>IFERROR(I50*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="149">
+        <f>IFERROR(J50/F50/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="107">
+      <c r="A51" s="112" t="n">
+        <v>35</v>
+      </c>
+      <c r="B51" s="148" t="inlineStr">
+        <is>
+          <t>الأجاويد</t>
+        </is>
+      </c>
+      <c r="C51" s="112" t="inlineStr">
+        <is>
+          <t>جدة</t>
+        </is>
+      </c>
+      <c r="D51" s="149" t="n">
+        <v>5722940</v>
+      </c>
+      <c r="E51" s="149" t="n">
+        <v>938</v>
+      </c>
+      <c r="F51" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" s="112" t="n"/>
+      <c r="H51" s="149">
+        <f>IFERROR(D51*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="150">
+        <f>IFERROR(H51-D51,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="149">
+        <f>IFERROR(I51*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K51" s="149">
+        <f>IFERROR(J51/F51/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1" s="107">
+      <c r="A52" s="112" t="n">
+        <v>36</v>
+      </c>
+      <c r="B52" s="148" t="inlineStr">
+        <is>
+          <t>القسوم - أحد المسارحة</t>
+        </is>
+      </c>
+      <c r="C52" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D52" s="149" t="n">
+        <v>5647921</v>
+      </c>
+      <c r="E52" s="149" t="n">
+        <v>800</v>
+      </c>
+      <c r="F52" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" s="112" t="n"/>
+      <c r="H52" s="149">
+        <f>IFERROR(D52*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="150">
+        <f>IFERROR(H52-D52,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="149">
+        <f>IFERROR(I52*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K52" s="149">
+        <f>IFERROR(J52/F52/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" s="107">
+      <c r="A53" s="112" t="n">
+        <v>37</v>
+      </c>
+      <c r="B53" s="148" t="inlineStr">
+        <is>
+          <t>الكر النازل</t>
+        </is>
+      </c>
+      <c r="C53" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D53" s="149" t="n">
+        <v>5545862</v>
+      </c>
+      <c r="E53" s="149" t="n">
+        <v>537</v>
+      </c>
+      <c r="F53" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" s="112" t="n"/>
+      <c r="H53" s="149">
+        <f>IFERROR(D53*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="150">
+        <f>IFERROR(H53-D53,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="149">
+        <f>IFERROR(I53*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K53" s="149">
+        <f>IFERROR(J53/F53/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="107">
+      <c r="A54" s="112" t="n">
+        <v>38</v>
+      </c>
+      <c r="B54" s="148" t="inlineStr">
+        <is>
+          <t>الملك خالد</t>
+        </is>
+      </c>
+      <c r="C54" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D54" s="149" t="n">
+        <v>5284855</v>
+      </c>
+      <c r="E54" s="149" t="n">
+        <v>685</v>
+      </c>
+      <c r="F54" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" s="112" t="n"/>
+      <c r="H54" s="149">
+        <f>IFERROR(D54*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="150">
+        <f>IFERROR(H54-D54,"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="149">
+        <f>IFERROR(I54*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K54" s="149">
+        <f>IFERROR(J54/F54/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="107">
+      <c r="A55" s="112" t="n">
+        <v>39</v>
+      </c>
+      <c r="B55" s="148" t="inlineStr">
+        <is>
+          <t>كورنيش الخبر</t>
+        </is>
+      </c>
+      <c r="C55" s="112" t="inlineStr">
+        <is>
+          <t>الشرقية</t>
+        </is>
+      </c>
+      <c r="D55" s="149" t="n">
+        <v>5197774</v>
+      </c>
+      <c r="E55" s="149" t="n">
+        <v>591</v>
+      </c>
+      <c r="F55" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G55" s="112" t="n"/>
+      <c r="H55" s="149">
+        <f>IFERROR(D55*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I55" s="150">
+        <f>IFERROR(H55-D55,"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="149">
+        <f>IFERROR(I55*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K55" s="149">
+        <f>IFERROR(J55/F55/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="107">
+      <c r="A56" s="112" t="n">
+        <v>40</v>
+      </c>
+      <c r="B56" s="148" t="inlineStr">
+        <is>
+          <t>خبت نخلان</t>
+        </is>
+      </c>
+      <c r="C56" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D56" s="149" t="n">
+        <v>4362115</v>
+      </c>
+      <c r="E56" s="149" t="n">
+        <v>650</v>
+      </c>
+      <c r="F56" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" s="112" t="n"/>
+      <c r="H56" s="149">
+        <f>IFERROR(D56*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I56" s="150">
+        <f>IFERROR(H56-D56,"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="149">
+        <f>IFERROR(I56*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K56" s="149">
+        <f>IFERROR(J56/F56/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1" s="107">
+      <c r="A57" s="112" t="n">
+        <v>41</v>
+      </c>
+      <c r="B57" s="148" t="inlineStr">
+        <is>
+          <t>غرناطة - طريق الملك عبدالله</t>
+        </is>
+      </c>
+      <c r="C57" s="112" t="inlineStr">
+        <is>
+          <t>الخرج</t>
+        </is>
+      </c>
+      <c r="D57" s="149" t="n">
+        <v>4341977</v>
+      </c>
+      <c r="E57" s="149" t="n">
+        <v>469</v>
+      </c>
+      <c r="F57" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" s="112" t="n"/>
+      <c r="H57" s="149">
+        <f>IFERROR(D57*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I57" s="150">
+        <f>IFERROR(H57-D57,"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="149">
+        <f>IFERROR(I57*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K57" s="149">
+        <f>IFERROR(J57/F57/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1" s="107">
+      <c r="A58" s="112" t="n">
+        <v>42</v>
+      </c>
+      <c r="B58" s="148" t="inlineStr">
+        <is>
+          <t>طريق صبيا</t>
+        </is>
+      </c>
+      <c r="C58" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D58" s="149" t="n">
+        <v>4191108</v>
+      </c>
+      <c r="E58" s="149" t="n">
+        <v>538</v>
+      </c>
+      <c r="F58" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" s="112" t="n"/>
+      <c r="H58" s="149">
+        <f>IFERROR(D58*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I58" s="150">
+        <f>IFERROR(H58-D58,"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="149">
+        <f>IFERROR(I58*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K58" s="149">
+        <f>IFERROR(J58/F58/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1" s="107">
+      <c r="A59" s="112" t="n">
+        <v>43</v>
+      </c>
+      <c r="B59" s="148" t="inlineStr">
+        <is>
+          <t>بطحاء قريش 2</t>
+        </is>
+      </c>
+      <c r="C59" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D59" s="149" t="n">
+        <v>4156161</v>
+      </c>
+      <c r="E59" s="149" t="n">
+        <v>586</v>
+      </c>
+      <c r="F59" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="112" t="n"/>
+      <c r="H59" s="149">
+        <f>IFERROR(D59*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I59" s="150">
+        <f>IFERROR(H59-D59,"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="149">
+        <f>IFERROR(I59*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K59" s="149">
+        <f>IFERROR(J59/F59/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1" s="107">
+      <c r="A60" s="112" t="n">
+        <v>44</v>
+      </c>
+      <c r="B60" s="148" t="inlineStr">
+        <is>
+          <t>الشرايع</t>
+        </is>
+      </c>
+      <c r="C60" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D60" s="149" t="n">
+        <v>3857645</v>
+      </c>
+      <c r="E60" s="149" t="n">
+        <v>456</v>
+      </c>
+      <c r="F60" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" s="149">
+        <f>IFERROR(D60*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I60" s="150">
+        <f>IFERROR(H60-D60,"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="149">
+        <f>IFERROR(I60*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K60" s="149">
+        <f>IFERROR(J60/F60/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1" s="107">
+      <c r="A61" s="112" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" s="148" t="inlineStr">
+        <is>
+          <t>خليص</t>
+        </is>
+      </c>
+      <c r="C61" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D61" s="149" t="n">
+        <v>3791200</v>
+      </c>
+      <c r="E61" s="149" t="n">
+        <v>423</v>
+      </c>
+      <c r="F61" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" s="112" t="n"/>
+      <c r="H61" s="149">
+        <f>IFERROR(D61*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I61" s="150">
+        <f>IFERROR(H61-D61,"")</f>
+        <v/>
+      </c>
+      <c r="J61" s="149">
+        <f>IFERROR(I61*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K61" s="149">
+        <f>IFERROR(J61/F61/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1" s="107">
+      <c r="A62" s="112" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" s="148" t="inlineStr">
+        <is>
+          <t>جبل ثور - جوهرة النسيم</t>
+        </is>
+      </c>
+      <c r="C62" s="112" t="inlineStr">
+        <is>
+          <t>مكة</t>
+        </is>
+      </c>
+      <c r="D62" s="149" t="n">
+        <v>3708152</v>
+      </c>
+      <c r="E62" s="149" t="n">
+        <v>451</v>
+      </c>
+      <c r="F62" s="112" t="n"/>
+      <c r="G62" s="112" t="n"/>
+      <c r="H62" s="149">
+        <f>IFERROR(D62*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I62" s="150">
+        <f>IFERROR(H62-D62,"")</f>
+        <v/>
+      </c>
+      <c r="J62" s="149">
+        <f>IFERROR(I62*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K62" s="149">
+        <f>IFERROR(J62/F62/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1" s="107">
+      <c r="A63" s="112" t="n">
+        <v>47</v>
+      </c>
+      <c r="B63" s="148" t="inlineStr">
+        <is>
+          <t>الدائري الشرقي</t>
+        </is>
+      </c>
+      <c r="C63" s="112" t="inlineStr">
+        <is>
+          <t>القصيم</t>
+        </is>
+      </c>
+      <c r="D63" s="149" t="n">
+        <v>3599745</v>
+      </c>
+      <c r="E63" s="149" t="n">
+        <v>441</v>
+      </c>
+      <c r="F63" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" s="112" t="n"/>
+      <c r="H63" s="149">
+        <f>IFERROR(D63*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I63" s="150">
+        <f>IFERROR(H63-D63,"")</f>
+        <v/>
+      </c>
+      <c r="J63" s="149">
+        <f>IFERROR(I63*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K63" s="149">
+        <f>IFERROR(J63/F63/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1" s="107">
+      <c r="A64" s="112" t="n">
+        <v>48</v>
+      </c>
+      <c r="B64" s="148" t="inlineStr">
+        <is>
+          <t>الناصفة</t>
+        </is>
+      </c>
+      <c r="C64" s="112" t="inlineStr">
+        <is>
+          <t>الخرج</t>
+        </is>
+      </c>
+      <c r="D64" s="149" t="n">
+        <v>3433425</v>
+      </c>
+      <c r="E64" s="149" t="n">
+        <v>402</v>
+      </c>
+      <c r="F64" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" s="112" t="n"/>
+      <c r="H64" s="149">
+        <f>IFERROR(D64*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I64" s="150">
+        <f>IFERROR(H64-D64,"")</f>
+        <v/>
+      </c>
+      <c r="J64" s="149">
+        <f>IFERROR(I64*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K64" s="149">
+        <f>IFERROR(J64/F64/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1" s="107">
+      <c r="A65" s="112" t="n">
+        <v>49</v>
+      </c>
+      <c r="B65" s="148" t="inlineStr">
+        <is>
+          <t>البيعة</t>
+        </is>
+      </c>
+      <c r="C65" s="112" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="D65" s="149" t="n">
+        <v>3315559</v>
+      </c>
+      <c r="E65" s="149" t="n">
+        <v>455</v>
+      </c>
+      <c r="F65" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" s="112" t="n"/>
+      <c r="H65" s="149">
+        <f>IFERROR(D65*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="150">
+        <f>IFERROR(H65-D65,"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="149">
+        <f>IFERROR(I65*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K65" s="149">
+        <f>IFERROR(J65/F65/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1" s="107">
+      <c r="A66" s="112" t="n">
+        <v>50</v>
+      </c>
+      <c r="B66" s="148" t="inlineStr">
+        <is>
+          <t>العريفي</t>
+        </is>
+      </c>
+      <c r="C66" s="112" t="inlineStr">
+        <is>
+          <t>حائل</t>
+        </is>
+      </c>
+      <c r="D66" s="149" t="n">
+        <v>2663618</v>
+      </c>
+      <c r="E66" s="149" t="n">
+        <v>327</v>
+      </c>
+      <c r="F66" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G66" s="112" t="n"/>
+      <c r="H66" s="149">
+        <f>IFERROR(D66*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="150">
+        <f>IFERROR(H66-D66,"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="149">
+        <f>IFERROR(I66*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K66" s="149">
+        <f>IFERROR(J66/F66/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1" s="107">
+      <c r="A67" s="112" t="n">
+        <v>51</v>
+      </c>
+      <c r="B67" s="148" t="inlineStr">
+        <is>
+          <t>الكوثر</t>
+        </is>
+      </c>
+      <c r="C67" s="112" t="inlineStr">
+        <is>
+          <t>جدة</t>
+        </is>
+      </c>
+      <c r="D67" s="149" t="n">
+        <v>2286567</v>
+      </c>
+      <c r="E67" s="149" t="n">
+        <v>333</v>
+      </c>
+      <c r="F67" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" s="112" t="n"/>
+      <c r="H67" s="149">
+        <f>IFERROR(D67*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="150">
+        <f>IFERROR(H67-D67,"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="149">
+        <f>IFERROR(I67*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K67" s="149">
+        <f>IFERROR(J67/F67/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1" s="107">
+      <c r="A68" s="112" t="n">
+        <v>52</v>
+      </c>
+      <c r="B68" s="148" t="inlineStr">
+        <is>
+          <t>الروابي - المودة</t>
+        </is>
+      </c>
+      <c r="C68" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D68" s="149" t="n">
+        <v>2086987</v>
+      </c>
+      <c r="E68" s="149" t="n">
+        <v>281</v>
+      </c>
+      <c r="F68" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" s="112" t="n"/>
+      <c r="H68" s="149">
+        <f>IFERROR(D68*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="150">
+        <f>IFERROR(H68-D68,"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="149">
+        <f>IFERROR(I68*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K68" s="149">
+        <f>IFERROR(J68/F68/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1" s="107">
+      <c r="A69" s="112" t="n">
+        <v>53</v>
+      </c>
+      <c r="B69" s="148" t="inlineStr">
+        <is>
+          <t>صناعية صامطة</t>
+        </is>
+      </c>
+      <c r="C69" s="112" t="inlineStr">
+        <is>
+          <t>جازان</t>
+        </is>
+      </c>
+      <c r="D69" s="149" t="n">
+        <v>1960098</v>
+      </c>
+      <c r="E69" s="149" t="n">
+        <v>408</v>
+      </c>
+      <c r="F69" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" s="112" t="n"/>
+      <c r="H69" s="149">
+        <f>IFERROR(D69*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="150">
+        <f>IFERROR(H69-D69,"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="149">
+        <f>IFERROR(I69*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K69" s="149">
+        <f>IFERROR(J69/F69/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1" s="107">
+      <c r="A70" s="112" t="n">
+        <v>54</v>
+      </c>
+      <c r="B70" s="148" t="inlineStr">
+        <is>
+          <t>طريق السلام</t>
+        </is>
+      </c>
+      <c r="C70" s="112" t="inlineStr">
+        <is>
+          <t>المدينة المنورة</t>
+        </is>
+      </c>
+      <c r="D70" s="149" t="n">
+        <v>1451309</v>
+      </c>
+      <c r="E70" s="149" t="n">
+        <v>196</v>
+      </c>
+      <c r="F70" s="112" t="n"/>
+      <c r="G70" s="112" t="n"/>
+      <c r="H70" s="149">
+        <f>IFERROR(D70*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="150">
+        <f>IFERROR(H70-D70,"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="149">
+        <f>IFERROR(I70*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K70" s="149">
+        <f>IFERROR(J70/F70/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1" s="107">
+      <c r="A71" s="112" t="n">
+        <v>55</v>
+      </c>
+      <c r="B71" s="148" t="inlineStr">
+        <is>
+          <t>المركب</t>
+        </is>
+      </c>
+      <c r="C71" s="112" t="inlineStr">
+        <is>
+          <t>نجران</t>
+        </is>
+      </c>
+      <c r="D71" s="149" t="n">
+        <v>1099275</v>
+      </c>
+      <c r="E71" s="149" t="n">
+        <v>154</v>
+      </c>
+      <c r="F71" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" s="112" t="n"/>
+      <c r="H71" s="149">
+        <f>IFERROR(D71*(1+$C$13),"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="150">
+        <f>IFERROR(H71-D71,"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="149">
+        <f>IFERROR(I71*$C$11/100*$C$12,"")</f>
+        <v/>
+      </c>
+      <c r="K71" s="149">
+        <f>IFERROR(J71/F71/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="107">
+      <c r="A72" s="152" t="n"/>
+      <c r="B72" s="152" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="C72" s="152" t="n"/>
+      <c r="D72" s="153">
+        <f>SUM(D17:D71)</f>
+        <v/>
+      </c>
+      <c r="E72" s="153">
+        <f>SUM(E17:E71)</f>
+        <v/>
+      </c>
+      <c r="F72" s="153">
+        <f>SUM(F17:F71)</f>
+        <v/>
+      </c>
+      <c r="G72" s="153">
+        <f>SUM(G17:G71)</f>
+        <v/>
+      </c>
+      <c r="H72" s="153">
+        <f>SUM(H17:H71)</f>
+        <v/>
+      </c>
+      <c r="I72" s="153">
+        <f>SUM(I17:I71)</f>
+        <v/>
+      </c>
+      <c r="J72" s="153">
+        <f>SUM(J17:J71)</f>
+        <v/>
+      </c>
+      <c r="K72" s="152" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="109" t="n"/>
+      <c r="B73" s="109" t="n"/>
+      <c r="C73" s="109" t="n"/>
+      <c r="D73" s="109" t="n"/>
+      <c r="E73" s="109" t="n"/>
+      <c r="F73" s="109" t="n"/>
+      <c r="G73" s="109" t="n"/>
+      <c r="H73" s="109" t="n"/>
+      <c r="I73" s="109" t="n"/>
+      <c r="J73" s="109" t="n"/>
+      <c r="K73" s="109" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="107">
+      <c r="A74" s="109" t="n"/>
+      <c r="B74" s="128" t="inlineStr">
+        <is>
+          <t>آلية الحافز</t>
+        </is>
+      </c>
+      <c r="C74" s="109" t="n"/>
+      <c r="D74" s="109" t="n"/>
+      <c r="E74" s="109" t="n"/>
+      <c r="F74" s="109" t="n"/>
+      <c r="G74" s="109" t="n"/>
+      <c r="H74" s="109" t="n"/>
+      <c r="I74" s="109" t="n"/>
+      <c r="J74" s="109" t="n"/>
+      <c r="K74" s="109" t="n"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="107">
+      <c r="A75" s="109" t="n"/>
+      <c r="B75" s="109" t="n"/>
+      <c r="C75" s="129" t="inlineStr">
+        <is>
+          <t>•  الحافز نسبة من هامش اللتر الإضافي — لا مبلغ ثابت</t>
+        </is>
+      </c>
+      <c r="D75" s="109" t="n"/>
+      <c r="E75" s="109" t="n"/>
+      <c r="F75" s="109" t="n"/>
+      <c r="G75" s="109" t="n"/>
+      <c r="H75" s="109" t="n"/>
+      <c r="I75" s="109" t="n"/>
+      <c r="J75" s="109" t="n"/>
+      <c r="K75" s="109" t="n"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" s="107">
+      <c r="A76" s="109" t="n"/>
+      <c r="B76" s="109" t="n"/>
+      <c r="C76" s="129" t="inlineStr">
+        <is>
+          <t>•  فلا يُصرف إلا إذا تحقق النمو، ويتناسب مع حجمه</t>
+        </is>
+      </c>
+      <c r="D76" s="109" t="n"/>
+      <c r="E76" s="109" t="n"/>
+      <c r="F76" s="109" t="n"/>
+      <c r="G76" s="109" t="n"/>
+      <c r="H76" s="109" t="n"/>
+      <c r="I76" s="109" t="n"/>
+      <c r="J76" s="109" t="n"/>
+      <c r="K76" s="109" t="n"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="107">
+      <c r="A77" s="109" t="n"/>
+      <c r="B77" s="109" t="n"/>
+      <c r="C77" s="129" t="inlineStr">
+        <is>
+          <t>•  التوزيع على عمال المحطة يربط الأجر بنتيجة المحطة مباشرة</t>
+        </is>
+      </c>
+      <c r="D77" s="109" t="n"/>
+      <c r="E77" s="109" t="n"/>
+      <c r="F77" s="109" t="n"/>
+      <c r="G77" s="109" t="n"/>
+      <c r="H77" s="109" t="n"/>
+      <c r="I77" s="109" t="n"/>
+      <c r="J77" s="109" t="n"/>
+      <c r="K77" s="109" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="109" t="n"/>
+      <c r="B78" s="109" t="n"/>
+      <c r="C78" s="109" t="n"/>
+      <c r="D78" s="109" t="n"/>
+      <c r="E78" s="109" t="n"/>
+      <c r="F78" s="109" t="n"/>
+      <c r="G78" s="109" t="n"/>
+      <c r="H78" s="109" t="n"/>
+      <c r="I78" s="109" t="n"/>
+      <c r="J78" s="109" t="n"/>
+      <c r="K78" s="109" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="107">
+      <c r="A79" s="109" t="n"/>
+      <c r="B79" s="117" t="inlineStr">
+        <is>
+          <t>شرط نجاحه</t>
+        </is>
+      </c>
+      <c r="C79" s="109" t="n"/>
+      <c r="D79" s="109" t="n"/>
+      <c r="E79" s="109" t="n"/>
+      <c r="F79" s="109" t="n"/>
+      <c r="G79" s="109" t="n"/>
+      <c r="H79" s="109" t="n"/>
+      <c r="I79" s="109" t="n"/>
+      <c r="J79" s="109" t="n"/>
+      <c r="K79" s="109" t="n"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="107">
+      <c r="A80" s="109" t="n"/>
+      <c r="B80" s="109" t="n"/>
+      <c r="C80" s="129" t="inlineStr">
+        <is>
+          <t>•  قياس شهري معلن لكل محطة — العامل يرى موقعه من المستهدف</t>
+        </is>
+      </c>
+      <c r="D80" s="109" t="n"/>
+      <c r="E80" s="109" t="n"/>
+      <c r="F80" s="109" t="n"/>
+      <c r="G80" s="109" t="n"/>
+      <c r="H80" s="109" t="n"/>
+      <c r="I80" s="109" t="n"/>
+      <c r="J80" s="109" t="n"/>
+      <c r="K80" s="109" t="n"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" s="107">
+      <c r="A81" s="109" t="n"/>
+      <c r="B81" s="109" t="n"/>
+      <c r="C81" s="129" t="inlineStr">
+        <is>
+          <t>•  ربطه بمؤشر الخدمة أيضاً: الشكاوى وزمن التعبئة</t>
+        </is>
+      </c>
+      <c r="D81" s="109" t="n"/>
+      <c r="E81" s="109" t="n"/>
+      <c r="F81" s="109" t="n"/>
+      <c r="G81" s="109" t="n"/>
+      <c r="H81" s="109" t="n"/>
+      <c r="I81" s="109" t="n"/>
+      <c r="J81" s="109" t="n"/>
+      <c r="K81" s="109" t="n"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1" s="107">
+      <c r="A82" s="109" t="n"/>
+      <c r="B82" s="109" t="n"/>
+      <c r="C82" s="129" t="inlineStr">
+        <is>
+          <t>•  بلا قياس زمن الخدمة يتحوّل الحافز إلى مكافأة حجم لا مكافأة أداء</t>
+        </is>
+      </c>
+      <c r="D82" s="109" t="n"/>
+      <c r="E82" s="109" t="n"/>
+      <c r="F82" s="109" t="n"/>
+      <c r="G82" s="109" t="n"/>
+      <c r="H82" s="109" t="n"/>
+      <c r="I82" s="109" t="n"/>
+      <c r="J82" s="109" t="n"/>
+      <c r="K82" s="109" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="109" t="n"/>
+      <c r="B83" s="109" t="n"/>
+      <c r="C83" s="109" t="n"/>
+      <c r="D83" s="109" t="n"/>
+      <c r="E83" s="109" t="n"/>
+      <c r="F83" s="109" t="n"/>
+      <c r="G83" s="109" t="n"/>
+      <c r="H83" s="109" t="n"/>
+      <c r="I83" s="109" t="n"/>
+      <c r="J83" s="109" t="n"/>
+      <c r="K83" s="109" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="107">
+      <c r="A84" s="109" t="n"/>
+      <c r="B84" s="117" t="inlineStr">
+        <is>
+          <t>حدّ خفض المصاريف</t>
+        </is>
+      </c>
+      <c r="C84" s="109" t="n"/>
+      <c r="D84" s="109" t="n"/>
+      <c r="E84" s="109" t="n"/>
+      <c r="F84" s="109" t="n"/>
+      <c r="G84" s="109" t="n"/>
+      <c r="H84" s="109" t="n"/>
+      <c r="I84" s="109" t="n"/>
+      <c r="J84" s="109" t="n"/>
+      <c r="K84" s="109" t="n"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="107">
+      <c r="A85" s="109" t="n"/>
+      <c r="B85" s="109" t="n"/>
+      <c r="C85" s="129" t="inlineStr">
+        <is>
+          <t>•  المصاريف النقدية 0.94 هللة لكل لتر — و88% من المصاريف إهلاك</t>
+        </is>
+      </c>
+      <c r="D85" s="109" t="n"/>
+      <c r="E85" s="109" t="n"/>
+      <c r="F85" s="109" t="n"/>
+      <c r="G85" s="109" t="n"/>
+      <c r="H85" s="109" t="n"/>
+      <c r="I85" s="109" t="n"/>
+      <c r="J85" s="109" t="n"/>
+      <c r="K85" s="109" t="n"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="107">
+      <c r="A86" s="109" t="n"/>
+      <c r="B86" s="109" t="n"/>
+      <c r="C86" s="129" t="inlineStr">
+        <is>
+          <t>•  فالخفض يعطي أقل من هللة، بينما النمو 5% يعطي أضعافه</t>
+        </is>
+      </c>
+      <c r="D86" s="109" t="n"/>
+      <c r="E86" s="109" t="n"/>
+      <c r="F86" s="109" t="n"/>
+      <c r="G86" s="109" t="n"/>
+      <c r="H86" s="109" t="n"/>
+      <c r="I86" s="109" t="n"/>
+      <c r="J86" s="109" t="n"/>
+      <c r="K86" s="109" t="n"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="107">
+      <c r="A87" s="109" t="n"/>
+      <c r="B87" s="109" t="n"/>
+      <c r="C87" s="129" t="inlineStr">
+        <is>
+          <t>•  الأولوية للحجم والخدمة لا لبند المصاريف</t>
+        </is>
+      </c>
+      <c r="D87" s="109" t="n"/>
+      <c r="E87" s="109" t="n"/>
+      <c r="F87" s="109" t="n"/>
+      <c r="G87" s="109" t="n"/>
+      <c r="H87" s="109" t="n"/>
+      <c r="I87" s="109" t="n"/>
+      <c r="J87" s="109" t="n"/>
+      <c r="K87" s="109" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="C82:K82"/>
+    <mergeCell ref="C85:K85"/>
+    <mergeCell ref="C81:K81"/>
+    <mergeCell ref="C76:K76"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="C75:K75"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="C80:K80"/>
+    <mergeCell ref="C87:K87"/>
+    <mergeCell ref="C77:K77"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C86:K86"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9864,7 +14782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10787,2959 +15705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:K87"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="4" customWidth="1" style="106" min="1" max="1"/>
-    <col width="24" customWidth="1" style="106" min="2" max="2"/>
-    <col width="13" customWidth="1" style="106" min="3" max="4"/>
-    <col width="12" customWidth="1" style="106" min="5" max="7"/>
-    <col width="13" customWidth="1" style="106" min="8" max="10"/>
-    <col width="34" customWidth="1" style="106" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
-        <is>
-          <t>الوقود — قناة الأفراد</t>
-        </is>
-      </c>
-      <c r="B1" s="109" t="n"/>
-      <c r="C1" s="109" t="n"/>
-      <c r="D1" s="109" t="n"/>
-      <c r="E1" s="109" t="n"/>
-      <c r="F1" s="109" t="n"/>
-      <c r="G1" s="109" t="n"/>
-      <c r="H1" s="109" t="n"/>
-      <c r="I1" s="109" t="n"/>
-      <c r="J1" s="109" t="n"/>
-      <c r="K1" s="109" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
-        <is>
-          <t>المنافس: كل مشغّلي المحطات · السلاح: سرعة الخدمة · الأداة: مستهدف لكل محطة وحافز لكل عامل</t>
-        </is>
-      </c>
-      <c r="B2" s="109" t="n"/>
-      <c r="C2" s="109" t="n"/>
-      <c r="D2" s="109" t="n"/>
-      <c r="E2" s="109" t="n"/>
-      <c r="F2" s="109" t="n"/>
-      <c r="G2" s="109" t="n"/>
-      <c r="H2" s="109" t="n"/>
-      <c r="I2" s="109" t="n"/>
-      <c r="J2" s="109" t="n"/>
-      <c r="K2" s="109" t="n"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" s="107">
-      <c r="A3" s="142" t="inlineStr">
-        <is>
-          <t>محاور الخطة الأربعة</t>
-        </is>
-      </c>
-      <c r="B3" s="143" t="n"/>
-      <c r="C3" s="143" t="n"/>
-      <c r="D3" s="143" t="n"/>
-      <c r="E3" s="143" t="n"/>
-      <c r="F3" s="143" t="n"/>
-      <c r="G3" s="143" t="n"/>
-      <c r="H3" s="143" t="n"/>
-      <c r="I3" s="143" t="n"/>
-      <c r="J3" s="143" t="n"/>
-      <c r="K3" s="143" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="107">
-      <c r="A4" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="113" t="inlineStr">
-        <is>
-          <t>تدريب العمالة</t>
-        </is>
-      </c>
-      <c r="C4" s="114" t="inlineStr">
-        <is>
-          <t>الشكاوى</t>
-        </is>
-      </c>
-      <c r="D4" s="114" t="inlineStr">
-        <is>
-          <t>56% من الشكاوى عن العامل: بطء الخدمة وسلوك</t>
-        </is>
-      </c>
-      <c r="E4" s="114" t="inlineStr">
-        <is>
-          <t>برنامج تدريب على زمن الخدمة والتعامل</t>
-        </is>
-      </c>
-      <c r="F4" s="114" t="n"/>
-      <c r="G4" s="114" t="n"/>
-      <c r="H4" s="114" t="n"/>
-      <c r="I4" s="114" t="n"/>
-      <c r="J4" s="114" t="n"/>
-      <c r="K4" s="114" t="inlineStr">
-        <is>
-          <t>يُقاس بانخفاض الشكاوى وزمن التعبئة</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="107">
-      <c r="A5" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="113" t="inlineStr">
-        <is>
-          <t>فهم مشاكل العملاء</t>
-        </is>
-      </c>
-      <c r="C5" s="114" t="inlineStr">
-        <is>
-          <t>الشكاوى + قوقل ماب</t>
-        </is>
-      </c>
-      <c r="D5" s="114" t="inlineStr">
-        <is>
-          <t>41 من 103 شكوى منشورة على قوقل ماب</t>
-        </is>
-      </c>
-      <c r="E5" s="114" t="inlineStr">
-        <is>
-          <t>تصنيف أسبوعي للشكاوى وإغلاقها بإجراء لا بتنبيه</t>
-        </is>
-      </c>
-      <c r="F5" s="114" t="n"/>
-      <c r="G5" s="114" t="n"/>
-      <c r="H5" s="114" t="n"/>
-      <c r="I5" s="114" t="n"/>
-      <c r="J5" s="114" t="n"/>
-      <c r="K5" s="114" t="inlineStr">
-        <is>
-          <t>من 58 شكوى: 31 انتهت بتنبيه وصفر إجراء</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="107">
-      <c r="A6" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="113" t="inlineStr">
-        <is>
-          <t>مستهدف وحافز</t>
-        </is>
-      </c>
-      <c r="C6" s="114" t="inlineStr">
-        <is>
-          <t>الجدول أدناه</t>
-        </is>
-      </c>
-      <c r="D6" s="114" t="inlineStr">
-        <is>
-          <t>مستهدف لكل محطة وحافز مرتبط به</t>
-        </is>
-      </c>
-      <c r="E6" s="114" t="inlineStr">
-        <is>
-          <t>الحافز نسبة من هامش اللتر الإضافي</t>
-        </is>
-      </c>
-      <c r="F6" s="114" t="n"/>
-      <c r="G6" s="114" t="n"/>
-      <c r="H6" s="114" t="n"/>
-      <c r="I6" s="114" t="n"/>
-      <c r="J6" s="114" t="n"/>
-      <c r="K6" s="114" t="inlineStr">
-        <is>
-          <t>يربط أجر العامل بنتيجة المحطة</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="107">
-      <c r="A7" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="113" t="inlineStr">
-        <is>
-          <t>خفض مصاريف المحطة</t>
-        </is>
-      </c>
-      <c r="C7" s="114" t="inlineStr">
-        <is>
-          <t>قائمة الدخل</t>
-        </is>
-      </c>
-      <c r="D7" s="114" t="inlineStr">
-        <is>
-          <t>المصاريف النقدية 0.94 هللة لكل لتر فقط</t>
-        </is>
-      </c>
-      <c r="E7" s="114" t="inlineStr">
-        <is>
-          <t>المجال ضيق — الأولوية للحجم لا للخفض</t>
-        </is>
-      </c>
-      <c r="F7" s="114" t="n"/>
-      <c r="G7" s="114" t="n"/>
-      <c r="H7" s="114" t="n"/>
-      <c r="I7" s="114" t="n"/>
-      <c r="J7" s="114" t="n"/>
-      <c r="K7" s="114" t="inlineStr">
-        <is>
-          <t>88% من المصاريف إهلاك غير قابل للخفض</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="109" t="n"/>
-      <c r="B8" s="109" t="n"/>
-      <c r="C8" s="109" t="n"/>
-      <c r="D8" s="109" t="n"/>
-      <c r="E8" s="109" t="n"/>
-      <c r="F8" s="109" t="n"/>
-      <c r="G8" s="109" t="n"/>
-      <c r="H8" s="109" t="n"/>
-      <c r="I8" s="109" t="n"/>
-      <c r="J8" s="109" t="n"/>
-      <c r="K8" s="109" t="n"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="107">
-      <c r="A9" s="142" t="inlineStr">
-        <is>
-          <t>مُدخلات النموذج</t>
-        </is>
-      </c>
-      <c r="B9" s="143" t="n"/>
-      <c r="C9" s="143" t="n"/>
-      <c r="D9" s="143" t="n"/>
-      <c r="E9" s="143" t="n"/>
-      <c r="F9" s="143" t="n"/>
-      <c r="G9" s="143" t="n"/>
-      <c r="H9" s="143" t="n"/>
-      <c r="I9" s="143" t="n"/>
-      <c r="J9" s="143" t="n"/>
-      <c r="K9" s="143" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="107">
-      <c r="A10" s="109" t="n"/>
-      <c r="B10" s="144" t="inlineStr">
-        <is>
-          <t>سعر البيع المرجّح (ريال/لتر)</t>
-        </is>
-      </c>
-      <c r="C10" s="145" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D10" s="109" t="n"/>
-      <c r="E10" s="109" t="n"/>
-      <c r="F10" s="109" t="n"/>
-      <c r="G10" s="109" t="n"/>
-      <c r="H10" s="109" t="n"/>
-      <c r="I10" s="109" t="n"/>
-      <c r="J10" s="109" t="n"/>
-      <c r="K10" s="109" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="107">
-      <c r="A11" s="109" t="n"/>
-      <c r="B11" s="144" t="inlineStr">
-        <is>
-          <t>هامش المساهمة لكل لتر (هللة)</t>
-        </is>
-      </c>
-      <c r="C11" s="146" t="n"/>
-      <c r="D11" s="109" t="n"/>
-      <c r="E11" s="109" t="n"/>
-      <c r="F11" s="109" t="n"/>
-      <c r="G11" s="109" t="n"/>
-      <c r="H11" s="109" t="n"/>
-      <c r="I11" s="109" t="n"/>
-      <c r="J11" s="109" t="n"/>
-      <c r="K11" s="109" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="107">
-      <c r="A12" s="109" t="n"/>
-      <c r="B12" s="144" t="inlineStr">
-        <is>
-          <t>نسبة الحافز من الهامش الإضافي</t>
-        </is>
-      </c>
-      <c r="C12" s="147" t="n"/>
-      <c r="D12" s="109" t="n"/>
-      <c r="E12" s="109" t="n"/>
-      <c r="F12" s="109" t="n"/>
-      <c r="G12" s="109" t="n"/>
-      <c r="H12" s="109" t="n"/>
-      <c r="I12" s="109" t="n"/>
-      <c r="J12" s="109" t="n"/>
-      <c r="K12" s="109" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="107">
-      <c r="A13" s="109" t="n"/>
-      <c r="B13" s="144" t="inlineStr">
-        <is>
-          <t>معدل النمو المستهدف للبنزين</t>
-        </is>
-      </c>
-      <c r="C13" s="147" t="n"/>
-      <c r="D13" s="109" t="n"/>
-      <c r="E13" s="109" t="n"/>
-      <c r="F13" s="109" t="n"/>
-      <c r="G13" s="109" t="n"/>
-      <c r="H13" s="109" t="n"/>
-      <c r="I13" s="109" t="n"/>
-      <c r="J13" s="109" t="n"/>
-      <c r="K13" s="109" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="109" t="n"/>
-      <c r="B14" s="109" t="n"/>
-      <c r="C14" s="109" t="n"/>
-      <c r="D14" s="109" t="n"/>
-      <c r="E14" s="109" t="n"/>
-      <c r="F14" s="109" t="n"/>
-      <c r="G14" s="109" t="n"/>
-      <c r="H14" s="109" t="n"/>
-      <c r="I14" s="109" t="n"/>
-      <c r="J14" s="109" t="n"/>
-      <c r="K14" s="109" t="n"/>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" s="107">
-      <c r="A15" s="142" t="inlineStr">
-        <is>
-          <t>المستهدف والحافز لكل محطة</t>
-        </is>
-      </c>
-      <c r="B15" s="143" t="n"/>
-      <c r="C15" s="143" t="n"/>
-      <c r="D15" s="143" t="n"/>
-      <c r="E15" s="143" t="n"/>
-      <c r="F15" s="143" t="n"/>
-      <c r="G15" s="143" t="n"/>
-      <c r="H15" s="143" t="n"/>
-      <c r="I15" s="143" t="n"/>
-      <c r="J15" s="143" t="n"/>
-      <c r="K15" s="143" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="107">
-      <c r="A16" s="111" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B16" s="111" t="inlineStr">
-        <is>
-          <t>المحطة</t>
-        </is>
-      </c>
-      <c r="C16" s="111" t="inlineStr">
-        <is>
-          <t>المنطقة</t>
-        </is>
-      </c>
-      <c r="D16" s="111" t="inlineStr">
-        <is>
-          <t>بنزين سنوي</t>
-        </is>
-      </c>
-      <c r="E16" s="111" t="inlineStr">
-        <is>
-          <t>زيارة/يوم</t>
-        </is>
-      </c>
-      <c r="F16" s="111" t="inlineStr">
-        <is>
-          <t>عمال</t>
-        </is>
-      </c>
-      <c r="G16" s="111" t="inlineStr">
-        <is>
-          <t>الشكاوى</t>
-        </is>
-      </c>
-      <c r="H16" s="111" t="inlineStr">
-        <is>
-          <t>المستهدف</t>
-        </is>
-      </c>
-      <c r="I16" s="111" t="inlineStr">
-        <is>
-          <t>الزيادة</t>
-        </is>
-      </c>
-      <c r="J16" s="111" t="inlineStr">
-        <is>
-          <t>الحافز (ريال/سنة)</t>
-        </is>
-      </c>
-      <c r="K16" s="111" t="inlineStr">
-        <is>
-          <t>لكل عامل شهرياً</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" s="107">
-      <c r="A17" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="148" t="inlineStr">
-        <is>
-          <t>العوالي</t>
-        </is>
-      </c>
-      <c r="C17" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D17" s="149" t="n">
-        <v>35464924</v>
-      </c>
-      <c r="E17" s="149" t="n">
-        <v>3561</v>
-      </c>
-      <c r="F17" s="112" t="n">
-        <v>42</v>
-      </c>
-      <c r="G17" s="112" t="n"/>
-      <c r="H17" s="149">
-        <f>IFERROR(D17*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="150">
-        <f>IFERROR(H17-D17,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="149">
-        <f>IFERROR(I17*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="149">
-        <f>IFERROR(J17/F17/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" s="107">
-      <c r="A18" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="148" t="inlineStr">
-        <is>
-          <t>العمرة الجديدة</t>
-        </is>
-      </c>
-      <c r="C18" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D18" s="149" t="n">
-        <v>34063312</v>
-      </c>
-      <c r="E18" s="149" t="n">
-        <v>4236</v>
-      </c>
-      <c r="F18" s="112" t="n">
-        <v>32</v>
-      </c>
-      <c r="G18" s="151" t="n">
-        <v>58</v>
-      </c>
-      <c r="H18" s="149">
-        <f>IFERROR(D18*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="150">
-        <f>IFERROR(H18-D18,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="149">
-        <f>IFERROR(I18*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="149">
-        <f>IFERROR(J18/F18/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" s="107">
-      <c r="A19" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" s="148" t="inlineStr">
-        <is>
-          <t>عاصفة الصحراء</t>
-        </is>
-      </c>
-      <c r="C19" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D19" s="149" t="n">
-        <v>19648510</v>
-      </c>
-      <c r="E19" s="149" t="n">
-        <v>2137</v>
-      </c>
-      <c r="F19" s="112" t="n">
-        <v>19</v>
-      </c>
-      <c r="G19" s="112" t="n"/>
-      <c r="H19" s="149">
-        <f>IFERROR(D19*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="150">
-        <f>IFERROR(H19-D19,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="149">
-        <f>IFERROR(I19*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K19" s="149">
-        <f>IFERROR(J19/F19/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" s="107">
-      <c r="A20" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="148" t="inlineStr">
-        <is>
-          <t>العزيزية</t>
-        </is>
-      </c>
-      <c r="C20" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D20" s="149" t="n">
-        <v>16732843</v>
-      </c>
-      <c r="E20" s="149" t="n">
-        <v>2359</v>
-      </c>
-      <c r="F20" s="112" t="n">
-        <v>14</v>
-      </c>
-      <c r="G20" s="151" t="n">
-        <v>28</v>
-      </c>
-      <c r="H20" s="149">
-        <f>IFERROR(D20*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="150">
-        <f>IFERROR(H20-D20,"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="149">
-        <f>IFERROR(I20*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K20" s="149">
-        <f>IFERROR(J20/F20/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" s="107">
-      <c r="A21" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="148" t="inlineStr">
-        <is>
-          <t>الشيباني</t>
-        </is>
-      </c>
-      <c r="C21" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D21" s="149" t="n">
-        <v>16309064</v>
-      </c>
-      <c r="E21" s="149" t="n">
-        <v>1726</v>
-      </c>
-      <c r="F21" s="112" t="n">
-        <v>18</v>
-      </c>
-      <c r="G21" s="112" t="n"/>
-      <c r="H21" s="149">
-        <f>IFERROR(D21*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="150">
-        <f>IFERROR(H21-D21,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="149">
-        <f>IFERROR(I21*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="149">
-        <f>IFERROR(J21/F21/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1" s="107">
-      <c r="A22" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="B22" s="148" t="inlineStr">
-        <is>
-          <t>النسيم</t>
-        </is>
-      </c>
-      <c r="C22" s="112" t="inlineStr">
-        <is>
-          <t>جدة</t>
-        </is>
-      </c>
-      <c r="D22" s="149" t="n">
-        <v>16280701</v>
-      </c>
-      <c r="E22" s="149" t="n">
-        <v>2041</v>
-      </c>
-      <c r="F22" s="112" t="n">
-        <v>20</v>
-      </c>
-      <c r="G22" s="112" t="n"/>
-      <c r="H22" s="149">
-        <f>IFERROR(D22*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="150">
-        <f>IFERROR(H22-D22,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="149">
-        <f>IFERROR(I22*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="149">
-        <f>IFERROR(J22/F22/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="107">
-      <c r="A23" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="B23" s="148" t="inlineStr">
-        <is>
-          <t>أحلى مساء</t>
-        </is>
-      </c>
-      <c r="C23" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D23" s="149" t="n">
-        <v>14309768</v>
-      </c>
-      <c r="E23" s="149" t="n">
-        <v>1414</v>
-      </c>
-      <c r="F23" s="112" t="n">
-        <v>13</v>
-      </c>
-      <c r="G23" s="112" t="n"/>
-      <c r="H23" s="149">
-        <f>IFERROR(D23*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="150">
-        <f>IFERROR(H23-D23,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="149">
-        <f>IFERROR(I23*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="149">
-        <f>IFERROR(J23/F23/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="107">
-      <c r="A24" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="B24" s="148" t="inlineStr">
-        <is>
-          <t>الحليس - طريق الجنوب</t>
-        </is>
-      </c>
-      <c r="C24" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D24" s="149" t="n">
-        <v>13354076</v>
-      </c>
-      <c r="E24" s="149" t="n">
-        <v>1694</v>
-      </c>
-      <c r="F24" s="112" t="n">
-        <v>12</v>
-      </c>
-      <c r="G24" s="112" t="n"/>
-      <c r="H24" s="149">
-        <f>IFERROR(D24*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="150">
-        <f>IFERROR(H24-D24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="149">
-        <f>IFERROR(I24*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="149">
-        <f>IFERROR(J24/F24/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" s="107">
-      <c r="A25" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="B25" s="148" t="inlineStr">
-        <is>
-          <t>جنوب الطائف</t>
-        </is>
-      </c>
-      <c r="C25" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D25" s="149" t="n">
-        <v>13311973</v>
-      </c>
-      <c r="E25" s="149" t="n">
-        <v>1483</v>
-      </c>
-      <c r="F25" s="112" t="n">
-        <v>13</v>
-      </c>
-      <c r="G25" s="112" t="n"/>
-      <c r="H25" s="149">
-        <f>IFERROR(D25*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="150">
-        <f>IFERROR(H25-D25,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="149">
-        <f>IFERROR(I25*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="149">
-        <f>IFERROR(J25/F25/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" s="107">
-      <c r="A26" s="112" t="n">
-        <v>10</v>
-      </c>
-      <c r="B26" s="148" t="inlineStr">
-        <is>
-          <t>جبل النور</t>
-        </is>
-      </c>
-      <c r="C26" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D26" s="149" t="n">
-        <v>13248903</v>
-      </c>
-      <c r="E26" s="149" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F26" s="112" t="n">
-        <v>10</v>
-      </c>
-      <c r="G26" s="112" t="n"/>
-      <c r="H26" s="149">
-        <f>IFERROR(D26*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="150">
-        <f>IFERROR(H26-D26,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="149">
-        <f>IFERROR(I26*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="149">
-        <f>IFERROR(J26/F26/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="107">
-      <c r="A27" s="112" t="n">
-        <v>11</v>
-      </c>
-      <c r="B27" s="148" t="inlineStr">
-        <is>
-          <t>الدائري الشمالي</t>
-        </is>
-      </c>
-      <c r="C27" s="112" t="inlineStr">
-        <is>
-          <t>الرياض</t>
-        </is>
-      </c>
-      <c r="D27" s="149" t="n">
-        <v>13247588</v>
-      </c>
-      <c r="E27" s="149" t="n">
-        <v>1169</v>
-      </c>
-      <c r="F27" s="112" t="n">
-        <v>10</v>
-      </c>
-      <c r="G27" s="112" t="n"/>
-      <c r="H27" s="149">
-        <f>IFERROR(D27*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="150">
-        <f>IFERROR(H27-D27,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="149">
-        <f>IFERROR(I27*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="149">
-        <f>IFERROR(J27/F27/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="107">
-      <c r="A28" s="112" t="n">
-        <v>12</v>
-      </c>
-      <c r="B28" s="148" t="inlineStr">
-        <is>
-          <t>القادسية</t>
-        </is>
-      </c>
-      <c r="C28" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D28" s="149" t="n">
-        <v>12654914</v>
-      </c>
-      <c r="E28" s="149" t="n">
-        <v>1702</v>
-      </c>
-      <c r="F28" s="112" t="n">
-        <v>10</v>
-      </c>
-      <c r="G28" s="112" t="n"/>
-      <c r="H28" s="149">
-        <f>IFERROR(D28*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="150">
-        <f>IFERROR(H28-D28,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="149">
-        <f>IFERROR(I28*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K28" s="149">
-        <f>IFERROR(J28/F28/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1" s="107">
-      <c r="A29" s="112" t="n">
-        <v>13</v>
-      </c>
-      <c r="B29" s="148" t="inlineStr">
-        <is>
-          <t>الدائري الثالث - الذكرى</t>
-        </is>
-      </c>
-      <c r="C29" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D29" s="149" t="n">
-        <v>11988986</v>
-      </c>
-      <c r="E29" s="149" t="n">
-        <v>1566</v>
-      </c>
-      <c r="F29" s="112" t="n">
-        <v>12</v>
-      </c>
-      <c r="G29" s="112" t="n"/>
-      <c r="H29" s="149">
-        <f>IFERROR(D29*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="150">
-        <f>IFERROR(H29-D29,"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="149">
-        <f>IFERROR(I29*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K29" s="149">
-        <f>IFERROR(J29/F29/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" s="107">
-      <c r="A30" s="112" t="n">
-        <v>14</v>
-      </c>
-      <c r="B30" s="148" t="inlineStr">
-        <is>
-          <t>الصفا - أحد المسارحة</t>
-        </is>
-      </c>
-      <c r="C30" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D30" s="149" t="n">
-        <v>11882308</v>
-      </c>
-      <c r="E30" s="149" t="n">
-        <v>1807</v>
-      </c>
-      <c r="F30" s="112" t="n"/>
-      <c r="G30" s="112" t="n"/>
-      <c r="H30" s="149">
-        <f>IFERROR(D30*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="150">
-        <f>IFERROR(H30-D30,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="149">
-        <f>IFERROR(I30*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K30" s="149">
-        <f>IFERROR(J30/F30/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" s="107">
-      <c r="A31" s="112" t="n">
-        <v>15</v>
-      </c>
-      <c r="B31" s="148" t="inlineStr">
-        <is>
-          <t>الحسينية</t>
-        </is>
-      </c>
-      <c r="C31" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D31" s="149" t="n">
-        <v>11625662</v>
-      </c>
-      <c r="E31" s="149" t="n">
-        <v>1643</v>
-      </c>
-      <c r="F31" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="G31" s="112" t="n"/>
-      <c r="H31" s="149">
-        <f>IFERROR(D31*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="150">
-        <f>IFERROR(H31-D31,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="149">
-        <f>IFERROR(I31*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="149">
-        <f>IFERROR(J31/F31/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" s="107">
-      <c r="A32" s="112" t="n">
-        <v>16</v>
-      </c>
-      <c r="B32" s="148" t="inlineStr">
-        <is>
-          <t>الرصيفة</t>
-        </is>
-      </c>
-      <c r="C32" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D32" s="149" t="n">
-        <v>11101203</v>
-      </c>
-      <c r="E32" s="149" t="n">
-        <v>1573</v>
-      </c>
-      <c r="F32" s="112" t="n">
-        <v>11</v>
-      </c>
-      <c r="G32" s="112" t="n"/>
-      <c r="H32" s="149">
-        <f>IFERROR(D32*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="150">
-        <f>IFERROR(H32-D32,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="149">
-        <f>IFERROR(I32*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="149">
-        <f>IFERROR(J32/F32/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" s="107">
-      <c r="A33" s="112" t="n">
-        <v>17</v>
-      </c>
-      <c r="B33" s="148" t="inlineStr">
-        <is>
-          <t>طريق الليث - الفضيلة</t>
-        </is>
-      </c>
-      <c r="C33" s="112" t="inlineStr">
-        <is>
-          <t>جدة</t>
-        </is>
-      </c>
-      <c r="D33" s="149" t="n">
-        <v>10864480</v>
-      </c>
-      <c r="E33" s="149" t="n">
-        <v>1892</v>
-      </c>
-      <c r="F33" s="112" t="n"/>
-      <c r="G33" s="112" t="n"/>
-      <c r="H33" s="149">
-        <f>IFERROR(D33*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="150">
-        <f>IFERROR(H33-D33,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="149">
-        <f>IFERROR(I33*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="149">
-        <f>IFERROR(J33/F33/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1" s="107">
-      <c r="A34" s="112" t="n">
-        <v>18</v>
-      </c>
-      <c r="B34" s="148" t="inlineStr">
-        <is>
-          <t>عرفات الشوقية</t>
-        </is>
-      </c>
-      <c r="C34" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D34" s="149" t="n">
-        <v>9931491</v>
-      </c>
-      <c r="E34" s="149" t="n">
-        <v>1290</v>
-      </c>
-      <c r="F34" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="G34" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="H34" s="149">
-        <f>IFERROR(D34*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="150">
-        <f>IFERROR(H34-D34,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="149">
-        <f>IFERROR(I34*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="149">
-        <f>IFERROR(J34/F34/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1" s="107">
-      <c r="A35" s="112" t="n">
-        <v>19</v>
-      </c>
-      <c r="B35" s="148" t="inlineStr">
-        <is>
-          <t>ممشى الشوقية</t>
-        </is>
-      </c>
-      <c r="C35" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D35" s="149" t="n">
-        <v>9558604</v>
-      </c>
-      <c r="E35" s="149" t="n">
-        <v>1363</v>
-      </c>
-      <c r="F35" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="G35" s="112" t="n"/>
-      <c r="H35" s="149">
-        <f>IFERROR(D35*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="150">
-        <f>IFERROR(H35-D35,"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="149">
-        <f>IFERROR(I35*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="149">
-        <f>IFERROR(J35/F35/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1" s="107">
-      <c r="A36" s="112" t="n">
-        <v>20</v>
-      </c>
-      <c r="B36" s="148" t="inlineStr">
-        <is>
-          <t>السواط - شهار</t>
-        </is>
-      </c>
-      <c r="C36" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D36" s="149" t="n">
-        <v>9064151</v>
-      </c>
-      <c r="E36" s="149" t="n">
-        <v>1144</v>
-      </c>
-      <c r="F36" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="G36" s="112" t="n"/>
-      <c r="H36" s="149">
-        <f>IFERROR(D36*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="150">
-        <f>IFERROR(H36-D36,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="149">
-        <f>IFERROR(I36*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="149">
-        <f>IFERROR(J36/F36/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" s="107">
-      <c r="A37" s="112" t="n">
-        <v>21</v>
-      </c>
-      <c r="B37" s="148" t="inlineStr">
-        <is>
-          <t>أبو وافي العمرة</t>
-        </is>
-      </c>
-      <c r="C37" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D37" s="149" t="n">
-        <v>8548346</v>
-      </c>
-      <c r="E37" s="149" t="n">
-        <v>1380</v>
-      </c>
-      <c r="F37" s="112" t="n">
-        <v>13</v>
-      </c>
-      <c r="G37" s="112" t="n"/>
-      <c r="H37" s="149">
-        <f>IFERROR(D37*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="150">
-        <f>IFERROR(H37-D37,"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="149">
-        <f>IFERROR(I37*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="149">
-        <f>IFERROR(J37/F37/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1" s="107">
-      <c r="A38" s="112" t="n">
-        <v>22</v>
-      </c>
-      <c r="B38" s="148" t="inlineStr">
-        <is>
-          <t>الفلاح - فلسطين</t>
-        </is>
-      </c>
-      <c r="C38" s="112" t="inlineStr">
-        <is>
-          <t>جدة</t>
-        </is>
-      </c>
-      <c r="D38" s="149" t="n">
-        <v>7867941</v>
-      </c>
-      <c r="E38" s="149" t="n">
-        <v>1328</v>
-      </c>
-      <c r="F38" s="112" t="n"/>
-      <c r="G38" s="112" t="n"/>
-      <c r="H38" s="149">
-        <f>IFERROR(D38*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="150">
-        <f>IFERROR(H38-D38,"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="149">
-        <f>IFERROR(I38*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="149">
-        <f>IFERROR(J38/F38/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1" s="107">
-      <c r="A39" s="112" t="n">
-        <v>23</v>
-      </c>
-      <c r="B39" s="148" t="inlineStr">
-        <is>
-          <t>كورنيش جيزان</t>
-        </is>
-      </c>
-      <c r="C39" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D39" s="149" t="n">
-        <v>7444371</v>
-      </c>
-      <c r="E39" s="149" t="n">
-        <v>922</v>
-      </c>
-      <c r="F39" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="G39" s="112" t="n"/>
-      <c r="H39" s="149">
-        <f>IFERROR(D39*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="150">
-        <f>IFERROR(H39-D39,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="149">
-        <f>IFERROR(I39*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="149">
-        <f>IFERROR(J39/F39/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1" s="107">
-      <c r="A40" s="112" t="n">
-        <v>24</v>
-      </c>
-      <c r="B40" s="148" t="inlineStr">
-        <is>
-          <t>الجعرانة</t>
-        </is>
-      </c>
-      <c r="C40" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D40" s="149" t="n">
-        <v>7193020</v>
-      </c>
-      <c r="E40" s="149" t="n">
-        <v>1112</v>
-      </c>
-      <c r="F40" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="G40" s="112" t="n"/>
-      <c r="H40" s="149">
-        <f>IFERROR(D40*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="150">
-        <f>IFERROR(H40-D40,"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="149">
-        <f>IFERROR(I40*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="149">
-        <f>IFERROR(J40/F40/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1" s="107">
-      <c r="A41" s="112" t="n">
-        <v>25</v>
-      </c>
-      <c r="B41" s="148" t="inlineStr">
-        <is>
-          <t>الحمرا - طريق الملك عبدالله</t>
-        </is>
-      </c>
-      <c r="C41" s="112" t="inlineStr">
-        <is>
-          <t>الخرج</t>
-        </is>
-      </c>
-      <c r="D41" s="149" t="n">
-        <v>7191456</v>
-      </c>
-      <c r="E41" s="149" t="n">
-        <v>864</v>
-      </c>
-      <c r="F41" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G41" s="112" t="n"/>
-      <c r="H41" s="149">
-        <f>IFERROR(D41*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="150">
-        <f>IFERROR(H41-D41,"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="149">
-        <f>IFERROR(I41*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="149">
-        <f>IFERROR(J41/F41/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1" s="107">
-      <c r="A42" s="112" t="n">
-        <v>26</v>
-      </c>
-      <c r="B42" s="148" t="inlineStr">
-        <is>
-          <t>المعيصم</t>
-        </is>
-      </c>
-      <c r="C42" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D42" s="149" t="n">
-        <v>6999984</v>
-      </c>
-      <c r="E42" s="149" t="n">
-        <v>913</v>
-      </c>
-      <c r="F42" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G42" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="149">
-        <f>IFERROR(D42*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="150">
-        <f>IFERROR(H42-D42,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="149">
-        <f>IFERROR(I42*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="149">
-        <f>IFERROR(J42/F42/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" s="107">
-      <c r="A43" s="112" t="n">
-        <v>27</v>
-      </c>
-      <c r="B43" s="148" t="inlineStr">
-        <is>
-          <t>مدخل محايل</t>
-        </is>
-      </c>
-      <c r="C43" s="112" t="inlineStr">
-        <is>
-          <t>عسير</t>
-        </is>
-      </c>
-      <c r="D43" s="149" t="n">
-        <v>6980426</v>
-      </c>
-      <c r="E43" s="149" t="n">
-        <v>952</v>
-      </c>
-      <c r="F43" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G43" s="112" t="n"/>
-      <c r="H43" s="149">
-        <f>IFERROR(D43*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="150">
-        <f>IFERROR(H43-D43,"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="149">
-        <f>IFERROR(I43*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="149">
-        <f>IFERROR(J43/F43/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1" s="107">
-      <c r="A44" s="112" t="n">
-        <v>28</v>
-      </c>
-      <c r="B44" s="148" t="inlineStr">
-        <is>
-          <t>الرصيفة المسار</t>
-        </is>
-      </c>
-      <c r="C44" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D44" s="149" t="n">
-        <v>6955614</v>
-      </c>
-      <c r="E44" s="149" t="n">
-        <v>1025</v>
-      </c>
-      <c r="F44" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="G44" s="112" t="n"/>
-      <c r="H44" s="149">
-        <f>IFERROR(D44*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="150">
-        <f>IFERROR(H44-D44,"")</f>
-        <v/>
-      </c>
-      <c r="J44" s="149">
-        <f>IFERROR(I44*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K44" s="149">
-        <f>IFERROR(J44/F44/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1" s="107">
-      <c r="A45" s="112" t="n">
-        <v>29</v>
-      </c>
-      <c r="B45" s="148" t="inlineStr">
-        <is>
-          <t>الجمعية الوسام</t>
-        </is>
-      </c>
-      <c r="C45" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D45" s="149" t="n">
-        <v>6835043</v>
-      </c>
-      <c r="E45" s="149" t="n">
-        <v>823</v>
-      </c>
-      <c r="F45" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="G45" s="112" t="n"/>
-      <c r="H45" s="149">
-        <f>IFERROR(D45*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="150">
-        <f>IFERROR(H45-D45,"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="149">
-        <f>IFERROR(I45*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K45" s="149">
-        <f>IFERROR(J45/F45/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1" s="107">
-      <c r="A46" s="112" t="n">
-        <v>30</v>
-      </c>
-      <c r="B46" s="148" t="inlineStr">
-        <is>
-          <t>الجموم - الكنيدري</t>
-        </is>
-      </c>
-      <c r="C46" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D46" s="149" t="n">
-        <v>6267957</v>
-      </c>
-      <c r="E46" s="149" t="n">
-        <v>931</v>
-      </c>
-      <c r="F46" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" s="112" t="n"/>
-      <c r="H46" s="149">
-        <f>IFERROR(D46*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="150">
-        <f>IFERROR(H46-D46,"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="149">
-        <f>IFERROR(I46*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K46" s="149">
-        <f>IFERROR(J46/F46/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1" s="107">
-      <c r="A47" s="112" t="n">
-        <v>31</v>
-      </c>
-      <c r="B47" s="148" t="inlineStr">
-        <is>
-          <t>بطحاء قريش 1</t>
-        </is>
-      </c>
-      <c r="C47" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D47" s="149" t="n">
-        <v>6241831</v>
-      </c>
-      <c r="E47" s="149" t="n">
-        <v>816</v>
-      </c>
-      <c r="F47" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="G47" s="112" t="n"/>
-      <c r="H47" s="149">
-        <f>IFERROR(D47*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="150">
-        <f>IFERROR(H47-D47,"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="149">
-        <f>IFERROR(I47*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="149">
-        <f>IFERROR(J47/F47/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1" s="107">
-      <c r="A48" s="112" t="n">
-        <v>32</v>
-      </c>
-      <c r="B48" s="148" t="inlineStr">
-        <is>
-          <t>طريق السيل</t>
-        </is>
-      </c>
-      <c r="C48" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D48" s="149" t="n">
-        <v>6066855</v>
-      </c>
-      <c r="E48" s="149" t="n">
-        <v>680</v>
-      </c>
-      <c r="F48" s="112" t="n">
-        <v>11</v>
-      </c>
-      <c r="G48" s="112" t="n"/>
-      <c r="H48" s="149">
-        <f>IFERROR(D48*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="150">
-        <f>IFERROR(H48-D48,"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="149">
-        <f>IFERROR(I48*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="149">
-        <f>IFERROR(J48/F48/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" s="107">
-      <c r="A49" s="112" t="n">
-        <v>33</v>
-      </c>
-      <c r="B49" s="148" t="inlineStr">
-        <is>
-          <t>جنوب صبيا</t>
-        </is>
-      </c>
-      <c r="C49" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D49" s="149" t="n">
-        <v>6046920</v>
-      </c>
-      <c r="E49" s="149" t="n">
-        <v>1227</v>
-      </c>
-      <c r="F49" s="112" t="n"/>
-      <c r="G49" s="112" t="n"/>
-      <c r="H49" s="149">
-        <f>IFERROR(D49*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="150">
-        <f>IFERROR(H49-D49,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="149">
-        <f>IFERROR(I49*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="149">
-        <f>IFERROR(J49/F49/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1" s="107">
-      <c r="A50" s="112" t="n">
-        <v>34</v>
-      </c>
-      <c r="B50" s="148" t="inlineStr">
-        <is>
-          <t>بن درويش</t>
-        </is>
-      </c>
-      <c r="C50" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D50" s="149" t="n">
-        <v>5899223</v>
-      </c>
-      <c r="E50" s="149" t="n">
-        <v>807</v>
-      </c>
-      <c r="F50" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G50" s="112" t="n"/>
-      <c r="H50" s="149">
-        <f>IFERROR(D50*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="150">
-        <f>IFERROR(H50-D50,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="149">
-        <f>IFERROR(I50*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K50" s="149">
-        <f>IFERROR(J50/F50/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" s="107">
-      <c r="A51" s="112" t="n">
-        <v>35</v>
-      </c>
-      <c r="B51" s="148" t="inlineStr">
-        <is>
-          <t>الأجاويد</t>
-        </is>
-      </c>
-      <c r="C51" s="112" t="inlineStr">
-        <is>
-          <t>جدة</t>
-        </is>
-      </c>
-      <c r="D51" s="149" t="n">
-        <v>5722940</v>
-      </c>
-      <c r="E51" s="149" t="n">
-        <v>938</v>
-      </c>
-      <c r="F51" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G51" s="112" t="n"/>
-      <c r="H51" s="149">
-        <f>IFERROR(D51*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="150">
-        <f>IFERROR(H51-D51,"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="149">
-        <f>IFERROR(I51*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K51" s="149">
-        <f>IFERROR(J51/F51/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1" s="107">
-      <c r="A52" s="112" t="n">
-        <v>36</v>
-      </c>
-      <c r="B52" s="148" t="inlineStr">
-        <is>
-          <t>القسوم - أحد المسارحة</t>
-        </is>
-      </c>
-      <c r="C52" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D52" s="149" t="n">
-        <v>5647921</v>
-      </c>
-      <c r="E52" s="149" t="n">
-        <v>800</v>
-      </c>
-      <c r="F52" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G52" s="112" t="n"/>
-      <c r="H52" s="149">
-        <f>IFERROR(D52*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="150">
-        <f>IFERROR(H52-D52,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="149">
-        <f>IFERROR(I52*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K52" s="149">
-        <f>IFERROR(J52/F52/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" s="107">
-      <c r="A53" s="112" t="n">
-        <v>37</v>
-      </c>
-      <c r="B53" s="148" t="inlineStr">
-        <is>
-          <t>الكر النازل</t>
-        </is>
-      </c>
-      <c r="C53" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D53" s="149" t="n">
-        <v>5545862</v>
-      </c>
-      <c r="E53" s="149" t="n">
-        <v>537</v>
-      </c>
-      <c r="F53" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="G53" s="112" t="n"/>
-      <c r="H53" s="149">
-        <f>IFERROR(D53*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="150">
-        <f>IFERROR(H53-D53,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="149">
-        <f>IFERROR(I53*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K53" s="149">
-        <f>IFERROR(J53/F53/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" s="107">
-      <c r="A54" s="112" t="n">
-        <v>38</v>
-      </c>
-      <c r="B54" s="148" t="inlineStr">
-        <is>
-          <t>الملك خالد</t>
-        </is>
-      </c>
-      <c r="C54" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D54" s="149" t="n">
-        <v>5284855</v>
-      </c>
-      <c r="E54" s="149" t="n">
-        <v>685</v>
-      </c>
-      <c r="F54" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="G54" s="112" t="n"/>
-      <c r="H54" s="149">
-        <f>IFERROR(D54*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="150">
-        <f>IFERROR(H54-D54,"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="149">
-        <f>IFERROR(I54*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K54" s="149">
-        <f>IFERROR(J54/F54/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1" s="107">
-      <c r="A55" s="112" t="n">
-        <v>39</v>
-      </c>
-      <c r="B55" s="148" t="inlineStr">
-        <is>
-          <t>كورنيش الخبر</t>
-        </is>
-      </c>
-      <c r="C55" s="112" t="inlineStr">
-        <is>
-          <t>الشرقية</t>
-        </is>
-      </c>
-      <c r="D55" s="149" t="n">
-        <v>5197774</v>
-      </c>
-      <c r="E55" s="149" t="n">
-        <v>591</v>
-      </c>
-      <c r="F55" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="G55" s="112" t="n"/>
-      <c r="H55" s="149">
-        <f>IFERROR(D55*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="150">
-        <f>IFERROR(H55-D55,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="149">
-        <f>IFERROR(I55*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K55" s="149">
-        <f>IFERROR(J55/F55/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1" s="107">
-      <c r="A56" s="112" t="n">
-        <v>40</v>
-      </c>
-      <c r="B56" s="148" t="inlineStr">
-        <is>
-          <t>خبت نخلان</t>
-        </is>
-      </c>
-      <c r="C56" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D56" s="149" t="n">
-        <v>4362115</v>
-      </c>
-      <c r="E56" s="149" t="n">
-        <v>650</v>
-      </c>
-      <c r="F56" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="G56" s="112" t="n"/>
-      <c r="H56" s="149">
-        <f>IFERROR(D56*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I56" s="150">
-        <f>IFERROR(H56-D56,"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="149">
-        <f>IFERROR(I56*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K56" s="149">
-        <f>IFERROR(J56/F56/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1" s="107">
-      <c r="A57" s="112" t="n">
-        <v>41</v>
-      </c>
-      <c r="B57" s="148" t="inlineStr">
-        <is>
-          <t>غرناطة - طريق الملك عبدالله</t>
-        </is>
-      </c>
-      <c r="C57" s="112" t="inlineStr">
-        <is>
-          <t>الخرج</t>
-        </is>
-      </c>
-      <c r="D57" s="149" t="n">
-        <v>4341977</v>
-      </c>
-      <c r="E57" s="149" t="n">
-        <v>469</v>
-      </c>
-      <c r="F57" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="G57" s="112" t="n"/>
-      <c r="H57" s="149">
-        <f>IFERROR(D57*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I57" s="150">
-        <f>IFERROR(H57-D57,"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="149">
-        <f>IFERROR(I57*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K57" s="149">
-        <f>IFERROR(J57/F57/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1" s="107">
-      <c r="A58" s="112" t="n">
-        <v>42</v>
-      </c>
-      <c r="B58" s="148" t="inlineStr">
-        <is>
-          <t>طريق صبيا</t>
-        </is>
-      </c>
-      <c r="C58" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D58" s="149" t="n">
-        <v>4191108</v>
-      </c>
-      <c r="E58" s="149" t="n">
-        <v>538</v>
-      </c>
-      <c r="F58" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="G58" s="112" t="n"/>
-      <c r="H58" s="149">
-        <f>IFERROR(D58*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="150">
-        <f>IFERROR(H58-D58,"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="149">
-        <f>IFERROR(I58*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K58" s="149">
-        <f>IFERROR(J58/F58/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1" s="107">
-      <c r="A59" s="112" t="n">
-        <v>43</v>
-      </c>
-      <c r="B59" s="148" t="inlineStr">
-        <is>
-          <t>بطحاء قريش 2</t>
-        </is>
-      </c>
-      <c r="C59" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D59" s="149" t="n">
-        <v>4156161</v>
-      </c>
-      <c r="E59" s="149" t="n">
-        <v>586</v>
-      </c>
-      <c r="F59" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="G59" s="112" t="n"/>
-      <c r="H59" s="149">
-        <f>IFERROR(D59*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I59" s="150">
-        <f>IFERROR(H59-D59,"")</f>
-        <v/>
-      </c>
-      <c r="J59" s="149">
-        <f>IFERROR(I59*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K59" s="149">
-        <f>IFERROR(J59/F59/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1" s="107">
-      <c r="A60" s="112" t="n">
-        <v>44</v>
-      </c>
-      <c r="B60" s="148" t="inlineStr">
-        <is>
-          <t>الشرايع</t>
-        </is>
-      </c>
-      <c r="C60" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D60" s="149" t="n">
-        <v>3857645</v>
-      </c>
-      <c r="E60" s="149" t="n">
-        <v>456</v>
-      </c>
-      <c r="F60" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="H60" s="149">
-        <f>IFERROR(D60*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I60" s="150">
-        <f>IFERROR(H60-D60,"")</f>
-        <v/>
-      </c>
-      <c r="J60" s="149">
-        <f>IFERROR(I60*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K60" s="149">
-        <f>IFERROR(J60/F60/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1" s="107">
-      <c r="A61" s="112" t="n">
-        <v>45</v>
-      </c>
-      <c r="B61" s="148" t="inlineStr">
-        <is>
-          <t>خليص</t>
-        </is>
-      </c>
-      <c r="C61" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D61" s="149" t="n">
-        <v>3791200</v>
-      </c>
-      <c r="E61" s="149" t="n">
-        <v>423</v>
-      </c>
-      <c r="F61" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="G61" s="112" t="n"/>
-      <c r="H61" s="149">
-        <f>IFERROR(D61*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I61" s="150">
-        <f>IFERROR(H61-D61,"")</f>
-        <v/>
-      </c>
-      <c r="J61" s="149">
-        <f>IFERROR(I61*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K61" s="149">
-        <f>IFERROR(J61/F61/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1" s="107">
-      <c r="A62" s="112" t="n">
-        <v>46</v>
-      </c>
-      <c r="B62" s="148" t="inlineStr">
-        <is>
-          <t>جبل ثور - جوهرة النسيم</t>
-        </is>
-      </c>
-      <c r="C62" s="112" t="inlineStr">
-        <is>
-          <t>مكة</t>
-        </is>
-      </c>
-      <c r="D62" s="149" t="n">
-        <v>3708152</v>
-      </c>
-      <c r="E62" s="149" t="n">
-        <v>451</v>
-      </c>
-      <c r="F62" s="112" t="n"/>
-      <c r="G62" s="112" t="n"/>
-      <c r="H62" s="149">
-        <f>IFERROR(D62*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I62" s="150">
-        <f>IFERROR(H62-D62,"")</f>
-        <v/>
-      </c>
-      <c r="J62" s="149">
-        <f>IFERROR(I62*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K62" s="149">
-        <f>IFERROR(J62/F62/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1" s="107">
-      <c r="A63" s="112" t="n">
-        <v>47</v>
-      </c>
-      <c r="B63" s="148" t="inlineStr">
-        <is>
-          <t>الدائري الشرقي</t>
-        </is>
-      </c>
-      <c r="C63" s="112" t="inlineStr">
-        <is>
-          <t>القصيم</t>
-        </is>
-      </c>
-      <c r="D63" s="149" t="n">
-        <v>3599745</v>
-      </c>
-      <c r="E63" s="149" t="n">
-        <v>441</v>
-      </c>
-      <c r="F63" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="G63" s="112" t="n"/>
-      <c r="H63" s="149">
-        <f>IFERROR(D63*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I63" s="150">
-        <f>IFERROR(H63-D63,"")</f>
-        <v/>
-      </c>
-      <c r="J63" s="149">
-        <f>IFERROR(I63*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K63" s="149">
-        <f>IFERROR(J63/F63/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1" s="107">
-      <c r="A64" s="112" t="n">
-        <v>48</v>
-      </c>
-      <c r="B64" s="148" t="inlineStr">
-        <is>
-          <t>الناصفة</t>
-        </is>
-      </c>
-      <c r="C64" s="112" t="inlineStr">
-        <is>
-          <t>الخرج</t>
-        </is>
-      </c>
-      <c r="D64" s="149" t="n">
-        <v>3433425</v>
-      </c>
-      <c r="E64" s="149" t="n">
-        <v>402</v>
-      </c>
-      <c r="F64" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="G64" s="112" t="n"/>
-      <c r="H64" s="149">
-        <f>IFERROR(D64*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I64" s="150">
-        <f>IFERROR(H64-D64,"")</f>
-        <v/>
-      </c>
-      <c r="J64" s="149">
-        <f>IFERROR(I64*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K64" s="149">
-        <f>IFERROR(J64/F64/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1" s="107">
-      <c r="A65" s="112" t="n">
-        <v>49</v>
-      </c>
-      <c r="B65" s="148" t="inlineStr">
-        <is>
-          <t>البيعة</t>
-        </is>
-      </c>
-      <c r="C65" s="112" t="inlineStr">
-        <is>
-          <t>الطائف</t>
-        </is>
-      </c>
-      <c r="D65" s="149" t="n">
-        <v>3315559</v>
-      </c>
-      <c r="E65" s="149" t="n">
-        <v>455</v>
-      </c>
-      <c r="F65" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="G65" s="112" t="n"/>
-      <c r="H65" s="149">
-        <f>IFERROR(D65*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I65" s="150">
-        <f>IFERROR(H65-D65,"")</f>
-        <v/>
-      </c>
-      <c r="J65" s="149">
-        <f>IFERROR(I65*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K65" s="149">
-        <f>IFERROR(J65/F65/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1" s="107">
-      <c r="A66" s="112" t="n">
-        <v>50</v>
-      </c>
-      <c r="B66" s="148" t="inlineStr">
-        <is>
-          <t>العريفي</t>
-        </is>
-      </c>
-      <c r="C66" s="112" t="inlineStr">
-        <is>
-          <t>حائل</t>
-        </is>
-      </c>
-      <c r="D66" s="149" t="n">
-        <v>2663618</v>
-      </c>
-      <c r="E66" s="149" t="n">
-        <v>327</v>
-      </c>
-      <c r="F66" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="G66" s="112" t="n"/>
-      <c r="H66" s="149">
-        <f>IFERROR(D66*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I66" s="150">
-        <f>IFERROR(H66-D66,"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="149">
-        <f>IFERROR(I66*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K66" s="149">
-        <f>IFERROR(J66/F66/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1" s="107">
-      <c r="A67" s="112" t="n">
-        <v>51</v>
-      </c>
-      <c r="B67" s="148" t="inlineStr">
-        <is>
-          <t>الكوثر</t>
-        </is>
-      </c>
-      <c r="C67" s="112" t="inlineStr">
-        <is>
-          <t>جدة</t>
-        </is>
-      </c>
-      <c r="D67" s="149" t="n">
-        <v>2286567</v>
-      </c>
-      <c r="E67" s="149" t="n">
-        <v>333</v>
-      </c>
-      <c r="F67" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="G67" s="112" t="n"/>
-      <c r="H67" s="149">
-        <f>IFERROR(D67*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I67" s="150">
-        <f>IFERROR(H67-D67,"")</f>
-        <v/>
-      </c>
-      <c r="J67" s="149">
-        <f>IFERROR(I67*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K67" s="149">
-        <f>IFERROR(J67/F67/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1" s="107">
-      <c r="A68" s="112" t="n">
-        <v>52</v>
-      </c>
-      <c r="B68" s="148" t="inlineStr">
-        <is>
-          <t>الروابي - المودة</t>
-        </is>
-      </c>
-      <c r="C68" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D68" s="149" t="n">
-        <v>2086987</v>
-      </c>
-      <c r="E68" s="149" t="n">
-        <v>281</v>
-      </c>
-      <c r="F68" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="G68" s="112" t="n"/>
-      <c r="H68" s="149">
-        <f>IFERROR(D68*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I68" s="150">
-        <f>IFERROR(H68-D68,"")</f>
-        <v/>
-      </c>
-      <c r="J68" s="149">
-        <f>IFERROR(I68*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K68" s="149">
-        <f>IFERROR(J68/F68/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1" s="107">
-      <c r="A69" s="112" t="n">
-        <v>53</v>
-      </c>
-      <c r="B69" s="148" t="inlineStr">
-        <is>
-          <t>صناعية صامطة</t>
-        </is>
-      </c>
-      <c r="C69" s="112" t="inlineStr">
-        <is>
-          <t>جازان</t>
-        </is>
-      </c>
-      <c r="D69" s="149" t="n">
-        <v>1960098</v>
-      </c>
-      <c r="E69" s="149" t="n">
-        <v>408</v>
-      </c>
-      <c r="F69" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="G69" s="112" t="n"/>
-      <c r="H69" s="149">
-        <f>IFERROR(D69*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I69" s="150">
-        <f>IFERROR(H69-D69,"")</f>
-        <v/>
-      </c>
-      <c r="J69" s="149">
-        <f>IFERROR(I69*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K69" s="149">
-        <f>IFERROR(J69/F69/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1" s="107">
-      <c r="A70" s="112" t="n">
-        <v>54</v>
-      </c>
-      <c r="B70" s="148" t="inlineStr">
-        <is>
-          <t>طريق السلام</t>
-        </is>
-      </c>
-      <c r="C70" s="112" t="inlineStr">
-        <is>
-          <t>المدينة المنورة</t>
-        </is>
-      </c>
-      <c r="D70" s="149" t="n">
-        <v>1451309</v>
-      </c>
-      <c r="E70" s="149" t="n">
-        <v>196</v>
-      </c>
-      <c r="F70" s="112" t="n"/>
-      <c r="G70" s="112" t="n"/>
-      <c r="H70" s="149">
-        <f>IFERROR(D70*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I70" s="150">
-        <f>IFERROR(H70-D70,"")</f>
-        <v/>
-      </c>
-      <c r="J70" s="149">
-        <f>IFERROR(I70*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K70" s="149">
-        <f>IFERROR(J70/F70/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1" s="107">
-      <c r="A71" s="112" t="n">
-        <v>55</v>
-      </c>
-      <c r="B71" s="148" t="inlineStr">
-        <is>
-          <t>المركب</t>
-        </is>
-      </c>
-      <c r="C71" s="112" t="inlineStr">
-        <is>
-          <t>نجران</t>
-        </is>
-      </c>
-      <c r="D71" s="149" t="n">
-        <v>1099275</v>
-      </c>
-      <c r="E71" s="149" t="n">
-        <v>154</v>
-      </c>
-      <c r="F71" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="G71" s="112" t="n"/>
-      <c r="H71" s="149">
-        <f>IFERROR(D71*(1+$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="I71" s="150">
-        <f>IFERROR(H71-D71,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="149">
-        <f>IFERROR(I71*$C$11/100*$C$12,"")</f>
-        <v/>
-      </c>
-      <c r="K71" s="149">
-        <f>IFERROR(J71/F71/12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="107">
-      <c r="A72" s="152" t="n"/>
-      <c r="B72" s="152" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="C72" s="152" t="n"/>
-      <c r="D72" s="153">
-        <f>SUM(D17:D71)</f>
-        <v/>
-      </c>
-      <c r="E72" s="153">
-        <f>SUM(E17:E71)</f>
-        <v/>
-      </c>
-      <c r="F72" s="153">
-        <f>SUM(F17:F71)</f>
-        <v/>
-      </c>
-      <c r="G72" s="153">
-        <f>SUM(G17:G71)</f>
-        <v/>
-      </c>
-      <c r="H72" s="153">
-        <f>SUM(H17:H71)</f>
-        <v/>
-      </c>
-      <c r="I72" s="153">
-        <f>SUM(I17:I71)</f>
-        <v/>
-      </c>
-      <c r="J72" s="153">
-        <f>SUM(J17:J71)</f>
-        <v/>
-      </c>
-      <c r="K72" s="152" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="109" t="n"/>
-      <c r="B73" s="109" t="n"/>
-      <c r="C73" s="109" t="n"/>
-      <c r="D73" s="109" t="n"/>
-      <c r="E73" s="109" t="n"/>
-      <c r="F73" s="109" t="n"/>
-      <c r="G73" s="109" t="n"/>
-      <c r="H73" s="109" t="n"/>
-      <c r="I73" s="109" t="n"/>
-      <c r="J73" s="109" t="n"/>
-      <c r="K73" s="109" t="n"/>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="107">
-      <c r="A74" s="109" t="n"/>
-      <c r="B74" s="115" t="inlineStr">
-        <is>
-          <t>آلية الحافز</t>
-        </is>
-      </c>
-      <c r="C74" s="109" t="n"/>
-      <c r="D74" s="109" t="n"/>
-      <c r="E74" s="109" t="n"/>
-      <c r="F74" s="109" t="n"/>
-      <c r="G74" s="109" t="n"/>
-      <c r="H74" s="109" t="n"/>
-      <c r="I74" s="109" t="n"/>
-      <c r="J74" s="109" t="n"/>
-      <c r="K74" s="109" t="n"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" s="107">
-      <c r="A75" s="109" t="n"/>
-      <c r="B75" s="109" t="n"/>
-      <c r="C75" s="116" t="inlineStr">
-        <is>
-          <t>•  الحافز نسبة من هامش اللتر الإضافي — لا مبلغ ثابت</t>
-        </is>
-      </c>
-      <c r="D75" s="109" t="n"/>
-      <c r="E75" s="109" t="n"/>
-      <c r="F75" s="109" t="n"/>
-      <c r="G75" s="109" t="n"/>
-      <c r="H75" s="109" t="n"/>
-      <c r="I75" s="109" t="n"/>
-      <c r="J75" s="109" t="n"/>
-      <c r="K75" s="109" t="n"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" s="107">
-      <c r="A76" s="109" t="n"/>
-      <c r="B76" s="109" t="n"/>
-      <c r="C76" s="116" t="inlineStr">
-        <is>
-          <t>•  فلا يُصرف إلا إذا تحقق النمو، ويتناسب مع حجمه</t>
-        </is>
-      </c>
-      <c r="D76" s="109" t="n"/>
-      <c r="E76" s="109" t="n"/>
-      <c r="F76" s="109" t="n"/>
-      <c r="G76" s="109" t="n"/>
-      <c r="H76" s="109" t="n"/>
-      <c r="I76" s="109" t="n"/>
-      <c r="J76" s="109" t="n"/>
-      <c r="K76" s="109" t="n"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" s="107">
-      <c r="A77" s="109" t="n"/>
-      <c r="B77" s="109" t="n"/>
-      <c r="C77" s="116" t="inlineStr">
-        <is>
-          <t>•  التوزيع على عمال المحطة يربط الأجر بنتيجة المحطة مباشرة</t>
-        </is>
-      </c>
-      <c r="D77" s="109" t="n"/>
-      <c r="E77" s="109" t="n"/>
-      <c r="F77" s="109" t="n"/>
-      <c r="G77" s="109" t="n"/>
-      <c r="H77" s="109" t="n"/>
-      <c r="I77" s="109" t="n"/>
-      <c r="J77" s="109" t="n"/>
-      <c r="K77" s="109" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="109" t="n"/>
-      <c r="B78" s="109" t="n"/>
-      <c r="C78" s="109" t="n"/>
-      <c r="D78" s="109" t="n"/>
-      <c r="E78" s="109" t="n"/>
-      <c r="F78" s="109" t="n"/>
-      <c r="G78" s="109" t="n"/>
-      <c r="H78" s="109" t="n"/>
-      <c r="I78" s="109" t="n"/>
-      <c r="J78" s="109" t="n"/>
-      <c r="K78" s="109" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="107">
-      <c r="A79" s="109" t="n"/>
-      <c r="B79" s="117" t="inlineStr">
-        <is>
-          <t>شرط نجاحه</t>
-        </is>
-      </c>
-      <c r="C79" s="109" t="n"/>
-      <c r="D79" s="109" t="n"/>
-      <c r="E79" s="109" t="n"/>
-      <c r="F79" s="109" t="n"/>
-      <c r="G79" s="109" t="n"/>
-      <c r="H79" s="109" t="n"/>
-      <c r="I79" s="109" t="n"/>
-      <c r="J79" s="109" t="n"/>
-      <c r="K79" s="109" t="n"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" s="107">
-      <c r="A80" s="109" t="n"/>
-      <c r="B80" s="109" t="n"/>
-      <c r="C80" s="116" t="inlineStr">
-        <is>
-          <t>•  قياس شهري معلن لكل محطة — العامل يرى موقعه من المستهدف</t>
-        </is>
-      </c>
-      <c r="D80" s="109" t="n"/>
-      <c r="E80" s="109" t="n"/>
-      <c r="F80" s="109" t="n"/>
-      <c r="G80" s="109" t="n"/>
-      <c r="H80" s="109" t="n"/>
-      <c r="I80" s="109" t="n"/>
-      <c r="J80" s="109" t="n"/>
-      <c r="K80" s="109" t="n"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" s="107">
-      <c r="A81" s="109" t="n"/>
-      <c r="B81" s="109" t="n"/>
-      <c r="C81" s="116" t="inlineStr">
-        <is>
-          <t>•  ربطه بمؤشر الخدمة أيضاً: الشكاوى وزمن التعبئة</t>
-        </is>
-      </c>
-      <c r="D81" s="109" t="n"/>
-      <c r="E81" s="109" t="n"/>
-      <c r="F81" s="109" t="n"/>
-      <c r="G81" s="109" t="n"/>
-      <c r="H81" s="109" t="n"/>
-      <c r="I81" s="109" t="n"/>
-      <c r="J81" s="109" t="n"/>
-      <c r="K81" s="109" t="n"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" s="107">
-      <c r="A82" s="109" t="n"/>
-      <c r="B82" s="109" t="n"/>
-      <c r="C82" s="116" t="inlineStr">
-        <is>
-          <t>•  بلا قياس زمن الخدمة يتحوّل الحافز إلى مكافأة حجم لا مكافأة أداء</t>
-        </is>
-      </c>
-      <c r="D82" s="109" t="n"/>
-      <c r="E82" s="109" t="n"/>
-      <c r="F82" s="109" t="n"/>
-      <c r="G82" s="109" t="n"/>
-      <c r="H82" s="109" t="n"/>
-      <c r="I82" s="109" t="n"/>
-      <c r="J82" s="109" t="n"/>
-      <c r="K82" s="109" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="109" t="n"/>
-      <c r="B83" s="109" t="n"/>
-      <c r="C83" s="109" t="n"/>
-      <c r="D83" s="109" t="n"/>
-      <c r="E83" s="109" t="n"/>
-      <c r="F83" s="109" t="n"/>
-      <c r="G83" s="109" t="n"/>
-      <c r="H83" s="109" t="n"/>
-      <c r="I83" s="109" t="n"/>
-      <c r="J83" s="109" t="n"/>
-      <c r="K83" s="109" t="n"/>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="107">
-      <c r="A84" s="109" t="n"/>
-      <c r="B84" s="117" t="inlineStr">
-        <is>
-          <t>حدّ خفض المصاريف</t>
-        </is>
-      </c>
-      <c r="C84" s="109" t="n"/>
-      <c r="D84" s="109" t="n"/>
-      <c r="E84" s="109" t="n"/>
-      <c r="F84" s="109" t="n"/>
-      <c r="G84" s="109" t="n"/>
-      <c r="H84" s="109" t="n"/>
-      <c r="I84" s="109" t="n"/>
-      <c r="J84" s="109" t="n"/>
-      <c r="K84" s="109" t="n"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" s="107">
-      <c r="A85" s="109" t="n"/>
-      <c r="B85" s="109" t="n"/>
-      <c r="C85" s="116" t="inlineStr">
-        <is>
-          <t>•  المصاريف النقدية 0.94 هللة لكل لتر — و88% من المصاريف إهلاك</t>
-        </is>
-      </c>
-      <c r="D85" s="109" t="n"/>
-      <c r="E85" s="109" t="n"/>
-      <c r="F85" s="109" t="n"/>
-      <c r="G85" s="109" t="n"/>
-      <c r="H85" s="109" t="n"/>
-      <c r="I85" s="109" t="n"/>
-      <c r="J85" s="109" t="n"/>
-      <c r="K85" s="109" t="n"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" s="107">
-      <c r="A86" s="109" t="n"/>
-      <c r="B86" s="109" t="n"/>
-      <c r="C86" s="116" t="inlineStr">
-        <is>
-          <t>•  فالخفض يعطي أقل من هللة، بينما النمو 5% يعطي أضعافه</t>
-        </is>
-      </c>
-      <c r="D86" s="109" t="n"/>
-      <c r="E86" s="109" t="n"/>
-      <c r="F86" s="109" t="n"/>
-      <c r="G86" s="109" t="n"/>
-      <c r="H86" s="109" t="n"/>
-      <c r="I86" s="109" t="n"/>
-      <c r="J86" s="109" t="n"/>
-      <c r="K86" s="109" t="n"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="107">
-      <c r="A87" s="109" t="n"/>
-      <c r="B87" s="109" t="n"/>
-      <c r="C87" s="116" t="inlineStr">
-        <is>
-          <t>•  الأولوية للحجم والخدمة لا لبند المصاريف</t>
-        </is>
-      </c>
-      <c r="D87" s="109" t="n"/>
-      <c r="E87" s="109" t="n"/>
-      <c r="F87" s="109" t="n"/>
-      <c r="G87" s="109" t="n"/>
-      <c r="H87" s="109" t="n"/>
-      <c r="I87" s="109" t="n"/>
-      <c r="J87" s="109" t="n"/>
-      <c r="K87" s="109" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="C82:K82"/>
-    <mergeCell ref="C85:K85"/>
-    <mergeCell ref="C81:K81"/>
-    <mergeCell ref="C76:K76"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="C75:K75"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="C80:K80"/>
-    <mergeCell ref="C87:K87"/>
-    <mergeCell ref="C77:K77"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C86:K86"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13755,7 +15721,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>الوقود — قناة الشركات</t>
         </is>
@@ -13768,7 +15734,7 @@
       <c r="G1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>المنافس: بترو آب وواعي والمنصات · السلاح: مندوب أساطيل + خصم هللة + الاشتراك في كل منصة</t>
         </is>
@@ -13946,7 +15912,7 @@
           <t>هامش المساهمة قبل الخصم (هللة)</t>
         </is>
       </c>
-      <c r="C10" s="146" t="n"/>
+      <c r="C10" s="183" t="n"/>
       <c r="D10" s="109" t="n"/>
       <c r="E10" s="109" t="n"/>
       <c r="F10" s="109" t="n"/>
@@ -13959,7 +15925,7 @@
           <t>الخصم الممنوح (هللة)</t>
         </is>
       </c>
-      <c r="C11" s="146" t="n">
+      <c r="C11" s="183" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="109" t="n"/>
@@ -13974,7 +15940,7 @@
           <t>اللترات المتعاقدة المستهدفة (سنوياً)</t>
         </is>
       </c>
-      <c r="C12" s="154" t="n"/>
+      <c r="C12" s="185" t="n"/>
       <c r="D12" s="109" t="n"/>
       <c r="E12" s="109" t="n"/>
       <c r="F12" s="109" t="n"/>
@@ -14391,7 +16357,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" s="107">
       <c r="A32" s="109" t="n"/>
-      <c r="B32" s="115" t="inlineStr">
+      <c r="B32" s="128" t="inlineStr">
         <is>
           <t>حجم الفرصة</t>
         </is>
@@ -14405,7 +16371,7 @@
     <row r="33" ht="15.75" customHeight="1" s="107">
       <c r="A33" s="109" t="n"/>
       <c r="B33" s="109" t="n"/>
-      <c r="C33" s="116" t="inlineStr">
+      <c r="C33" s="129" t="inlineStr">
         <is>
           <t>•  الديزل 109.4 مليون لتر سنوياً — وهو سوق الأساطيل المتاح داخل شبكتنا</t>
         </is>
@@ -14418,7 +16384,7 @@
     <row r="34" ht="15.75" customHeight="1" s="107">
       <c r="A34" s="109" t="n"/>
       <c r="B34" s="109" t="n"/>
-      <c r="C34" s="116" t="inlineStr">
+      <c r="C34" s="129" t="inlineStr">
         <is>
           <t>•  MK289 ديزلها 64% و43.7 لتر لكل زيارة — أرقام أسطول لا أفراد</t>
         </is>
@@ -14431,7 +16397,7 @@
     <row r="35" ht="15.75" customHeight="1" s="107">
       <c r="A35" s="109" t="n"/>
       <c r="B35" s="109" t="n"/>
-      <c r="C35" s="116" t="inlineStr">
+      <c r="C35" s="129" t="inlineStr">
         <is>
           <t>•  الحجم يمرّ عندنا اليوم بلا عقد — فالتعاقد تثبيت لا اكتساب</t>
         </is>
@@ -14452,7 +16418,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" s="107">
       <c r="A37" s="109" t="n"/>
-      <c r="B37" s="115" t="inlineStr">
+      <c r="B37" s="128" t="inlineStr">
         <is>
           <t>لماذا المساران معاً</t>
         </is>
@@ -14466,7 +16432,7 @@
     <row r="38" ht="15.75" customHeight="1" s="107">
       <c r="A38" s="109" t="n"/>
       <c r="B38" s="109" t="n"/>
-      <c r="C38" s="116" t="inlineStr">
+      <c r="C38" s="129" t="inlineStr">
         <is>
           <t>•  المندوب يصل إلى أساطيل الحج والعمرة مباشرة — عقد وبيانات وهامش كامل</t>
         </is>
@@ -14479,7 +16445,7 @@
     <row r="39" ht="15.75" customHeight="1" s="107">
       <c r="A39" s="109" t="n"/>
       <c r="B39" s="109" t="n"/>
-      <c r="C39" s="116" t="inlineStr">
+      <c r="C39" s="129" t="inlineStr">
         <is>
           <t>•  والمنصات تلتقط ما لا يصله المندوب مقابل عمولة</t>
         </is>
@@ -14492,7 +16458,7 @@
     <row r="40" ht="15.75" customHeight="1" s="107">
       <c r="A40" s="109" t="n"/>
       <c r="B40" s="109" t="n"/>
-      <c r="C40" s="116" t="inlineStr">
+      <c r="C40" s="129" t="inlineStr">
         <is>
           <t>•  المعيار: عمولة المنصة لكل لتر مقابل تكلفة المندوب لكل لتر — يُراجع كل ربع</t>
         </is>
@@ -14527,7 +16493,7 @@
     <row r="43" ht="15.75" customHeight="1" s="107">
       <c r="A43" s="109" t="n"/>
       <c r="B43" s="109" t="n"/>
-      <c r="C43" s="116" t="inlineStr">
+      <c r="C43" s="129" t="inlineStr">
         <is>
           <t>•  آلية ائتمان وفوترة قبل أول عقد — لا يمكن بيع الأسطول نقداً</t>
         </is>
@@ -14540,7 +16506,7 @@
     <row r="44" ht="15.75" customHeight="1" s="107">
       <c r="A44" s="109" t="n"/>
       <c r="B44" s="109" t="n"/>
-      <c r="C44" s="116" t="inlineStr">
+      <c r="C44" s="129" t="inlineStr">
         <is>
           <t>•  تعريف الحد الأدنى للحجم الذي يستحق الخصم</t>
         </is>
@@ -14572,7 +16538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14588,7 +16554,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>العقار والتأجير</t>
         </is>
@@ -14601,7 +16567,7 @@
       <c r="G1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>المسيطر: الوسطاء · القاعدة: الوحدة الشاغرة تكلفة لا فرصة ضائعة</t>
         </is>
@@ -14779,7 +16745,7 @@
           <t>الإيجار السنوي المتوقع للوحدة</t>
         </is>
       </c>
-      <c r="C10" s="154" t="n"/>
+      <c r="C10" s="185" t="n"/>
       <c r="D10" s="109" t="n"/>
       <c r="E10" s="109" t="n"/>
       <c r="F10" s="109" t="n"/>
@@ -14792,7 +16758,7 @@
           <t>تكلفة التمويل والإهلاك للوحدة سنوياً</t>
         </is>
       </c>
-      <c r="C11" s="154" t="n"/>
+      <c r="C11" s="185" t="n"/>
       <c r="D11" s="109" t="n"/>
       <c r="E11" s="109" t="n"/>
       <c r="F11" s="109" t="n"/>
@@ -14805,7 +16771,7 @@
           <t>عمولة الوسيط (% من الإيجار السنوي)</t>
         </is>
       </c>
-      <c r="C12" s="147" t="n"/>
+      <c r="C12" s="184" t="n"/>
       <c r="D12" s="109" t="n"/>
       <c r="E12" s="109" t="n"/>
       <c r="F12" s="109" t="n"/>
@@ -14818,7 +16784,7 @@
           <t>أشهر الشغور المتوقعة بلا وسيط</t>
         </is>
       </c>
-      <c r="C13" s="160" t="n"/>
+      <c r="C13" s="186" t="n"/>
       <c r="D13" s="109" t="n"/>
       <c r="E13" s="109" t="n"/>
       <c r="F13" s="109" t="n"/>
@@ -15211,7 +17177,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" s="107">
       <c r="A30" s="109" t="n"/>
-      <c r="B30" s="115" t="inlineStr">
+      <c r="B30" s="128" t="inlineStr">
         <is>
           <t>لماذا الوسطاء</t>
         </is>
@@ -15225,7 +17191,7 @@
     <row r="31" ht="15.75" customHeight="1" s="107">
       <c r="A31" s="109" t="n"/>
       <c r="B31" s="109" t="n"/>
-      <c r="C31" s="116" t="inlineStr">
+      <c r="C31" s="129" t="inlineStr">
         <is>
           <t>•  الوسيط يملك قائمة المستأجرين الباحثين — ونحن لا نملكها</t>
         </is>
@@ -15238,7 +17204,7 @@
     <row r="32" ht="15.75" customHeight="1" s="107">
       <c r="A32" s="109" t="n"/>
       <c r="B32" s="109" t="n"/>
-      <c r="C32" s="116" t="inlineStr">
+      <c r="C32" s="129" t="inlineStr">
         <is>
           <t>•  ووكيل الامتياز هو من يقرّر أين تفتح العلامة فرعها لا العلامة نفسها</t>
         </is>
@@ -15251,7 +17217,7 @@
     <row r="33" ht="15.75" customHeight="1" s="107">
       <c r="A33" s="109" t="n"/>
       <c r="B33" s="109" t="n"/>
-      <c r="C33" s="116" t="inlineStr">
+      <c r="C33" s="129" t="inlineStr">
         <is>
           <t>•  العمولة تكلفة متغيرة تُدفع عند الإشغال فقط</t>
         </is>
@@ -15286,7 +17252,7 @@
     <row r="36" ht="15.75" customHeight="1" s="107">
       <c r="A36" s="109" t="n"/>
       <c r="B36" s="109" t="n"/>
-      <c r="C36" s="116" t="inlineStr">
+      <c r="C36" s="129" t="inlineStr">
         <is>
           <t>•  التمويل وإهلاك حق الاستخدام مدفوعان على الأرض كاملة</t>
         </is>
@@ -15299,7 +17265,7 @@
     <row r="37" ht="15.75" customHeight="1" s="107">
       <c r="A37" s="109" t="n"/>
       <c r="B37" s="109" t="n"/>
-      <c r="C37" s="116" t="inlineStr">
+      <c r="C37" s="129" t="inlineStr">
         <is>
           <t>•  في العمرة يلتهمان 63% من دخل الإيجار وفي الشرايع 106%</t>
         </is>
@@ -15312,7 +17278,7 @@
     <row r="38" ht="15.75" customHeight="1" s="107">
       <c r="A38" s="109" t="n"/>
       <c r="B38" s="109" t="n"/>
-      <c r="C38" s="116" t="inlineStr">
+      <c r="C38" s="129" t="inlineStr">
         <is>
           <t>•  فكل ريال إيجار إضافي يتدفّق إلى الربح شبه كاملاً</t>
         </is>
@@ -15347,7 +17313,7 @@
     <row r="41" ht="15.75" customHeight="1" s="107">
       <c r="A41" s="109" t="n"/>
       <c r="B41" s="109" t="n"/>
-      <c r="C41" s="116" t="inlineStr">
+      <c r="C41" s="129" t="inlineStr">
         <is>
           <t>•  52 محطة تحت الإنشاء — إدراج المغسلة والسوبرماركت في تصميمها الآن</t>
         </is>
@@ -15360,7 +17326,7 @@
     <row r="42" ht="15.75" customHeight="1" s="107">
       <c r="A42" s="109" t="n"/>
       <c r="B42" s="109" t="n"/>
-      <c r="C42" s="116" t="inlineStr">
+      <c r="C42" s="129" t="inlineStr">
         <is>
           <t>•  التعاقد قبل الافتتاح أرخص وأسرع من ملء محطة عاملة</t>
         </is>
@@ -15392,7 +17358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15408,7 +17374,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>الإكسسوارات</t>
         </is>
@@ -15421,7 +17387,7 @@
       <c r="G1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>المسيطر: أصحاب محلات التجزئة · النموذج: مساحة بيع ومساحة في التطبيق مقابل نسبة</t>
         </is>
@@ -15634,7 +17600,7 @@
           <t>اسم الشريك</t>
         </is>
       </c>
-      <c r="C11" s="162" t="n"/>
+      <c r="C11" s="177" t="n"/>
       <c r="D11" s="112" t="inlineStr">
         <is>
           <t>نص</t>
@@ -15657,7 +17623,7 @@
           <t>الفئة</t>
         </is>
       </c>
-      <c r="C12" s="162" t="n"/>
+      <c r="C12" s="177" t="n"/>
       <c r="D12" s="112" t="inlineStr">
         <is>
           <t>نص</t>
@@ -15680,7 +17646,7 @@
           <t>المحطات المشمولة</t>
         </is>
       </c>
-      <c r="C13" s="154" t="n"/>
+      <c r="C13" s="185" t="n"/>
       <c r="D13" s="112" t="inlineStr">
         <is>
           <t>عدد</t>
@@ -15703,7 +17669,7 @@
           <t>مساحة البيع لكل محطة</t>
         </is>
       </c>
-      <c r="C14" s="154" t="n"/>
+      <c r="C14" s="185" t="n"/>
       <c r="D14" s="112" t="inlineStr">
         <is>
           <t>م²</t>
@@ -15726,7 +17692,7 @@
           <t>مساحة التطبيق</t>
         </is>
       </c>
-      <c r="C15" s="162" t="n"/>
+      <c r="C15" s="177" t="n"/>
       <c r="D15" s="112" t="inlineStr">
         <is>
           <t>نعم / لا</t>
@@ -15749,7 +17715,7 @@
           <t>الحد الأدنى المضمون شهرياً</t>
         </is>
       </c>
-      <c r="C16" s="154" t="n"/>
+      <c r="C16" s="185" t="n"/>
       <c r="D16" s="112" t="inlineStr">
         <is>
           <t>ريال</t>
@@ -15772,7 +17738,7 @@
           <t>نسبة درب من المبيعات</t>
         </is>
       </c>
-      <c r="C17" s="147" t="n"/>
+      <c r="C17" s="184" t="n"/>
       <c r="D17" s="112" t="inlineStr">
         <is>
           <t>%</t>
@@ -15795,7 +17761,7 @@
           <t>مبيعات الشريك المتوقعة شهرياً</t>
         </is>
       </c>
-      <c r="C18" s="154" t="n"/>
+      <c r="C18" s="185" t="n"/>
       <c r="D18" s="112" t="inlineStr">
         <is>
           <t>ريال</t>
@@ -15908,7 +17874,7 @@
           <t>مدة العقد</t>
         </is>
       </c>
-      <c r="C22" s="154" t="n"/>
+      <c r="C22" s="185" t="n"/>
       <c r="D22" s="112" t="inlineStr">
         <is>
           <t>شهر</t>
@@ -15931,7 +17897,7 @@
           <t>شرط مشاركة بيانات المبيعات</t>
         </is>
       </c>
-      <c r="C23" s="162" t="n"/>
+      <c r="C23" s="177" t="n"/>
       <c r="D23" s="112" t="inlineStr">
         <is>
           <t>نعم / لا</t>
@@ -15969,7 +17935,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" s="107">
       <c r="A26" s="109" t="n"/>
-      <c r="B26" s="115" t="inlineStr">
+      <c r="B26" s="128" t="inlineStr">
         <is>
           <t>لماذا النسبة لا الإيجار الثابت</t>
         </is>
@@ -15983,7 +17949,7 @@
     <row r="27" ht="15.75" customHeight="1" s="107">
       <c r="A27" s="109" t="n"/>
       <c r="B27" s="109" t="n"/>
-      <c r="C27" s="116" t="inlineStr">
+      <c r="C27" s="129" t="inlineStr">
         <is>
           <t>•  المخزون بطيء والمرتجعات عالية — والمخاطرة على الشريك</t>
         </is>
@@ -15996,7 +17962,7 @@
     <row r="28" ht="15.75" customHeight="1" s="107">
       <c r="A28" s="109" t="n"/>
       <c r="B28" s="109" t="n"/>
-      <c r="C28" s="116" t="inlineStr">
+      <c r="C28" s="129" t="inlineStr">
         <is>
           <t>•  الحد الأدنى المضمون يحمي عائدنا والنسبة ترفع سقفه</t>
         </is>
@@ -16009,7 +17975,7 @@
     <row r="29" ht="15.75" customHeight="1" s="107">
       <c r="A29" s="109" t="n"/>
       <c r="B29" s="109" t="n"/>
-      <c r="C29" s="116" t="inlineStr">
+      <c r="C29" s="129" t="inlineStr">
         <is>
           <t>•  شرط مشاركة بيانات المبيعات أساس العقد — بدونه لا يمكن التحقق</t>
         </is>
@@ -16030,7 +17996,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" s="107">
       <c r="A31" s="109" t="n"/>
-      <c r="B31" s="115" t="inlineStr">
+      <c r="B31" s="128" t="inlineStr">
         <is>
           <t>مساحة التطبيق</t>
         </is>
@@ -16044,7 +18010,7 @@
     <row r="32" ht="15.75" customHeight="1" s="107">
       <c r="A32" s="109" t="n"/>
       <c r="B32" s="109" t="n"/>
-      <c r="C32" s="116" t="inlineStr">
+      <c r="C32" s="129" t="inlineStr">
         <is>
           <t>•  أصل رقمي نملكه ولا نبيعه اليوم</t>
         </is>
@@ -16057,7 +18023,7 @@
     <row r="33" ht="15.75" customHeight="1" s="107">
       <c r="A33" s="109" t="n"/>
       <c r="B33" s="109" t="n"/>
-      <c r="C33" s="116" t="inlineStr">
+      <c r="C33" s="129" t="inlineStr">
         <is>
           <t>•  تُسعَّر ضمن الحزمة مع مساحة البيع</t>
         </is>
@@ -16070,7 +18036,7 @@
     <row r="34" ht="15.75" customHeight="1" s="107">
       <c r="A34" s="109" t="n"/>
       <c r="B34" s="109" t="n"/>
-      <c r="C34" s="116" t="inlineStr">
+      <c r="C34" s="129" t="inlineStr">
         <is>
           <t>•  توسّع سوق الشريك خارج المحطة وترفع قيمة التطبيق نفسه</t>
         </is>
@@ -16091,7 +18057,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" s="107">
       <c r="A36" s="109" t="n"/>
-      <c r="B36" s="115" t="inlineStr">
+      <c r="B36" s="128" t="inlineStr">
         <is>
           <t>الشريحتان</t>
         </is>
@@ -16105,7 +18071,7 @@
     <row r="37" ht="15.75" customHeight="1" s="107">
       <c r="A37" s="109" t="n"/>
       <c r="B37" s="109" t="n"/>
-      <c r="C37" s="116" t="inlineStr">
+      <c r="C37" s="129" t="inlineStr">
         <is>
           <t>•  سريع الدوران (زيوت · معطرات · شواحن): رفّ عند الكاشير — يبدأ فوراً</t>
         </is>
@@ -16118,7 +18084,7 @@
     <row r="38" ht="15.75" customHeight="1" s="107">
       <c r="A38" s="109" t="n"/>
       <c r="B38" s="109" t="n"/>
-      <c r="C38" s="116" t="inlineStr">
+      <c r="C38" s="129" t="inlineStr">
         <is>
           <t>•  الزينة والتجهيز (تظليل · أفلام · إضاءة): وحدة مستقلة لمتخصص</t>
         </is>
@@ -16149,7 +18115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16166,7 +18132,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
+      <c r="A1" s="118" t="inlineStr">
         <is>
           <t>اقتصاديات اللتر</t>
         </is>
@@ -16178,7 +18144,7 @@
       <c r="F1" s="109" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="119" t="inlineStr">
         <is>
           <t>أرقام محققة من قائمة الدخل — النصف الأول 2026 · الوحدة: هللة</t>
         </is>
@@ -16444,7 +18410,7 @@
     <row r="14" ht="15.75" customHeight="1" s="107">
       <c r="A14" s="109" t="n"/>
       <c r="B14" s="109" t="n"/>
-      <c r="C14" s="116" t="inlineStr">
+      <c r="C14" s="129" t="inlineStr">
         <is>
           <t>•  المصاريف النقدية 0.94 هللة لكل لتر فقط</t>
         </is>
@@ -16456,7 +18422,7 @@
     <row r="15" ht="15.75" customHeight="1" s="107">
       <c r="A15" s="109" t="n"/>
       <c r="B15" s="109" t="n"/>
-      <c r="C15" s="116" t="inlineStr">
+      <c r="C15" s="129" t="inlineStr">
         <is>
           <t>•  الإهلاك 88% من المصاريف — غير نقدي وغير قابل للخفض</t>
         </is>
@@ -16468,7 +18434,7 @@
     <row r="16" ht="15.75" customHeight="1" s="107">
       <c r="A16" s="109" t="n"/>
       <c r="B16" s="109" t="n"/>
-      <c r="C16" s="116" t="inlineStr">
+      <c r="C16" s="129" t="inlineStr">
         <is>
           <t>•  فرفع الحجم 5% يعطي أضعاف ما يعطيه أي خفض ممكن</t>
         </is>
@@ -16487,7 +18453,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" s="107">
       <c r="A18" s="109" t="n"/>
-      <c r="B18" s="115" t="inlineStr">
+      <c r="B18" s="128" t="inlineStr">
         <is>
           <t>الديزل يسحب الهامش</t>
         </is>
@@ -16500,7 +18466,7 @@
     <row r="19" ht="15.75" customHeight="1" s="107">
       <c r="A19" s="109" t="n"/>
       <c r="B19" s="109" t="n"/>
-      <c r="C19" s="116" t="inlineStr">
+      <c r="C19" s="129" t="inlineStr">
         <is>
           <t>•  العمرة ديزلها 28% وهامشها 10.07 هللة</t>
         </is>
@@ -16512,7 +18478,7 @@
     <row r="20" ht="15.75" customHeight="1" s="107">
       <c r="A20" s="109" t="n"/>
       <c r="B20" s="109" t="n"/>
-      <c r="C20" s="116" t="inlineStr">
+      <c r="C20" s="129" t="inlineStr">
         <is>
           <t>•  الشرايع بلا ديزل وهامشها 13.36 هللة</t>
         </is>
@@ -16524,7 +18490,7 @@
     <row r="21" ht="15.75" customHeight="1" s="107">
       <c r="A21" s="109" t="n"/>
       <c r="B21" s="109" t="n"/>
-      <c r="C21" s="116" t="inlineStr">
+      <c r="C21" s="129" t="inlineStr">
         <is>
           <t>•  ورفع حصة البنزين رفع مباشر للهامش لا مجرد زيادة إيراد</t>
         </is>
@@ -16556,7 +18522,7 @@
     <row r="24" ht="15.75" customHeight="1" s="107">
       <c r="A24" s="109" t="n"/>
       <c r="B24" s="109" t="n"/>
-      <c r="C24" s="116" t="inlineStr">
+      <c r="C24" s="129" t="inlineStr">
         <is>
           <t>•  التمويل وإهلاك حق الاستخدام ثابتان ومدفوعان</t>
         </is>
@@ -16568,7 +18534,7 @@
     <row r="25" ht="15.75" customHeight="1" s="107">
       <c r="A25" s="109" t="n"/>
       <c r="B25" s="109" t="n"/>
-      <c r="C25" s="116" t="inlineStr">
+      <c r="C25" s="129" t="inlineStr">
         <is>
           <t>•  يلتهمان 63% من دخل الإيجار في العمرة و106% في الشرايع</t>
         </is>
@@ -16580,7 +18546,7 @@
     <row r="26" ht="15.75" customHeight="1" s="107">
       <c r="A26" s="109" t="n"/>
       <c r="B26" s="109" t="n"/>
-      <c r="C26" s="116" t="inlineStr">
+      <c r="C26" s="129" t="inlineStr">
         <is>
           <t>•  فكل إيجار إضافي ربح شبه صافٍ</t>
         </is>
@@ -16607,616 +18573,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="4" customWidth="1" style="106" min="1" max="1"/>
-    <col width="26" customWidth="1" style="106" min="2" max="2"/>
-    <col width="16" customWidth="1" style="106" min="3" max="5"/>
-    <col width="38" customWidth="1" style="106" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="108" t="inlineStr">
-        <is>
-          <t>النموذج التجريبي</t>
-        </is>
-      </c>
-      <c r="B1" s="109" t="n"/>
-      <c r="C1" s="109" t="n"/>
-      <c r="D1" s="109" t="n"/>
-      <c r="E1" s="109" t="n"/>
-      <c r="F1" s="109" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="110" t="inlineStr">
-        <is>
-          <t>محطتان للوقود ومحطة للمستأجرين</t>
-        </is>
-      </c>
-      <c r="B2" s="109" t="n"/>
-      <c r="C2" s="109" t="n"/>
-      <c r="D2" s="109" t="n"/>
-      <c r="E2" s="109" t="n"/>
-      <c r="F2" s="109" t="n"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" s="107">
-      <c r="A3" s="142" t="inlineStr">
-        <is>
-          <t>التصميم</t>
-        </is>
-      </c>
-      <c r="B3" s="143" t="n"/>
-      <c r="C3" s="143" t="n"/>
-      <c r="D3" s="143" t="n"/>
-      <c r="E3" s="143" t="n"/>
-      <c r="F3" s="143" t="n"/>
-    </row>
-    <row r="4" ht="21.75" customHeight="1" s="107">
-      <c r="A4" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="113" t="inlineStr">
-        <is>
-          <t>عرفات الشوقية MK017</t>
-        </is>
-      </c>
-      <c r="C4" s="112" t="inlineStr">
-        <is>
-          <t>وقود</t>
-        </is>
-      </c>
-      <c r="D4" s="114" t="inlineStr">
-        <is>
-          <t>نامية +6.9%</t>
-        </is>
-      </c>
-      <c r="E4" s="114" t="n"/>
-      <c r="F4" s="114" t="inlineStr">
-        <is>
-          <t>المرجع — ماذا تفعل الناجحة</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21.75" customHeight="1" s="107">
-      <c r="A5" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="113" t="inlineStr">
-        <is>
-          <t>بن درويش MK023</t>
-        </is>
-      </c>
-      <c r="C5" s="112" t="inlineStr">
-        <is>
-          <t>وقود</t>
-        </is>
-      </c>
-      <c r="D5" s="114" t="inlineStr">
-        <is>
-          <t>هابطة −12.1%</t>
-        </is>
-      </c>
-      <c r="E5" s="114" t="n"/>
-      <c r="F5" s="114" t="inlineStr">
-        <is>
-          <t>الهدف — ما الذي يمكن تغييره</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="107">
-      <c r="A6" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="113" t="inlineStr">
-        <is>
-          <t>النورية MK007</t>
-        </is>
-      </c>
-      <c r="C6" s="112" t="inlineStr">
-        <is>
-          <t>مستأجرون</t>
-        </is>
-      </c>
-      <c r="D6" s="114" t="inlineStr">
-        <is>
-          <t>أعلى حركة 4,236 زيارة/يوم</t>
-        </is>
-      </c>
-      <c r="E6" s="114" t="n"/>
-      <c r="F6" s="114" t="inlineStr">
-        <is>
-          <t>حملات المستأجرين وقياس أثرها</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="109" t="n"/>
-      <c r="B7" s="109" t="n"/>
-      <c r="C7" s="109" t="n"/>
-      <c r="D7" s="109" t="n"/>
-      <c r="E7" s="109" t="n"/>
-      <c r="F7" s="109" t="n"/>
-    </row>
-    <row r="8" ht="21.75" customHeight="1" s="107">
-      <c r="A8" s="142" t="inlineStr">
-        <is>
-          <t>مقارنة محطتَي الوقود</t>
-        </is>
-      </c>
-      <c r="B8" s="143" t="n"/>
-      <c r="C8" s="143" t="n"/>
-      <c r="D8" s="143" t="n"/>
-      <c r="E8" s="143" t="n"/>
-      <c r="F8" s="143" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="107">
-      <c r="A9" s="111" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="111" t="inlineStr">
-        <is>
-          <t>المؤشر</t>
-        </is>
-      </c>
-      <c r="C9" s="111" t="inlineStr">
-        <is>
-          <t>عرفات الشوقية</t>
-        </is>
-      </c>
-      <c r="D9" s="111" t="inlineStr">
-        <is>
-          <t>بن درويش</t>
-        </is>
-      </c>
-      <c r="E9" s="111" t="inlineStr">
-        <is>
-          <t>الفارق</t>
-        </is>
-      </c>
-      <c r="F9" s="111" t="inlineStr">
-        <is>
-          <t>الدلالة</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" s="107">
-      <c r="A10" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="148" t="inlineStr">
-        <is>
-          <t>النمو</t>
-        </is>
-      </c>
-      <c r="C10" s="112" t="inlineStr">
-        <is>
-          <t>+6.9%</t>
-        </is>
-      </c>
-      <c r="D10" s="112" t="inlineStr">
-        <is>
-          <t>-12.1%</t>
-        </is>
-      </c>
-      <c r="E10" s="112" t="n"/>
-      <c r="F10" s="114" t="inlineStr">
-        <is>
-          <t>المتغيّر المراد تفسيره</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" s="107">
-      <c r="A11" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="148" t="inlineStr">
-        <is>
-          <t>المنطقة والنمط</t>
-        </is>
-      </c>
-      <c r="C11" s="112" t="inlineStr">
-        <is>
-          <t>مكة · حيوية</t>
-        </is>
-      </c>
-      <c r="D11" s="112" t="inlineStr">
-        <is>
-          <t>مكة · حيوية</t>
-        </is>
-      </c>
-      <c r="E11" s="112" t="n"/>
-      <c r="F11" s="114" t="inlineStr">
-        <is>
-          <t>متطابق</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1" s="107">
-      <c r="A12" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="148" t="inlineStr">
-        <is>
-          <t>المزيج</t>
-        </is>
-      </c>
-      <c r="C12" s="112" t="inlineStr">
-        <is>
-          <t>51.7 / 48.3</t>
-        </is>
-      </c>
-      <c r="D12" s="112" t="inlineStr">
-        <is>
-          <t>54.0 / 46.0</t>
-        </is>
-      </c>
-      <c r="E12" s="112" t="n"/>
-      <c r="F12" s="114" t="inlineStr">
-        <is>
-          <t>متطابق · بلا ديزل</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1" s="107">
-      <c r="A13" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="148" t="inlineStr">
-        <is>
-          <t>طريقة الدفع</t>
-        </is>
-      </c>
-      <c r="C13" s="112" t="inlineStr">
-        <is>
-          <t>نقد 100%</t>
-        </is>
-      </c>
-      <c r="D13" s="112" t="inlineStr">
-        <is>
-          <t>نقد 100%</t>
-        </is>
-      </c>
-      <c r="E13" s="112" t="n"/>
-      <c r="F13" s="114" t="inlineStr">
-        <is>
-          <t>صفر شبكة وصفر تطبيق</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18.75" customHeight="1" s="107">
-      <c r="A14" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="148" t="inlineStr">
-        <is>
-          <t>الزيارات يومياً</t>
-        </is>
-      </c>
-      <c r="C14" s="169" t="n">
-        <v>1290</v>
-      </c>
-      <c r="D14" s="169" t="n">
-        <v>807</v>
-      </c>
-      <c r="E14" s="170">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="114" t="n"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" s="107">
-      <c r="A15" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="148" t="inlineStr">
-        <is>
-          <t>اللترات يومياً</t>
-        </is>
-      </c>
-      <c r="C15" s="169" t="n">
-        <v>27210</v>
-      </c>
-      <c r="D15" s="169" t="n">
-        <v>16162</v>
-      </c>
-      <c r="E15" s="170">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="114" t="n"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1" s="107">
-      <c r="A16" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" s="148" t="inlineStr">
-        <is>
-          <t>لتر لكل زيارة</t>
-        </is>
-      </c>
-      <c r="C16" s="169" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="D16" s="169" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="E16" s="170">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="114" t="inlineStr">
-        <is>
-          <t>سلة أكبر في عرفات</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" s="107">
-      <c r="A17" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="148" t="inlineStr">
-        <is>
-          <t>المضخات</t>
-        </is>
-      </c>
-      <c r="C17" s="169" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="169" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="170">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="114" t="n"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1" s="107">
-      <c r="A18" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="148" t="inlineStr">
-        <is>
-          <t>زيارة لكل مضخة</t>
-        </is>
-      </c>
-      <c r="C18" s="169" t="n">
-        <v>143</v>
-      </c>
-      <c r="D18" s="169" t="n">
-        <v>202</v>
-      </c>
-      <c r="E18" s="170">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="114" t="inlineStr">
-        <is>
-          <t>بن درويش أزحم رغم أنها أصغر</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" s="107">
-      <c r="A19" s="112" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="148" t="inlineStr">
-        <is>
-          <t>العمال</t>
-        </is>
-      </c>
-      <c r="C19" s="169" t="n">
-        <v>9</v>
-      </c>
-      <c r="D19" s="169" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" s="170">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="114" t="inlineStr">
-        <is>
-          <t>مطابق للمتفق عليه</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" s="107">
-      <c r="A20" s="112" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="148" t="inlineStr">
-        <is>
-          <t>الشكاوى</t>
-        </is>
-      </c>
-      <c r="C20" s="169" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="169" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="170">
-        <f>C20-D20</f>
-        <v/>
-      </c>
-      <c r="F20" s="114" t="inlineStr">
-        <is>
-          <t>بن درويش بلا شكاوى رغم تراجعها</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="109" t="n"/>
-      <c r="B21" s="109" t="n"/>
-      <c r="C21" s="109" t="n"/>
-      <c r="D21" s="109" t="n"/>
-      <c r="E21" s="109" t="n"/>
-      <c r="F21" s="109" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="107">
-      <c r="A22" s="109" t="n"/>
-      <c r="B22" s="115" t="inlineStr">
-        <is>
-          <t>ما يعزله التصميم</t>
-        </is>
-      </c>
-      <c r="C22" s="109" t="n"/>
-      <c r="D22" s="109" t="n"/>
-      <c r="E22" s="109" t="n"/>
-      <c r="F22" s="109" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="107">
-      <c r="A23" s="109" t="n"/>
-      <c r="B23" s="109" t="n"/>
-      <c r="C23" s="116" t="inlineStr">
-        <is>
-          <t>•  نفس المنطقة والنمط والمزيج وطريقة الدفع</t>
-        </is>
-      </c>
-      <c r="D23" s="109" t="n"/>
-      <c r="E23" s="109" t="n"/>
-      <c r="F23" s="109" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="107">
-      <c r="A24" s="109" t="n"/>
-      <c r="B24" s="109" t="n"/>
-      <c r="C24" s="116" t="inlineStr">
-        <is>
-          <t>•  فالفارق لا يُفسَّر بالموقع ولا المنتج ولا نوع العميل</t>
-        </is>
-      </c>
-      <c r="D24" s="109" t="n"/>
-      <c r="E24" s="109" t="n"/>
-      <c r="F24" s="109" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="109" t="n"/>
-      <c r="B25" s="109" t="n"/>
-      <c r="C25" s="109" t="n"/>
-      <c r="D25" s="109" t="n"/>
-      <c r="E25" s="109" t="n"/>
-      <c r="F25" s="109" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="107">
-      <c r="A26" s="109" t="n"/>
-      <c r="B26" s="115" t="inlineStr">
-        <is>
-          <t>ما يُقاس ميدانياً</t>
-        </is>
-      </c>
-      <c r="C26" s="109" t="n"/>
-      <c r="D26" s="109" t="n"/>
-      <c r="E26" s="109" t="n"/>
-      <c r="F26" s="109" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="107">
-      <c r="A27" s="109" t="n"/>
-      <c r="B27" s="109" t="n"/>
-      <c r="C27" s="116" t="inlineStr">
-        <is>
-          <t>•  زمن الخدمة لكل تعبئة في ساعة الذروة (21)</t>
-        </is>
-      </c>
-      <c r="D27" s="109" t="n"/>
-      <c r="E27" s="109" t="n"/>
-      <c r="F27" s="109" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="107">
-      <c r="A28" s="109" t="n"/>
-      <c r="B28" s="109" t="n"/>
-      <c r="C28" s="116" t="inlineStr">
-        <is>
-          <t>•  عدد المركبات التي تدخل ولا تعبّئ</t>
-        </is>
-      </c>
-      <c r="D28" s="109" t="n"/>
-      <c r="E28" s="109" t="n"/>
-      <c r="F28" s="109" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="107">
-      <c r="A29" s="109" t="n"/>
-      <c r="B29" s="109" t="n"/>
-      <c r="C29" s="116" t="inlineStr">
-        <is>
-          <t>•  المنافس الأقرب والمسافة إليه · وتغيّرات المسار</t>
-        </is>
-      </c>
-      <c r="D29" s="109" t="n"/>
-      <c r="E29" s="109" t="n"/>
-      <c r="F29" s="109" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="109" t="n"/>
-      <c r="B30" s="109" t="n"/>
-      <c r="C30" s="109" t="n"/>
-      <c r="D30" s="109" t="n"/>
-      <c r="E30" s="109" t="n"/>
-      <c r="F30" s="109" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="107">
-      <c r="A31" s="109" t="n"/>
-      <c r="B31" s="117" t="inlineStr">
-        <is>
-          <t>فرصة فورية مشتركة</t>
-        </is>
-      </c>
-      <c r="C31" s="109" t="n"/>
-      <c r="D31" s="109" t="n"/>
-      <c r="E31" s="109" t="n"/>
-      <c r="F31" s="109" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" s="107">
-      <c r="A32" s="109" t="n"/>
-      <c r="B32" s="109" t="n"/>
-      <c r="C32" s="116" t="inlineStr">
-        <is>
-          <t>•  الدفع نقد 100% في المحطتين — تفعيل الشبكة والتطبيق يبني قاعدة تعريف من الصفر</t>
-        </is>
-      </c>
-      <c r="D32" s="109" t="n"/>
-      <c r="E32" s="109" t="n"/>
-      <c r="F32" s="109" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" s="107">
-      <c r="A33" s="109" t="n"/>
-      <c r="B33" s="109" t="n"/>
-      <c r="C33" s="116" t="inlineStr">
-        <is>
-          <t>•  بن درويش 4 مضخات لـ807 زيارة — أقل من نصف طاقة عرفات</t>
-        </is>
-      </c>
-      <c r="D33" s="109" t="n"/>
-      <c r="E33" s="109" t="n"/>
-      <c r="F33" s="109" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C28:F28"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/docs/commercial-plan.xlsx
+++ b/docs/commercial-plan.xlsx
@@ -10,19 +10,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإطار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأداء المالي — يوليو ٢٠٢٦" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="وقود · أفراد" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنافسون" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="السيطرة الميدانية" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="وقود · شركات" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="وقود · شركات" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنافسون" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="السيطرة الميدانية" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العقار والتأجير" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإكسسوارات" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تكلفة اللتر" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجريبي — ثلاث محطات" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تشخيص فقدان الحركة" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج العامل" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مطابقة الوردية مع الطلب" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجربة الشرايع" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="البيانات" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بيانات الورديات" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل الوحدات التأجيرية" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإكسسوارات" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تكلفة اللتر" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجريبي — ثلاث محطات" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تشخيص فقدان الحركة" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نموذج العامل" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مطابقة الوردية مع الطلب" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجربة الشرايع" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="البيانات" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بيانات الورديات" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1940,7 +1941,7 @@
       </c>
       <c r="E7" s="114" t="inlineStr">
         <is>
-          <t>96 وحدة شاغرة · إشغال 25%</t>
+          <t>إشغال المشغّلة ٧٩٪ · ٦٨٩ وحدة تحت التنفيذ · ٢٦٩ في الامتياز</t>
         </is>
       </c>
       <c r="F7" s="114" t="inlineStr">
@@ -2114,6 +2115,466 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="106" min="1" max="1"/>
+    <col width="30" customWidth="1" style="106" min="2" max="2"/>
+    <col width="15" customWidth="1" style="106" min="3" max="4"/>
+    <col width="13" customWidth="1" style="106" min="5" max="5"/>
+    <col width="40" customWidth="1" style="106" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="107">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>اقتصاديات اللتر</t>
+        </is>
+      </c>
+      <c r="B1" s="109" t="n"/>
+      <c r="C1" s="109" t="n"/>
+      <c r="D1" s="109" t="n"/>
+      <c r="E1" s="109" t="n"/>
+      <c r="F1" s="109" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="107">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>أرقام محققة من قائمة الدخل — النصف الأول 2026 · الوحدة: هللة</t>
+        </is>
+      </c>
+      <c r="B2" s="109" t="n"/>
+      <c r="C2" s="109" t="n"/>
+      <c r="D2" s="109" t="n"/>
+      <c r="E2" s="109" t="n"/>
+      <c r="F2" s="109" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="107">
+      <c r="A3" s="111" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="111" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="C3" s="111" t="inlineStr">
+        <is>
+          <t>MK007 العمرة</t>
+        </is>
+      </c>
+      <c r="D3" s="111" t="inlineStr">
+        <is>
+          <t>MK019 الشرايع</t>
+        </is>
+      </c>
+      <c r="E3" s="111" t="inlineStr">
+        <is>
+          <t>الفارق</t>
+        </is>
+      </c>
+      <c r="F3" s="111" t="inlineStr">
+        <is>
+          <t>الدلالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1" s="107">
+      <c r="A4" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="148" t="inlineStr">
+        <is>
+          <t>الإيراد لكل لتر</t>
+        </is>
+      </c>
+      <c r="C4" s="155" t="n">
+        <v>182.51</v>
+      </c>
+      <c r="D4" s="155" t="n">
+        <v>196.77</v>
+      </c>
+      <c r="E4" s="163">
+        <f>C4-D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="114" t="inlineStr">
+        <is>
+          <t>قسمة الإيراد على اللترات</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.75" customHeight="1" s="107">
+      <c r="A5" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="148" t="inlineStr">
+        <is>
+          <t>تكلفة البضاعة</t>
+        </is>
+      </c>
+      <c r="C5" s="155" t="n">
+        <v>-170</v>
+      </c>
+      <c r="D5" s="155" t="n">
+        <v>-180.67</v>
+      </c>
+      <c r="E5" s="163">
+        <f>C5-D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="114" t="inlineStr">
+        <is>
+          <t>93% من الإيراد — خارج سيطرتنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="107">
+      <c r="A6" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="148" t="inlineStr">
+        <is>
+          <t>النقل</t>
+        </is>
+      </c>
+      <c r="C6" s="155" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="D6" s="155" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="E6" s="163">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="114" t="inlineStr">
+        <is>
+          <t>أجرة الرحلة الفعلية 623 ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.75" customHeight="1" s="107">
+      <c r="A7" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="148" t="inlineStr">
+        <is>
+          <t>التبخّر</t>
+        </is>
+      </c>
+      <c r="C7" s="155" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="D7" s="155" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="E7" s="163">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="114" t="inlineStr">
+        <is>
+          <t>0.32% من التكلفة</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.75" customHeight="1" s="107">
+      <c r="A8" s="164" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="165" t="inlineStr">
+        <is>
+          <t>هامش مساهمة الوقود</t>
+        </is>
+      </c>
+      <c r="C8" s="166" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="D8" s="166" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E8" s="167">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="168" t="inlineStr">
+        <is>
+          <t>الهدف 15 هللة</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="107">
+      <c r="A9" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="148" t="inlineStr">
+        <is>
+          <t>صافي التأجير</t>
+        </is>
+      </c>
+      <c r="C9" s="155" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D9" s="155" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="E9" s="163">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="114" t="inlineStr">
+        <is>
+          <t>سالب في الشرايع</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21.75" customHeight="1" s="107">
+      <c r="A10" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="148" t="inlineStr">
+        <is>
+          <t>المصاريف التشغيلية</t>
+        </is>
+      </c>
+      <c r="C10" s="155" t="n">
+        <v>-10.23</v>
+      </c>
+      <c r="D10" s="155" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="E10" s="163">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="114" t="inlineStr">
+        <is>
+          <t>88% منها إهلاك غير نقدي</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.75" customHeight="1" s="107">
+      <c r="A11" s="164" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="165" t="inlineStr">
+        <is>
+          <t>صافي الربح</t>
+        </is>
+      </c>
+      <c r="C11" s="166" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="D11" s="166" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E11" s="167">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="168" t="inlineStr">
+        <is>
+          <t>الفجوة عن الهدف 9.9 و11.1 هللة</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="109" t="n"/>
+      <c r="B12" s="109" t="n"/>
+      <c r="C12" s="109" t="n"/>
+      <c r="D12" s="109" t="n"/>
+      <c r="E12" s="109" t="n"/>
+      <c r="F12" s="109" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="107">
+      <c r="A13" s="109" t="n"/>
+      <c r="B13" s="117" t="inlineStr">
+        <is>
+          <t>لماذا لا يمرّ الحل عبر التكلفة</t>
+        </is>
+      </c>
+      <c r="C13" s="109" t="n"/>
+      <c r="D13" s="109" t="n"/>
+      <c r="E13" s="109" t="n"/>
+      <c r="F13" s="109" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="107">
+      <c r="A14" s="109" t="n"/>
+      <c r="B14" s="109" t="n"/>
+      <c r="C14" s="129" t="inlineStr">
+        <is>
+          <t>•  المصاريف النقدية 0.94 هللة لكل لتر فقط</t>
+        </is>
+      </c>
+      <c r="D14" s="109" t="n"/>
+      <c r="E14" s="109" t="n"/>
+      <c r="F14" s="109" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="107">
+      <c r="A15" s="109" t="n"/>
+      <c r="B15" s="109" t="n"/>
+      <c r="C15" s="129" t="inlineStr">
+        <is>
+          <t>•  الإهلاك 88% من المصاريف — غير نقدي وغير قابل للخفض</t>
+        </is>
+      </c>
+      <c r="D15" s="109" t="n"/>
+      <c r="E15" s="109" t="n"/>
+      <c r="F15" s="109" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="107">
+      <c r="A16" s="109" t="n"/>
+      <c r="B16" s="109" t="n"/>
+      <c r="C16" s="129" t="inlineStr">
+        <is>
+          <t>•  فرفع الحجم 5% يعطي أضعاف ما يعطيه أي خفض ممكن</t>
+        </is>
+      </c>
+      <c r="D16" s="109" t="n"/>
+      <c r="E16" s="109" t="n"/>
+      <c r="F16" s="109" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="109" t="n"/>
+      <c r="B17" s="109" t="n"/>
+      <c r="C17" s="109" t="n"/>
+      <c r="D17" s="109" t="n"/>
+      <c r="E17" s="109" t="n"/>
+      <c r="F17" s="109" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="107">
+      <c r="A18" s="109" t="n"/>
+      <c r="B18" s="128" t="inlineStr">
+        <is>
+          <t>الديزل يسحب الهامش</t>
+        </is>
+      </c>
+      <c r="C18" s="109" t="n"/>
+      <c r="D18" s="109" t="n"/>
+      <c r="E18" s="109" t="n"/>
+      <c r="F18" s="109" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="107">
+      <c r="A19" s="109" t="n"/>
+      <c r="B19" s="109" t="n"/>
+      <c r="C19" s="129" t="inlineStr">
+        <is>
+          <t>•  العمرة ديزلها 28% وهامشها 10.07 هللة</t>
+        </is>
+      </c>
+      <c r="D19" s="109" t="n"/>
+      <c r="E19" s="109" t="n"/>
+      <c r="F19" s="109" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="107">
+      <c r="A20" s="109" t="n"/>
+      <c r="B20" s="109" t="n"/>
+      <c r="C20" s="129" t="inlineStr">
+        <is>
+          <t>•  الشرايع بلا ديزل وهامشها 13.36 هللة</t>
+        </is>
+      </c>
+      <c r="D20" s="109" t="n"/>
+      <c r="E20" s="109" t="n"/>
+      <c r="F20" s="109" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="107">
+      <c r="A21" s="109" t="n"/>
+      <c r="B21" s="109" t="n"/>
+      <c r="C21" s="129" t="inlineStr">
+        <is>
+          <t>•  ورفع حصة البنزين رفع مباشر للهامش لا مجرد زيادة إيراد</t>
+        </is>
+      </c>
+      <c r="D21" s="109" t="n"/>
+      <c r="E21" s="109" t="n"/>
+      <c r="F21" s="109" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="109" t="n"/>
+      <c r="B22" s="109" t="n"/>
+      <c r="C22" s="109" t="n"/>
+      <c r="D22" s="109" t="n"/>
+      <c r="E22" s="109" t="n"/>
+      <c r="F22" s="109" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="107">
+      <c r="A23" s="109" t="n"/>
+      <c r="B23" s="117" t="inlineStr">
+        <is>
+          <t>التأجير رافعة الربح</t>
+        </is>
+      </c>
+      <c r="C23" s="109" t="n"/>
+      <c r="D23" s="109" t="n"/>
+      <c r="E23" s="109" t="n"/>
+      <c r="F23" s="109" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="107">
+      <c r="A24" s="109" t="n"/>
+      <c r="B24" s="109" t="n"/>
+      <c r="C24" s="129" t="inlineStr">
+        <is>
+          <t>•  التمويل وإهلاك حق الاستخدام ثابتان ومدفوعان</t>
+        </is>
+      </c>
+      <c r="D24" s="109" t="n"/>
+      <c r="E24" s="109" t="n"/>
+      <c r="F24" s="109" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="107">
+      <c r="A25" s="109" t="n"/>
+      <c r="B25" s="109" t="n"/>
+      <c r="C25" s="129" t="inlineStr">
+        <is>
+          <t>•  يلتهمان 63% من دخل الإيجار في العمرة و106% في الشرايع</t>
+        </is>
+      </c>
+      <c r="D25" s="109" t="n"/>
+      <c r="E25" s="109" t="n"/>
+      <c r="F25" s="109" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="107">
+      <c r="A26" s="109" t="n"/>
+      <c r="B26" s="109" t="n"/>
+      <c r="C26" s="129" t="inlineStr">
+        <is>
+          <t>•  فكل إيجار إضافي ربح شبه صافٍ</t>
+        </is>
+      </c>
+      <c r="D26" s="109" t="n"/>
+      <c r="E26" s="109" t="n"/>
+      <c r="F26" s="109" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C14:F14"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -2720,7 +3181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3460,7 +3921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5310,7 +5771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5738,7 +6199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6960,7 +7421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9705,7 +10166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14359,6 +14820,839 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="106" min="1" max="1"/>
+    <col width="26" customWidth="1" style="106" min="2" max="2"/>
+    <col width="16" customWidth="1" style="106" min="3" max="6"/>
+    <col width="38" customWidth="1" style="106" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="107">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>الوقود — قناة الشركات</t>
+        </is>
+      </c>
+      <c r="B1" s="109" t="n"/>
+      <c r="C1" s="109" t="n"/>
+      <c r="D1" s="109" t="n"/>
+      <c r="E1" s="109" t="n"/>
+      <c r="F1" s="109" t="n"/>
+      <c r="G1" s="109" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="107">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>المنافس: بترو آب وواعي والمنصات · السلاح: مندوب أساطيل + خصم هللة + الاشتراك في كل منصة</t>
+        </is>
+      </c>
+      <c r="B2" s="109" t="n"/>
+      <c r="C2" s="109" t="n"/>
+      <c r="D2" s="109" t="n"/>
+      <c r="E2" s="109" t="n"/>
+      <c r="F2" s="109" t="n"/>
+      <c r="G2" s="109" t="n"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="107">
+      <c r="A3" s="142" t="inlineStr">
+        <is>
+          <t>الخطة</t>
+        </is>
+      </c>
+      <c r="B3" s="143" t="n"/>
+      <c r="C3" s="143" t="n"/>
+      <c r="D3" s="143" t="n"/>
+      <c r="E3" s="143" t="n"/>
+      <c r="F3" s="143" t="n"/>
+      <c r="G3" s="143" t="n"/>
+    </row>
+    <row r="4" ht="27.75" customHeight="1" s="107">
+      <c r="A4" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="113" t="inlineStr">
+        <is>
+          <t>تعيين مندوب أساطيل</t>
+        </is>
+      </c>
+      <c r="C4" s="114" t="inlineStr">
+        <is>
+          <t>حج وعمرة أولاً</t>
+        </is>
+      </c>
+      <c r="D4" s="114" t="inlineStr">
+        <is>
+          <t>حصر الشركات والمكاتب والمشغّلين</t>
+        </is>
+      </c>
+      <c r="E4" s="114" t="inlineStr">
+        <is>
+          <t>قائمة أساطيل مستهدفة بأرقام مركبات</t>
+        </is>
+      </c>
+      <c r="F4" s="114" t="n"/>
+      <c r="G4" s="114" t="inlineStr">
+        <is>
+          <t>الأساطيل موجودة في محطاتنا اليوم بلا عقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27.75" customHeight="1" s="107">
+      <c r="A5" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="113" t="inlineStr">
+        <is>
+          <t>خصم هللة لكل لتر</t>
+        </is>
+      </c>
+      <c r="C5" s="114" t="inlineStr">
+        <is>
+          <t>أداة التعاقد</t>
+        </is>
+      </c>
+      <c r="D5" s="114" t="inlineStr">
+        <is>
+          <t>سعر تفضيلي مقابل التزام حجم</t>
+        </is>
+      </c>
+      <c r="E5" s="114" t="inlineStr">
+        <is>
+          <t>عقد سنوي بحد أدنى شهري</t>
+        </is>
+      </c>
+      <c r="F5" s="114" t="n"/>
+      <c r="G5" s="114" t="inlineStr">
+        <is>
+          <t>الاقتصاديات في الجدول أدناه</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27.75" customHeight="1" s="107">
+      <c r="A6" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="113" t="inlineStr">
+        <is>
+          <t>الرفع على سيارة آب</t>
+        </is>
+      </c>
+      <c r="C6" s="114" t="inlineStr">
+        <is>
+          <t>الشراكة القائمة</t>
+        </is>
+      </c>
+      <c r="D6" s="114" t="inlineStr">
+        <is>
+          <t>إدراج أساطيلنا على المنصة</t>
+        </is>
+      </c>
+      <c r="E6" s="114" t="inlineStr">
+        <is>
+          <t>استفادة من شبكتها 2,500 محطة</t>
+        </is>
+      </c>
+      <c r="F6" s="114" t="n"/>
+      <c r="G6" s="114" t="inlineStr">
+        <is>
+          <t>شراكة قائمة — أسرع مسار</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27.75" customHeight="1" s="107">
+      <c r="A7" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="113" t="inlineStr">
+        <is>
+          <t>الاشتراك في كل منصة</t>
+        </is>
+      </c>
+      <c r="C7" s="114" t="inlineStr">
+        <is>
+          <t>بترو آب · Fleet Plus</t>
+        </is>
+      </c>
+      <c r="D7" s="114" t="inlineStr">
+        <is>
+          <t>نقطة قبول في شبكاتها</t>
+        </is>
+      </c>
+      <c r="E7" s="114" t="inlineStr">
+        <is>
+          <t>حجم فوري مقابل عمولة</t>
+        </is>
+      </c>
+      <c r="F7" s="114" t="n"/>
+      <c r="G7" s="114" t="inlineStr">
+        <is>
+          <t>500 ألف مركبة و10 آلاف منشأة خارج شبكتنا</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="109" t="n"/>
+      <c r="B8" s="109" t="n"/>
+      <c r="C8" s="109" t="n"/>
+      <c r="D8" s="109" t="n"/>
+      <c r="E8" s="109" t="n"/>
+      <c r="F8" s="109" t="n"/>
+      <c r="G8" s="109" t="n"/>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="107">
+      <c r="A9" s="142" t="inlineStr">
+        <is>
+          <t>اقتصاديات خصم الهللة</t>
+        </is>
+      </c>
+      <c r="B9" s="143" t="n"/>
+      <c r="C9" s="143" t="n"/>
+      <c r="D9" s="143" t="n"/>
+      <c r="E9" s="143" t="n"/>
+      <c r="F9" s="143" t="n"/>
+      <c r="G9" s="143" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="107">
+      <c r="A10" s="109" t="n"/>
+      <c r="B10" s="144" t="inlineStr">
+        <is>
+          <t>هامش المساهمة قبل الخصم (هللة)</t>
+        </is>
+      </c>
+      <c r="C10" s="183" t="n"/>
+      <c r="D10" s="109" t="n"/>
+      <c r="E10" s="109" t="n"/>
+      <c r="F10" s="109" t="n"/>
+      <c r="G10" s="109" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="107">
+      <c r="A11" s="109" t="n"/>
+      <c r="B11" s="144" t="inlineStr">
+        <is>
+          <t>الخصم الممنوح (هللة)</t>
+        </is>
+      </c>
+      <c r="C11" s="183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="109" t="n"/>
+      <c r="E11" s="109" t="n"/>
+      <c r="F11" s="109" t="n"/>
+      <c r="G11" s="109" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="107">
+      <c r="A12" s="109" t="n"/>
+      <c r="B12" s="144" t="inlineStr">
+        <is>
+          <t>اللترات المتعاقدة المستهدفة (سنوياً)</t>
+        </is>
+      </c>
+      <c r="C12" s="185" t="n"/>
+      <c r="D12" s="109" t="n"/>
+      <c r="E12" s="109" t="n"/>
+      <c r="F12" s="109" t="n"/>
+      <c r="G12" s="109" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="107">
+      <c r="A13" s="111" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B13" s="111" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="C13" s="111" t="inlineStr">
+        <is>
+          <t>القيمة</t>
+        </is>
+      </c>
+      <c r="D13" s="111" t="n"/>
+      <c r="E13" s="111" t="n"/>
+      <c r="F13" s="111" t="n"/>
+      <c r="G13" s="111" t="inlineStr">
+        <is>
+          <t>الدلالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" s="107">
+      <c r="A14" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="148" t="inlineStr">
+        <is>
+          <t>الهامش بعد الخصم (هللة)</t>
+        </is>
+      </c>
+      <c r="C14" s="155">
+        <f>C10-C11</f>
+        <v/>
+      </c>
+      <c r="D14" s="112" t="n"/>
+      <c r="E14" s="112" t="n"/>
+      <c r="F14" s="112" t="n"/>
+      <c r="G14" s="114" t="inlineStr">
+        <is>
+          <t>ما يتبقى لنا لكل لتر</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1" s="107">
+      <c r="A15" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="148" t="inlineStr">
+        <is>
+          <t>نسبة التنازل من الهامش</t>
+        </is>
+      </c>
+      <c r="C15" s="156">
+        <f>IFERROR(C11/C10,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="112" t="n"/>
+      <c r="E15" s="112" t="n"/>
+      <c r="F15" s="112" t="n"/>
+      <c r="G15" s="114" t="inlineStr">
+        <is>
+          <t>كلفة اكتساب العقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" s="107">
+      <c r="A16" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="148" t="inlineStr">
+        <is>
+          <t>هامش اللترات المتعاقدة (ريال/سنة)</t>
+        </is>
+      </c>
+      <c r="C16" s="149">
+        <f>C12*(C10-C11)/100</f>
+        <v/>
+      </c>
+      <c r="D16" s="112" t="n"/>
+      <c r="E16" s="112" t="n"/>
+      <c r="F16" s="112" t="n"/>
+      <c r="G16" s="114" t="inlineStr">
+        <is>
+          <t>الربح من الحجم المتعاقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" s="107">
+      <c r="A17" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="148" t="inlineStr">
+        <is>
+          <t>قيمة الخصم الممنوح (ريال/سنة)</t>
+        </is>
+      </c>
+      <c r="C17" s="149">
+        <f>C12*C11/100</f>
+        <v/>
+      </c>
+      <c r="D17" s="112" t="n"/>
+      <c r="E17" s="112" t="n"/>
+      <c r="F17" s="112" t="n"/>
+      <c r="G17" s="114" t="inlineStr">
+        <is>
+          <t>ما تنازلنا عنه</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" s="107">
+      <c r="A18" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="148" t="inlineStr">
+        <is>
+          <t>نقطة التعادل — لتر إضافي مطلوب</t>
+        </is>
+      </c>
+      <c r="C18" s="157">
+        <f>IFERROR(C12*C11/(C10-C11),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="112" t="n"/>
+      <c r="E18" s="112" t="n"/>
+      <c r="F18" s="112" t="n"/>
+      <c r="G18" s="114" t="inlineStr">
+        <is>
+          <t>الحجم الإضافي الذي يعوّض الخصم</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1" s="107">
+      <c r="A19" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="148" t="inlineStr">
+        <is>
+          <t>نسبة النمو المطلوبة للتعادل</t>
+        </is>
+      </c>
+      <c r="C19" s="158">
+        <f>IFERROR(C11/(C10-C11),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="112" t="n"/>
+      <c r="E19" s="112" t="n"/>
+      <c r="F19" s="112" t="n"/>
+      <c r="G19" s="114" t="inlineStr">
+        <is>
+          <t>إن تحقق أقل منها فالخصم خاسر</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="109" t="n"/>
+      <c r="B20" s="109" t="n"/>
+      <c r="C20" s="109" t="n"/>
+      <c r="D20" s="109" t="n"/>
+      <c r="E20" s="109" t="n"/>
+      <c r="F20" s="109" t="n"/>
+      <c r="G20" s="109" t="n"/>
+    </row>
+    <row r="21" ht="21.75" customHeight="1" s="107">
+      <c r="A21" s="142" t="inlineStr">
+        <is>
+          <t>السوق المتاح — بصمة الأسطول في بياناتنا</t>
+        </is>
+      </c>
+      <c r="B21" s="143" t="n"/>
+      <c r="C21" s="143" t="n"/>
+      <c r="D21" s="143" t="n"/>
+      <c r="E21" s="143" t="n"/>
+      <c r="F21" s="143" t="n"/>
+      <c r="G21" s="143" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="107">
+      <c r="A22" s="111" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B22" s="111" t="inlineStr">
+        <is>
+          <t>المحطة</t>
+        </is>
+      </c>
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>حصة الديزل</t>
+        </is>
+      </c>
+      <c r="D22" s="111" t="inlineStr">
+        <is>
+          <t>ديزل سنوي (لتر)</t>
+        </is>
+      </c>
+      <c r="E22" s="111" t="inlineStr">
+        <is>
+          <t>لتر/زيارة</t>
+        </is>
+      </c>
+      <c r="F22" s="111" t="n"/>
+      <c r="G22" s="111" t="inlineStr">
+        <is>
+          <t>القراءة</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="107">
+      <c r="A23" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="148" t="inlineStr">
+        <is>
+          <t>MK289 طريق الليث - الفضيلة</t>
+        </is>
+      </c>
+      <c r="C23" s="156" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="D23" s="149" t="n">
+        <v>19344811</v>
+      </c>
+      <c r="E23" s="159" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="F23" s="112" t="n"/>
+      <c r="G23" s="114" t="inlineStr">
+        <is>
+          <t>أرقام أسطول لا أفراد</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="107">
+      <c r="A24" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="148" t="inlineStr">
+        <is>
+          <t>MK014 خليص</t>
+        </is>
+      </c>
+      <c r="C24" s="156" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="D24" s="149" t="n">
+        <v>4805625</v>
+      </c>
+      <c r="E24" s="159" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="F24" s="112" t="n"/>
+      <c r="G24" s="114" t="inlineStr">
+        <is>
+          <t>أرقام أسطول لا أفراد</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="107">
+      <c r="A25" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="148" t="inlineStr">
+        <is>
+          <t>MK033 أبو وافي العمرة</t>
+        </is>
+      </c>
+      <c r="C25" s="156" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="D25" s="149" t="n">
+        <v>7210207</v>
+      </c>
+      <c r="E25" s="159" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="F25" s="112" t="n"/>
+      <c r="G25" s="114" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="107">
+      <c r="A26" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="148" t="inlineStr">
+        <is>
+          <t>QS055 الدائري الشرقي</t>
+        </is>
+      </c>
+      <c r="C26" s="156" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="D26" s="149" t="n">
+        <v>2324712</v>
+      </c>
+      <c r="E26" s="159" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="F26" s="112" t="n"/>
+      <c r="G26" s="114" t="inlineStr">
+        <is>
+          <t>أرقام أسطول لا أفراد</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="107">
+      <c r="A27" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="148" t="inlineStr">
+        <is>
+          <t>JA061 طريق صبيا</t>
+        </is>
+      </c>
+      <c r="C27" s="156" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="D27" s="149" t="n">
+        <v>2493275</v>
+      </c>
+      <c r="E27" s="159" t="n">
+        <v>34</v>
+      </c>
+      <c r="F27" s="112" t="n"/>
+      <c r="G27" s="114" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="107">
+      <c r="A28" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="148" t="inlineStr">
+        <is>
+          <t>MK054 طريق السيل</t>
+        </is>
+      </c>
+      <c r="C28" s="156" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="D28" s="149" t="n">
+        <v>3252431</v>
+      </c>
+      <c r="E28" s="159" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F28" s="112" t="n"/>
+      <c r="G28" s="114" t="inlineStr">
+        <is>
+          <t>أرقام أسطول لا أفراد</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="107">
+      <c r="A29" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="148" t="inlineStr">
+        <is>
+          <t>MK004 عاصفة الصحراء</t>
+        </is>
+      </c>
+      <c r="C29" s="156" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="D29" s="149" t="n">
+        <v>10303487</v>
+      </c>
+      <c r="E29" s="159" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F29" s="112" t="n"/>
+      <c r="G29" s="114" t="inlineStr">
+        <is>
+          <t>أرقام أسطول لا أفراد</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="107">
+      <c r="A30" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="148" t="inlineStr">
+        <is>
+          <t>MK210 الفلاح - فلسطين</t>
+        </is>
+      </c>
+      <c r="C30" s="156" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="D30" s="149" t="n">
+        <v>3857753</v>
+      </c>
+      <c r="E30" s="159" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F30" s="112" t="n"/>
+      <c r="G30" s="114" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="109" t="n"/>
+      <c r="B31" s="109" t="n"/>
+      <c r="C31" s="109" t="n"/>
+      <c r="D31" s="109" t="n"/>
+      <c r="E31" s="109" t="n"/>
+      <c r="F31" s="109" t="n"/>
+      <c r="G31" s="109" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="107">
+      <c r="A32" s="109" t="n"/>
+      <c r="B32" s="128" t="inlineStr">
+        <is>
+          <t>حجم الفرصة</t>
+        </is>
+      </c>
+      <c r="C32" s="109" t="n"/>
+      <c r="D32" s="109" t="n"/>
+      <c r="E32" s="109" t="n"/>
+      <c r="F32" s="109" t="n"/>
+      <c r="G32" s="109" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="107">
+      <c r="A33" s="109" t="n"/>
+      <c r="B33" s="109" t="n"/>
+      <c r="C33" s="129" t="inlineStr">
+        <is>
+          <t>•  الديزل 109.4 مليون لتر سنوياً — وهو سوق الأساطيل المتاح داخل شبكتنا</t>
+        </is>
+      </c>
+      <c r="D33" s="109" t="n"/>
+      <c r="E33" s="109" t="n"/>
+      <c r="F33" s="109" t="n"/>
+      <c r="G33" s="109" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="107">
+      <c r="A34" s="109" t="n"/>
+      <c r="B34" s="109" t="n"/>
+      <c r="C34" s="129" t="inlineStr">
+        <is>
+          <t>•  MK289 ديزلها 64% و43.7 لتر لكل زيارة — أرقام أسطول لا أفراد</t>
+        </is>
+      </c>
+      <c r="D34" s="109" t="n"/>
+      <c r="E34" s="109" t="n"/>
+      <c r="F34" s="109" t="n"/>
+      <c r="G34" s="109" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="107">
+      <c r="A35" s="109" t="n"/>
+      <c r="B35" s="109" t="n"/>
+      <c r="C35" s="129" t="inlineStr">
+        <is>
+          <t>•  الحجم يمرّ عندنا اليوم بلا عقد — فالتعاقد تثبيت لا اكتساب</t>
+        </is>
+      </c>
+      <c r="D35" s="109" t="n"/>
+      <c r="E35" s="109" t="n"/>
+      <c r="F35" s="109" t="n"/>
+      <c r="G35" s="109" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="109" t="n"/>
+      <c r="B36" s="109" t="n"/>
+      <c r="C36" s="109" t="n"/>
+      <c r="D36" s="109" t="n"/>
+      <c r="E36" s="109" t="n"/>
+      <c r="F36" s="109" t="n"/>
+      <c r="G36" s="109" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="107">
+      <c r="A37" s="109" t="n"/>
+      <c r="B37" s="128" t="inlineStr">
+        <is>
+          <t>لماذا المساران معاً</t>
+        </is>
+      </c>
+      <c r="C37" s="109" t="n"/>
+      <c r="D37" s="109" t="n"/>
+      <c r="E37" s="109" t="n"/>
+      <c r="F37" s="109" t="n"/>
+      <c r="G37" s="109" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="107">
+      <c r="A38" s="109" t="n"/>
+      <c r="B38" s="109" t="n"/>
+      <c r="C38" s="129" t="inlineStr">
+        <is>
+          <t>•  المندوب يصل إلى أساطيل الحج والعمرة مباشرة — عقد وبيانات وهامش كامل</t>
+        </is>
+      </c>
+      <c r="D38" s="109" t="n"/>
+      <c r="E38" s="109" t="n"/>
+      <c r="F38" s="109" t="n"/>
+      <c r="G38" s="109" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="107">
+      <c r="A39" s="109" t="n"/>
+      <c r="B39" s="109" t="n"/>
+      <c r="C39" s="129" t="inlineStr">
+        <is>
+          <t>•  والمنصات تلتقط ما لا يصله المندوب مقابل عمولة</t>
+        </is>
+      </c>
+      <c r="D39" s="109" t="n"/>
+      <c r="E39" s="109" t="n"/>
+      <c r="F39" s="109" t="n"/>
+      <c r="G39" s="109" t="n"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="107">
+      <c r="A40" s="109" t="n"/>
+      <c r="B40" s="109" t="n"/>
+      <c r="C40" s="129" t="inlineStr">
+        <is>
+          <t>•  المعيار: عمولة المنصة لكل لتر مقابل تكلفة المندوب لكل لتر — يُراجع كل ربع</t>
+        </is>
+      </c>
+      <c r="D40" s="109" t="n"/>
+      <c r="E40" s="109" t="n"/>
+      <c r="F40" s="109" t="n"/>
+      <c r="G40" s="109" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="109" t="n"/>
+      <c r="B41" s="109" t="n"/>
+      <c r="C41" s="109" t="n"/>
+      <c r="D41" s="109" t="n"/>
+      <c r="E41" s="109" t="n"/>
+      <c r="F41" s="109" t="n"/>
+      <c r="G41" s="109" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="107">
+      <c r="A42" s="109" t="n"/>
+      <c r="B42" s="117" t="inlineStr">
+        <is>
+          <t>شرط التنفيذ</t>
+        </is>
+      </c>
+      <c r="C42" s="109" t="n"/>
+      <c r="D42" s="109" t="n"/>
+      <c r="E42" s="109" t="n"/>
+      <c r="F42" s="109" t="n"/>
+      <c r="G42" s="109" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="107">
+      <c r="A43" s="109" t="n"/>
+      <c r="B43" s="109" t="n"/>
+      <c r="C43" s="129" t="inlineStr">
+        <is>
+          <t>•  آلية ائتمان وفوترة قبل أول عقد — لا يمكن بيع الأسطول نقداً</t>
+        </is>
+      </c>
+      <c r="D43" s="109" t="n"/>
+      <c r="E43" s="109" t="n"/>
+      <c r="F43" s="109" t="n"/>
+      <c r="G43" s="109" t="n"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="107">
+      <c r="A44" s="109" t="n"/>
+      <c r="B44" s="109" t="n"/>
+      <c r="C44" s="129" t="inlineStr">
+        <is>
+          <t>•  تعريف الحد الأدنى للحجم الذي يستحق الخصم</t>
+        </is>
+      </c>
+      <c r="D44" s="109" t="n"/>
+      <c r="E44" s="109" t="n"/>
+      <c r="F44" s="109" t="n"/>
+      <c r="G44" s="109" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -14782,7 +16076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15705,839 +16999,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:G44"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="4" customWidth="1" style="106" min="1" max="1"/>
-    <col width="26" customWidth="1" style="106" min="2" max="2"/>
-    <col width="16" customWidth="1" style="106" min="3" max="6"/>
-    <col width="38" customWidth="1" style="106" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="118" t="inlineStr">
-        <is>
-          <t>الوقود — قناة الشركات</t>
-        </is>
-      </c>
-      <c r="B1" s="109" t="n"/>
-      <c r="C1" s="109" t="n"/>
-      <c r="D1" s="109" t="n"/>
-      <c r="E1" s="109" t="n"/>
-      <c r="F1" s="109" t="n"/>
-      <c r="G1" s="109" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="119" t="inlineStr">
-        <is>
-          <t>المنافس: بترو آب وواعي والمنصات · السلاح: مندوب أساطيل + خصم هللة + الاشتراك في كل منصة</t>
-        </is>
-      </c>
-      <c r="B2" s="109" t="n"/>
-      <c r="C2" s="109" t="n"/>
-      <c r="D2" s="109" t="n"/>
-      <c r="E2" s="109" t="n"/>
-      <c r="F2" s="109" t="n"/>
-      <c r="G2" s="109" t="n"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" s="107">
-      <c r="A3" s="142" t="inlineStr">
-        <is>
-          <t>الخطة</t>
-        </is>
-      </c>
-      <c r="B3" s="143" t="n"/>
-      <c r="C3" s="143" t="n"/>
-      <c r="D3" s="143" t="n"/>
-      <c r="E3" s="143" t="n"/>
-      <c r="F3" s="143" t="n"/>
-      <c r="G3" s="143" t="n"/>
-    </row>
-    <row r="4" ht="27.75" customHeight="1" s="107">
-      <c r="A4" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="113" t="inlineStr">
-        <is>
-          <t>تعيين مندوب أساطيل</t>
-        </is>
-      </c>
-      <c r="C4" s="114" t="inlineStr">
-        <is>
-          <t>حج وعمرة أولاً</t>
-        </is>
-      </c>
-      <c r="D4" s="114" t="inlineStr">
-        <is>
-          <t>حصر الشركات والمكاتب والمشغّلين</t>
-        </is>
-      </c>
-      <c r="E4" s="114" t="inlineStr">
-        <is>
-          <t>قائمة أساطيل مستهدفة بأرقام مركبات</t>
-        </is>
-      </c>
-      <c r="F4" s="114" t="n"/>
-      <c r="G4" s="114" t="inlineStr">
-        <is>
-          <t>الأساطيل موجودة في محطاتنا اليوم بلا عقد</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="27.75" customHeight="1" s="107">
-      <c r="A5" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="113" t="inlineStr">
-        <is>
-          <t>خصم هللة لكل لتر</t>
-        </is>
-      </c>
-      <c r="C5" s="114" t="inlineStr">
-        <is>
-          <t>أداة التعاقد</t>
-        </is>
-      </c>
-      <c r="D5" s="114" t="inlineStr">
-        <is>
-          <t>سعر تفضيلي مقابل التزام حجم</t>
-        </is>
-      </c>
-      <c r="E5" s="114" t="inlineStr">
-        <is>
-          <t>عقد سنوي بحد أدنى شهري</t>
-        </is>
-      </c>
-      <c r="F5" s="114" t="n"/>
-      <c r="G5" s="114" t="inlineStr">
-        <is>
-          <t>الاقتصاديات في الجدول أدناه</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="27.75" customHeight="1" s="107">
-      <c r="A6" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="113" t="inlineStr">
-        <is>
-          <t>الرفع على سيارة آب</t>
-        </is>
-      </c>
-      <c r="C6" s="114" t="inlineStr">
-        <is>
-          <t>الشراكة القائمة</t>
-        </is>
-      </c>
-      <c r="D6" s="114" t="inlineStr">
-        <is>
-          <t>إدراج أساطيلنا على المنصة</t>
-        </is>
-      </c>
-      <c r="E6" s="114" t="inlineStr">
-        <is>
-          <t>استفادة من شبكتها 2,500 محطة</t>
-        </is>
-      </c>
-      <c r="F6" s="114" t="n"/>
-      <c r="G6" s="114" t="inlineStr">
-        <is>
-          <t>شراكة قائمة — أسرع مسار</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27.75" customHeight="1" s="107">
-      <c r="A7" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="113" t="inlineStr">
-        <is>
-          <t>الاشتراك في كل منصة</t>
-        </is>
-      </c>
-      <c r="C7" s="114" t="inlineStr">
-        <is>
-          <t>بترو آب · Fleet Plus</t>
-        </is>
-      </c>
-      <c r="D7" s="114" t="inlineStr">
-        <is>
-          <t>نقطة قبول في شبكاتها</t>
-        </is>
-      </c>
-      <c r="E7" s="114" t="inlineStr">
-        <is>
-          <t>حجم فوري مقابل عمولة</t>
-        </is>
-      </c>
-      <c r="F7" s="114" t="n"/>
-      <c r="G7" s="114" t="inlineStr">
-        <is>
-          <t>500 ألف مركبة و10 آلاف منشأة خارج شبكتنا</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="109" t="n"/>
-      <c r="B8" s="109" t="n"/>
-      <c r="C8" s="109" t="n"/>
-      <c r="D8" s="109" t="n"/>
-      <c r="E8" s="109" t="n"/>
-      <c r="F8" s="109" t="n"/>
-      <c r="G8" s="109" t="n"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="107">
-      <c r="A9" s="142" t="inlineStr">
-        <is>
-          <t>اقتصاديات خصم الهللة</t>
-        </is>
-      </c>
-      <c r="B9" s="143" t="n"/>
-      <c r="C9" s="143" t="n"/>
-      <c r="D9" s="143" t="n"/>
-      <c r="E9" s="143" t="n"/>
-      <c r="F9" s="143" t="n"/>
-      <c r="G9" s="143" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="107">
-      <c r="A10" s="109" t="n"/>
-      <c r="B10" s="144" t="inlineStr">
-        <is>
-          <t>هامش المساهمة قبل الخصم (هللة)</t>
-        </is>
-      </c>
-      <c r="C10" s="183" t="n"/>
-      <c r="D10" s="109" t="n"/>
-      <c r="E10" s="109" t="n"/>
-      <c r="F10" s="109" t="n"/>
-      <c r="G10" s="109" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="107">
-      <c r="A11" s="109" t="n"/>
-      <c r="B11" s="144" t="inlineStr">
-        <is>
-          <t>الخصم الممنوح (هللة)</t>
-        </is>
-      </c>
-      <c r="C11" s="183" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="109" t="n"/>
-      <c r="E11" s="109" t="n"/>
-      <c r="F11" s="109" t="n"/>
-      <c r="G11" s="109" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="107">
-      <c r="A12" s="109" t="n"/>
-      <c r="B12" s="144" t="inlineStr">
-        <is>
-          <t>اللترات المتعاقدة المستهدفة (سنوياً)</t>
-        </is>
-      </c>
-      <c r="C12" s="185" t="n"/>
-      <c r="D12" s="109" t="n"/>
-      <c r="E12" s="109" t="n"/>
-      <c r="F12" s="109" t="n"/>
-      <c r="G12" s="109" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="107">
-      <c r="A13" s="111" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B13" s="111" t="inlineStr">
-        <is>
-          <t>البند</t>
-        </is>
-      </c>
-      <c r="C13" s="111" t="inlineStr">
-        <is>
-          <t>القيمة</t>
-        </is>
-      </c>
-      <c r="D13" s="111" t="n"/>
-      <c r="E13" s="111" t="n"/>
-      <c r="F13" s="111" t="n"/>
-      <c r="G13" s="111" t="inlineStr">
-        <is>
-          <t>الدلالة</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1" s="107">
-      <c r="A14" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="148" t="inlineStr">
-        <is>
-          <t>الهامش بعد الخصم (هللة)</t>
-        </is>
-      </c>
-      <c r="C14" s="155">
-        <f>C10-C11</f>
-        <v/>
-      </c>
-      <c r="D14" s="112" t="n"/>
-      <c r="E14" s="112" t="n"/>
-      <c r="F14" s="112" t="n"/>
-      <c r="G14" s="114" t="inlineStr">
-        <is>
-          <t>ما يتبقى لنا لكل لتر</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1" s="107">
-      <c r="A15" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="148" t="inlineStr">
-        <is>
-          <t>نسبة التنازل من الهامش</t>
-        </is>
-      </c>
-      <c r="C15" s="156">
-        <f>IFERROR(C11/C10,"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="112" t="n"/>
-      <c r="E15" s="112" t="n"/>
-      <c r="F15" s="112" t="n"/>
-      <c r="G15" s="114" t="inlineStr">
-        <is>
-          <t>كلفة اكتساب العقد</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1" s="107">
-      <c r="A16" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="148" t="inlineStr">
-        <is>
-          <t>هامش اللترات المتعاقدة (ريال/سنة)</t>
-        </is>
-      </c>
-      <c r="C16" s="149">
-        <f>C12*(C10-C11)/100</f>
-        <v/>
-      </c>
-      <c r="D16" s="112" t="n"/>
-      <c r="E16" s="112" t="n"/>
-      <c r="F16" s="112" t="n"/>
-      <c r="G16" s="114" t="inlineStr">
-        <is>
-          <t>الربح من الحجم المتعاقد</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1" s="107">
-      <c r="A17" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="148" t="inlineStr">
-        <is>
-          <t>قيمة الخصم الممنوح (ريال/سنة)</t>
-        </is>
-      </c>
-      <c r="C17" s="149">
-        <f>C12*C11/100</f>
-        <v/>
-      </c>
-      <c r="D17" s="112" t="n"/>
-      <c r="E17" s="112" t="n"/>
-      <c r="F17" s="112" t="n"/>
-      <c r="G17" s="114" t="inlineStr">
-        <is>
-          <t>ما تنازلنا عنه</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1" s="107">
-      <c r="A18" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="148" t="inlineStr">
-        <is>
-          <t>نقطة التعادل — لتر إضافي مطلوب</t>
-        </is>
-      </c>
-      <c r="C18" s="157">
-        <f>IFERROR(C12*C11/(C10-C11),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="112" t="n"/>
-      <c r="E18" s="112" t="n"/>
-      <c r="F18" s="112" t="n"/>
-      <c r="G18" s="114" t="inlineStr">
-        <is>
-          <t>الحجم الإضافي الذي يعوّض الخصم</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1" s="107">
-      <c r="A19" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" s="148" t="inlineStr">
-        <is>
-          <t>نسبة النمو المطلوبة للتعادل</t>
-        </is>
-      </c>
-      <c r="C19" s="158">
-        <f>IFERROR(C11/(C10-C11),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="112" t="n"/>
-      <c r="E19" s="112" t="n"/>
-      <c r="F19" s="112" t="n"/>
-      <c r="G19" s="114" t="inlineStr">
-        <is>
-          <t>إن تحقق أقل منها فالخصم خاسر</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="109" t="n"/>
-      <c r="B20" s="109" t="n"/>
-      <c r="C20" s="109" t="n"/>
-      <c r="D20" s="109" t="n"/>
-      <c r="E20" s="109" t="n"/>
-      <c r="F20" s="109" t="n"/>
-      <c r="G20" s="109" t="n"/>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" s="107">
-      <c r="A21" s="142" t="inlineStr">
-        <is>
-          <t>السوق المتاح — بصمة الأسطول في بياناتنا</t>
-        </is>
-      </c>
-      <c r="B21" s="143" t="n"/>
-      <c r="C21" s="143" t="n"/>
-      <c r="D21" s="143" t="n"/>
-      <c r="E21" s="143" t="n"/>
-      <c r="F21" s="143" t="n"/>
-      <c r="G21" s="143" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1" s="107">
-      <c r="A22" s="111" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B22" s="111" t="inlineStr">
-        <is>
-          <t>المحطة</t>
-        </is>
-      </c>
-      <c r="C22" s="111" t="inlineStr">
-        <is>
-          <t>حصة الديزل</t>
-        </is>
-      </c>
-      <c r="D22" s="111" t="inlineStr">
-        <is>
-          <t>ديزل سنوي (لتر)</t>
-        </is>
-      </c>
-      <c r="E22" s="111" t="inlineStr">
-        <is>
-          <t>لتر/زيارة</t>
-        </is>
-      </c>
-      <c r="F22" s="111" t="n"/>
-      <c r="G22" s="111" t="inlineStr">
-        <is>
-          <t>القراءة</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="107">
-      <c r="A23" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="148" t="inlineStr">
-        <is>
-          <t>MK289 طريق الليث - الفضيلة</t>
-        </is>
-      </c>
-      <c r="C23" s="156" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="D23" s="149" t="n">
-        <v>19344811</v>
-      </c>
-      <c r="E23" s="159" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="F23" s="112" t="n"/>
-      <c r="G23" s="114" t="inlineStr">
-        <is>
-          <t>أرقام أسطول لا أفراد</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="107">
-      <c r="A24" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="148" t="inlineStr">
-        <is>
-          <t>MK014 خليص</t>
-        </is>
-      </c>
-      <c r="C24" s="156" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="D24" s="149" t="n">
-        <v>4805625</v>
-      </c>
-      <c r="E24" s="159" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="F24" s="112" t="n"/>
-      <c r="G24" s="114" t="inlineStr">
-        <is>
-          <t>أرقام أسطول لا أفراد</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" s="107">
-      <c r="A25" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="148" t="inlineStr">
-        <is>
-          <t>MK033 أبو وافي العمرة</t>
-        </is>
-      </c>
-      <c r="C25" s="156" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="D25" s="149" t="n">
-        <v>7210207</v>
-      </c>
-      <c r="E25" s="159" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="F25" s="112" t="n"/>
-      <c r="G25" s="114" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" s="107">
-      <c r="A26" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="148" t="inlineStr">
-        <is>
-          <t>QS055 الدائري الشرقي</t>
-        </is>
-      </c>
-      <c r="C26" s="156" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="D26" s="149" t="n">
-        <v>2324712</v>
-      </c>
-      <c r="E26" s="159" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="F26" s="112" t="n"/>
-      <c r="G26" s="114" t="inlineStr">
-        <is>
-          <t>أرقام أسطول لا أفراد</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="107">
-      <c r="A27" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="148" t="inlineStr">
-        <is>
-          <t>JA061 طريق صبيا</t>
-        </is>
-      </c>
-      <c r="C27" s="156" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="D27" s="149" t="n">
-        <v>2493275</v>
-      </c>
-      <c r="E27" s="159" t="n">
-        <v>34</v>
-      </c>
-      <c r="F27" s="112" t="n"/>
-      <c r="G27" s="114" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="107">
-      <c r="A28" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="B28" s="148" t="inlineStr">
-        <is>
-          <t>MK054 طريق السيل</t>
-        </is>
-      </c>
-      <c r="C28" s="156" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="D28" s="149" t="n">
-        <v>3252431</v>
-      </c>
-      <c r="E28" s="159" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F28" s="112" t="n"/>
-      <c r="G28" s="114" t="inlineStr">
-        <is>
-          <t>أرقام أسطول لا أفراد</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1" s="107">
-      <c r="A29" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="B29" s="148" t="inlineStr">
-        <is>
-          <t>MK004 عاصفة الصحراء</t>
-        </is>
-      </c>
-      <c r="C29" s="156" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="D29" s="149" t="n">
-        <v>10303487</v>
-      </c>
-      <c r="E29" s="159" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="F29" s="112" t="n"/>
-      <c r="G29" s="114" t="inlineStr">
-        <is>
-          <t>أرقام أسطول لا أفراد</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" s="107">
-      <c r="A30" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="B30" s="148" t="inlineStr">
-        <is>
-          <t>MK210 الفلاح - فلسطين</t>
-        </is>
-      </c>
-      <c r="C30" s="156" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="D30" s="149" t="n">
-        <v>3857753</v>
-      </c>
-      <c r="E30" s="159" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F30" s="112" t="n"/>
-      <c r="G30" s="114" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="109" t="n"/>
-      <c r="B31" s="109" t="n"/>
-      <c r="C31" s="109" t="n"/>
-      <c r="D31" s="109" t="n"/>
-      <c r="E31" s="109" t="n"/>
-      <c r="F31" s="109" t="n"/>
-      <c r="G31" s="109" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="107">
-      <c r="A32" s="109" t="n"/>
-      <c r="B32" s="128" t="inlineStr">
-        <is>
-          <t>حجم الفرصة</t>
-        </is>
-      </c>
-      <c r="C32" s="109" t="n"/>
-      <c r="D32" s="109" t="n"/>
-      <c r="E32" s="109" t="n"/>
-      <c r="F32" s="109" t="n"/>
-      <c r="G32" s="109" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" s="107">
-      <c r="A33" s="109" t="n"/>
-      <c r="B33" s="109" t="n"/>
-      <c r="C33" s="129" t="inlineStr">
-        <is>
-          <t>•  الديزل 109.4 مليون لتر سنوياً — وهو سوق الأساطيل المتاح داخل شبكتنا</t>
-        </is>
-      </c>
-      <c r="D33" s="109" t="n"/>
-      <c r="E33" s="109" t="n"/>
-      <c r="F33" s="109" t="n"/>
-      <c r="G33" s="109" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" s="107">
-      <c r="A34" s="109" t="n"/>
-      <c r="B34" s="109" t="n"/>
-      <c r="C34" s="129" t="inlineStr">
-        <is>
-          <t>•  MK289 ديزلها 64% و43.7 لتر لكل زيارة — أرقام أسطول لا أفراد</t>
-        </is>
-      </c>
-      <c r="D34" s="109" t="n"/>
-      <c r="E34" s="109" t="n"/>
-      <c r="F34" s="109" t="n"/>
-      <c r="G34" s="109" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" s="107">
-      <c r="A35" s="109" t="n"/>
-      <c r="B35" s="109" t="n"/>
-      <c r="C35" s="129" t="inlineStr">
-        <is>
-          <t>•  الحجم يمرّ عندنا اليوم بلا عقد — فالتعاقد تثبيت لا اكتساب</t>
-        </is>
-      </c>
-      <c r="D35" s="109" t="n"/>
-      <c r="E35" s="109" t="n"/>
-      <c r="F35" s="109" t="n"/>
-      <c r="G35" s="109" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="109" t="n"/>
-      <c r="B36" s="109" t="n"/>
-      <c r="C36" s="109" t="n"/>
-      <c r="D36" s="109" t="n"/>
-      <c r="E36" s="109" t="n"/>
-      <c r="F36" s="109" t="n"/>
-      <c r="G36" s="109" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="107">
-      <c r="A37" s="109" t="n"/>
-      <c r="B37" s="128" t="inlineStr">
-        <is>
-          <t>لماذا المساران معاً</t>
-        </is>
-      </c>
-      <c r="C37" s="109" t="n"/>
-      <c r="D37" s="109" t="n"/>
-      <c r="E37" s="109" t="n"/>
-      <c r="F37" s="109" t="n"/>
-      <c r="G37" s="109" t="n"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" s="107">
-      <c r="A38" s="109" t="n"/>
-      <c r="B38" s="109" t="n"/>
-      <c r="C38" s="129" t="inlineStr">
-        <is>
-          <t>•  المندوب يصل إلى أساطيل الحج والعمرة مباشرة — عقد وبيانات وهامش كامل</t>
-        </is>
-      </c>
-      <c r="D38" s="109" t="n"/>
-      <c r="E38" s="109" t="n"/>
-      <c r="F38" s="109" t="n"/>
-      <c r="G38" s="109" t="n"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" s="107">
-      <c r="A39" s="109" t="n"/>
-      <c r="B39" s="109" t="n"/>
-      <c r="C39" s="129" t="inlineStr">
-        <is>
-          <t>•  والمنصات تلتقط ما لا يصله المندوب مقابل عمولة</t>
-        </is>
-      </c>
-      <c r="D39" s="109" t="n"/>
-      <c r="E39" s="109" t="n"/>
-      <c r="F39" s="109" t="n"/>
-      <c r="G39" s="109" t="n"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" s="107">
-      <c r="A40" s="109" t="n"/>
-      <c r="B40" s="109" t="n"/>
-      <c r="C40" s="129" t="inlineStr">
-        <is>
-          <t>•  المعيار: عمولة المنصة لكل لتر مقابل تكلفة المندوب لكل لتر — يُراجع كل ربع</t>
-        </is>
-      </c>
-      <c r="D40" s="109" t="n"/>
-      <c r="E40" s="109" t="n"/>
-      <c r="F40" s="109" t="n"/>
-      <c r="G40" s="109" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="109" t="n"/>
-      <c r="B41" s="109" t="n"/>
-      <c r="C41" s="109" t="n"/>
-      <c r="D41" s="109" t="n"/>
-      <c r="E41" s="109" t="n"/>
-      <c r="F41" s="109" t="n"/>
-      <c r="G41" s="109" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="107">
-      <c r="A42" s="109" t="n"/>
-      <c r="B42" s="117" t="inlineStr">
-        <is>
-          <t>شرط التنفيذ</t>
-        </is>
-      </c>
-      <c r="C42" s="109" t="n"/>
-      <c r="D42" s="109" t="n"/>
-      <c r="E42" s="109" t="n"/>
-      <c r="F42" s="109" t="n"/>
-      <c r="G42" s="109" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" s="107">
-      <c r="A43" s="109" t="n"/>
-      <c r="B43" s="109" t="n"/>
-      <c r="C43" s="129" t="inlineStr">
-        <is>
-          <t>•  آلية ائتمان وفوترة قبل أول عقد — لا يمكن بيع الأسطول نقداً</t>
-        </is>
-      </c>
-      <c r="D43" s="109" t="n"/>
-      <c r="E43" s="109" t="n"/>
-      <c r="F43" s="109" t="n"/>
-      <c r="G43" s="109" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" s="107">
-      <c r="A44" s="109" t="n"/>
-      <c r="B44" s="109" t="n"/>
-      <c r="C44" s="129" t="inlineStr">
-        <is>
-          <t>•  تعريف الحد الأدنى للحجم الذي يستحق الخصم</t>
-        </is>
-      </c>
-      <c r="D44" s="109" t="n"/>
-      <c r="E44" s="109" t="n"/>
-      <c r="F44" s="109" t="n"/>
-      <c r="G44" s="109" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -17360,6 +17821,1562 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="107" min="1" max="1"/>
+    <col width="20" customWidth="1" style="107" min="2" max="2"/>
+    <col width="10" customWidth="1" style="107" min="3" max="3"/>
+    <col width="11" customWidth="1" style="107" min="4" max="4"/>
+    <col width="11" customWidth="1" style="107" min="5" max="5"/>
+    <col width="11" customWidth="1" style="107" min="6" max="6"/>
+    <col width="11" customWidth="1" style="107" min="7" max="7"/>
+    <col width="11" customWidth="1" style="107" min="8" max="8"/>
+    <col width="11" customWidth="1" style="107" min="9" max="9"/>
+    <col width="11" customWidth="1" style="107" min="10" max="10"/>
+    <col width="40" customWidth="1" style="107" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="107">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>سجل الوحدات التأجيرية — ١٨٦ محطة</t>
+        </is>
+      </c>
+      <c r="B1" s="109" t="n"/>
+      <c r="C1" s="109" t="n"/>
+      <c r="D1" s="109" t="n"/>
+      <c r="E1" s="109" t="n"/>
+      <c r="F1" s="109" t="n"/>
+      <c r="G1" s="109" t="n"/>
+      <c r="H1" s="109" t="n"/>
+      <c r="I1" s="109" t="n"/>
+      <c r="J1" s="109" t="n"/>
+      <c r="K1" s="109" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="107">
+      <c r="A2" s="119" t="inlineStr">
+        <is>
+          <t>من سجل المحطات الرسمي · الوحدة = كشك أو محل أو درايف ثرو أو مغسلة أو سوبرماركت</t>
+        </is>
+      </c>
+      <c r="B2" s="109" t="n"/>
+      <c r="C2" s="109" t="n"/>
+      <c r="D2" s="109" t="n"/>
+      <c r="E2" s="109" t="n"/>
+      <c r="F2" s="109" t="n"/>
+      <c r="G2" s="109" t="n"/>
+      <c r="H2" s="109" t="n"/>
+      <c r="I2" s="109" t="n"/>
+      <c r="J2" s="109" t="n"/>
+      <c r="K2" s="109" t="n"/>
+    </row>
+    <row r="3" ht="3.5" customHeight="1" s="107">
+      <c r="A3" s="214" t="n"/>
+      <c r="B3" s="214" t="n"/>
+      <c r="C3" s="214" t="n"/>
+      <c r="D3" s="214" t="n"/>
+      <c r="E3" s="214" t="n"/>
+      <c r="F3" s="214" t="n"/>
+      <c r="G3" s="214" t="n"/>
+      <c r="H3" s="214" t="n"/>
+      <c r="I3" s="214" t="n"/>
+      <c r="J3" s="214" t="n"/>
+      <c r="K3" s="214" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="107">
+      <c r="A4" s="131" t="inlineStr">
+        <is>
+          <t>① الصورة الكاملة — ثلاث فئات لا واحدة</t>
+        </is>
+      </c>
+      <c r="B4" s="109" t="n"/>
+      <c r="C4" s="109" t="n"/>
+      <c r="D4" s="109" t="n"/>
+      <c r="E4" s="109" t="n"/>
+      <c r="F4" s="109" t="n"/>
+      <c r="G4" s="109" t="n"/>
+      <c r="H4" s="109" t="n"/>
+      <c r="I4" s="109" t="n"/>
+      <c r="J4" s="109" t="n"/>
+      <c r="K4" s="109" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="107">
+      <c r="A5" s="120" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="120" t="inlineStr">
+        <is>
+          <t>الفئة</t>
+        </is>
+      </c>
+      <c r="C5" s="120" t="inlineStr">
+        <is>
+          <t>محطات</t>
+        </is>
+      </c>
+      <c r="D5" s="120" t="inlineStr">
+        <is>
+          <t>الوحدات</t>
+        </is>
+      </c>
+      <c r="E5" s="120" t="inlineStr">
+        <is>
+          <t>المؤجر</t>
+        </is>
+      </c>
+      <c r="F5" s="120" t="inlineStr">
+        <is>
+          <t>المحجوز</t>
+        </is>
+      </c>
+      <c r="G5" s="120" t="inlineStr">
+        <is>
+          <t>الشاغر</t>
+        </is>
+      </c>
+      <c r="H5" s="120" t="inlineStr">
+        <is>
+          <t>الإشغال</t>
+        </is>
+      </c>
+      <c r="I5" s="120" t="inlineStr"/>
+      <c r="J5" s="120" t="inlineStr"/>
+      <c r="K5" s="120" t="inlineStr">
+        <is>
+          <t>القراءة</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="107">
+      <c r="A6" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="122" t="inlineStr">
+        <is>
+          <t>مشغّلة</t>
+        </is>
+      </c>
+      <c r="C6" s="200" t="n">
+        <v>52</v>
+      </c>
+      <c r="D6" s="132" t="n">
+        <v>635</v>
+      </c>
+      <c r="E6" s="132" t="n">
+        <v>501</v>
+      </c>
+      <c r="F6" s="132" t="n">
+        <v>27</v>
+      </c>
+      <c r="G6" s="132" t="n">
+        <v>131</v>
+      </c>
+      <c r="H6" s="133" t="n">
+        <v>0.7889763779527559</v>
+      </c>
+      <c r="I6" s="109" t="n"/>
+      <c r="J6" s="109" t="n"/>
+      <c r="K6" s="224" t="inlineStr">
+        <is>
+          <t>الشبكة العاملة — إشغال صحي ولا أزمة شغور</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="107">
+      <c r="A7" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="122" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="C7" s="200" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" s="132" t="n">
+        <v>790</v>
+      </c>
+      <c r="E7" s="132" t="n">
+        <v>101</v>
+      </c>
+      <c r="F7" s="132" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="132" t="n">
+        <v>689</v>
+      </c>
+      <c r="H7" s="133" t="n">
+        <v>0.1278481012658228</v>
+      </c>
+      <c r="I7" s="109" t="n"/>
+      <c r="J7" s="109" t="n"/>
+      <c r="K7" s="224" t="inlineStr">
+        <is>
+          <t>لم تفتح بعد — الشغور طبيعي، وهنا فرصة التأجير المسبق</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="107">
+      <c r="A8" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="122" t="inlineStr">
+        <is>
+          <t>امتياز</t>
+        </is>
+      </c>
+      <c r="C8" s="200" t="n">
+        <v>91</v>
+      </c>
+      <c r="D8" s="132" t="n">
+        <v>308</v>
+      </c>
+      <c r="E8" s="132" t="n">
+        <v>39</v>
+      </c>
+      <c r="F8" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="132" t="n">
+        <v>269</v>
+      </c>
+      <c r="H8" s="133" t="n">
+        <v>0.1266233766233766</v>
+      </c>
+      <c r="I8" s="109" t="n"/>
+      <c r="J8" s="109" t="n"/>
+      <c r="K8" s="224" t="inlineStr">
+        <is>
+          <t>الأسوأ إشغالاً — ومعظمها محلات لم تُسوَّق</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="194" t="n"/>
+      <c r="B9" s="194" t="inlineStr">
+        <is>
+          <t>المجموع</t>
+        </is>
+      </c>
+      <c r="C9" s="195">
+        <f>SUM(C6:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="195">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="195">
+        <f>SUM(E6:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="195">
+        <f>SUM(F6:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="195">
+        <f>SUM(G6:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="196">
+        <f>IFERROR(E9/D9,"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="194" t="n"/>
+      <c r="J9" s="194" t="n"/>
+      <c r="K9" s="194" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="109" t="n"/>
+      <c r="B10" s="109" t="n"/>
+      <c r="C10" s="109" t="n"/>
+      <c r="D10" s="109" t="n"/>
+      <c r="E10" s="109" t="n"/>
+      <c r="F10" s="109" t="n"/>
+      <c r="G10" s="109" t="n"/>
+      <c r="H10" s="109" t="n"/>
+      <c r="I10" s="109" t="n"/>
+      <c r="J10" s="109" t="n"/>
+      <c r="K10" s="109" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="107">
+      <c r="A11" s="131" t="inlineStr">
+        <is>
+          <t>② أي نوع من الوحدات لا يُؤجَّر</t>
+        </is>
+      </c>
+      <c r="B11" s="109" t="n"/>
+      <c r="C11" s="109" t="n"/>
+      <c r="D11" s="109" t="n"/>
+      <c r="E11" s="109" t="n"/>
+      <c r="F11" s="109" t="n"/>
+      <c r="G11" s="109" t="n"/>
+      <c r="H11" s="109" t="n"/>
+      <c r="I11" s="109" t="n"/>
+      <c r="J11" s="109" t="n"/>
+      <c r="K11" s="109" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="107">
+      <c r="A12" s="120" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="120" t="inlineStr">
+        <is>
+          <t>نوع الوحدة</t>
+        </is>
+      </c>
+      <c r="C12" s="120" t="inlineStr">
+        <is>
+          <t>مشغّلة — العدد</t>
+        </is>
+      </c>
+      <c r="D12" s="120" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ — العدد</t>
+        </is>
+      </c>
+      <c r="E12" s="120" t="inlineStr">
+        <is>
+          <t>امتياز — العدد</t>
+        </is>
+      </c>
+      <c r="F12" s="120" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="G12" s="120" t="inlineStr">
+        <is>
+          <t>المؤجر</t>
+        </is>
+      </c>
+      <c r="H12" s="120" t="inlineStr">
+        <is>
+          <t>الشاغر</t>
+        </is>
+      </c>
+      <c r="I12" s="120" t="inlineStr">
+        <is>
+          <t>الإشغال</t>
+        </is>
+      </c>
+      <c r="J12" s="120" t="inlineStr"/>
+      <c r="K12" s="120" t="inlineStr">
+        <is>
+          <t>الدلالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1" s="107">
+      <c r="A13" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="122" t="inlineStr">
+        <is>
+          <t>كشك</t>
+        </is>
+      </c>
+      <c r="C13" s="132" t="n">
+        <v>180</v>
+      </c>
+      <c r="D13" s="132" t="n">
+        <v>160</v>
+      </c>
+      <c r="E13" s="132" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" s="132" t="n">
+        <v>415</v>
+      </c>
+      <c r="G13" s="132" t="n">
+        <v>201</v>
+      </c>
+      <c r="H13" s="132" t="n">
+        <v>214</v>
+      </c>
+      <c r="I13" s="133" t="n">
+        <v>0.4843373493975904</v>
+      </c>
+      <c r="J13" s="109" t="n"/>
+      <c r="K13" s="224" t="inlineStr">
+        <is>
+          <t>الأعلى إشغالاً في المشغّلة</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1" s="107">
+      <c r="A14" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="122" t="inlineStr">
+        <is>
+          <t>محل</t>
+        </is>
+      </c>
+      <c r="C14" s="132" t="n">
+        <v>196</v>
+      </c>
+      <c r="D14" s="132" t="n">
+        <v>422</v>
+      </c>
+      <c r="E14" s="132" t="n">
+        <v>146</v>
+      </c>
+      <c r="F14" s="132" t="n">
+        <v>764</v>
+      </c>
+      <c r="G14" s="132" t="n">
+        <v>192</v>
+      </c>
+      <c r="H14" s="132" t="n">
+        <v>572</v>
+      </c>
+      <c r="I14" s="133" t="n">
+        <v>0.2513089005235602</v>
+      </c>
+      <c r="J14" s="109" t="n"/>
+      <c r="K14" s="224" t="inlineStr">
+        <is>
+          <t>المنتج العالق — أضعف إشغال في كل الفئات، وهو أكثر الوحدات عدداً</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="107">
+      <c r="A15" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="122" t="inlineStr">
+        <is>
+          <t>درايف ثرو</t>
+        </is>
+      </c>
+      <c r="C15" s="132" t="n">
+        <v>83</v>
+      </c>
+      <c r="D15" s="132" t="n">
+        <v>61</v>
+      </c>
+      <c r="E15" s="132" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="132" t="n">
+        <v>155</v>
+      </c>
+      <c r="G15" s="132" t="n">
+        <v>69</v>
+      </c>
+      <c r="H15" s="132" t="n">
+        <v>86</v>
+      </c>
+      <c r="I15" s="133" t="n">
+        <v>0.4451612903225807</v>
+      </c>
+      <c r="J15" s="109" t="n"/>
+      <c r="K15" s="224" t="inlineStr">
+        <is>
+          <t>عدد محدود وإشغال متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1" s="107">
+      <c r="A16" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="122" t="inlineStr">
+        <is>
+          <t>خدمات سيارات + مغسلة</t>
+        </is>
+      </c>
+      <c r="C16" s="132" t="n">
+        <v>117</v>
+      </c>
+      <c r="D16" s="132" t="n">
+        <v>101</v>
+      </c>
+      <c r="E16" s="132" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" s="132" t="n">
+        <v>266</v>
+      </c>
+      <c r="G16" s="132" t="n">
+        <v>117</v>
+      </c>
+      <c r="H16" s="132" t="n">
+        <v>149</v>
+      </c>
+      <c r="I16" s="133" t="n">
+        <v>0.4398496240601504</v>
+      </c>
+      <c r="J16" s="109" t="n"/>
+      <c r="K16" s="224" t="inlineStr">
+        <is>
+          <t>معيار الافتتاح الإلزامي — الطلب عليه قائم</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1" s="107">
+      <c r="A17" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="122" t="inlineStr">
+        <is>
+          <t>سوبرماركت</t>
+        </is>
+      </c>
+      <c r="C17" s="132" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" s="132" t="n">
+        <v>38</v>
+      </c>
+      <c r="E17" s="132" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="132" t="n">
+        <v>110</v>
+      </c>
+      <c r="G17" s="132" t="n">
+        <v>56</v>
+      </c>
+      <c r="H17" s="132" t="n">
+        <v>54</v>
+      </c>
+      <c r="I17" s="133" t="n">
+        <v>0.509090909090909</v>
+      </c>
+      <c r="J17" s="109" t="n"/>
+      <c r="K17" s="224" t="inlineStr">
+        <is>
+          <t>إشغال جيد حيث تعمل المحطة</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1" s="107">
+      <c r="A18" s="121" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="122" t="inlineStr">
+        <is>
+          <t>مرافق أخرى</t>
+        </is>
+      </c>
+      <c r="C18" s="132" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="132" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="132" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="132" t="n">
+        <v>23</v>
+      </c>
+      <c r="G18" s="132" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="132" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" s="133" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="J18" s="109" t="n"/>
+      <c r="K18" s="224" t="inlineStr">
+        <is>
+          <t>صرافات ومرافق — عدد هامشي</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="109" t="n"/>
+      <c r="B19" s="109" t="n"/>
+      <c r="C19" s="109" t="n"/>
+      <c r="D19" s="109" t="n"/>
+      <c r="E19" s="109" t="n"/>
+      <c r="F19" s="109" t="n"/>
+      <c r="G19" s="109" t="n"/>
+      <c r="H19" s="109" t="n"/>
+      <c r="I19" s="109" t="n"/>
+      <c r="J19" s="109" t="n"/>
+      <c r="K19" s="109" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="107">
+      <c r="A20" s="131" t="inlineStr">
+        <is>
+          <t>③ أكبر الفرص — أعلى المحطات بالوحدات الشاغرة</t>
+        </is>
+      </c>
+      <c r="B20" s="109" t="n"/>
+      <c r="C20" s="109" t="n"/>
+      <c r="D20" s="109" t="n"/>
+      <c r="E20" s="109" t="n"/>
+      <c r="F20" s="109" t="n"/>
+      <c r="G20" s="109" t="n"/>
+      <c r="H20" s="109" t="n"/>
+      <c r="I20" s="109" t="n"/>
+      <c r="J20" s="109" t="n"/>
+      <c r="K20" s="109" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="107">
+      <c r="A21" s="120" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B21" s="120" t="inlineStr">
+        <is>
+          <t>المحطة</t>
+        </is>
+      </c>
+      <c r="C21" s="120" t="inlineStr">
+        <is>
+          <t>الكود</t>
+        </is>
+      </c>
+      <c r="D21" s="120" t="inlineStr">
+        <is>
+          <t>المدينة</t>
+        </is>
+      </c>
+      <c r="E21" s="120" t="inlineStr">
+        <is>
+          <t>الفئة</t>
+        </is>
+      </c>
+      <c r="F21" s="120" t="inlineStr">
+        <is>
+          <t>التعاقد</t>
+        </is>
+      </c>
+      <c r="G21" s="120" t="inlineStr">
+        <is>
+          <t>الوحدات</t>
+        </is>
+      </c>
+      <c r="H21" s="120" t="inlineStr">
+        <is>
+          <t>المؤجر</t>
+        </is>
+      </c>
+      <c r="I21" s="120" t="inlineStr">
+        <is>
+          <t>الشاغر</t>
+        </is>
+      </c>
+      <c r="J21" s="120" t="inlineStr">
+        <is>
+          <t>الإشغال</t>
+        </is>
+      </c>
+      <c r="K21" s="120" t="inlineStr">
+        <is>
+          <t>ملاحظة</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="107">
+      <c r="A22" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="122" t="inlineStr">
+        <is>
+          <t>محطة حلي</t>
+        </is>
+      </c>
+      <c r="C22" s="121" t="inlineStr">
+        <is>
+          <t>MK036</t>
+        </is>
+      </c>
+      <c r="D22" s="121" t="inlineStr">
+        <is>
+          <t>حلي</t>
+        </is>
+      </c>
+      <c r="E22" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F22" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G22" s="132" t="n">
+        <v>92</v>
+      </c>
+      <c r="H22" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="132" t="n">
+        <v>92</v>
+      </c>
+      <c r="J22" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="107">
+      <c r="A23" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="122" t="inlineStr">
+        <is>
+          <t>القديه</t>
+        </is>
+      </c>
+      <c r="C23" s="121" t="inlineStr">
+        <is>
+          <t>RY073</t>
+        </is>
+      </c>
+      <c r="D23" s="121" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+      <c r="E23" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F23" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G23" s="132" t="n">
+        <v>59</v>
+      </c>
+      <c r="H23" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="132" t="n">
+        <v>59</v>
+      </c>
+      <c r="J23" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="107">
+      <c r="A24" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="122" t="inlineStr">
+        <is>
+          <t>الخمرة</t>
+        </is>
+      </c>
+      <c r="C24" s="121" t="inlineStr">
+        <is>
+          <t>MK104</t>
+        </is>
+      </c>
+      <c r="D24" s="121" t="inlineStr">
+        <is>
+          <t>جدة</t>
+        </is>
+      </c>
+      <c r="E24" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F24" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G24" s="132" t="n">
+        <v>47</v>
+      </c>
+      <c r="H24" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="132" t="n">
+        <v>47</v>
+      </c>
+      <c r="J24" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="107">
+      <c r="A25" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="122" t="inlineStr">
+        <is>
+          <t>الريان</t>
+        </is>
+      </c>
+      <c r="C25" s="121" t="inlineStr">
+        <is>
+          <t>MK057</t>
+        </is>
+      </c>
+      <c r="D25" s="121" t="inlineStr">
+        <is>
+          <t>الجموم</t>
+        </is>
+      </c>
+      <c r="E25" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F25" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G25" s="132" t="n">
+        <v>43</v>
+      </c>
+      <c r="H25" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="132" t="n">
+        <v>43</v>
+      </c>
+      <c r="J25" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="107">
+      <c r="A26" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="122" t="inlineStr">
+        <is>
+          <t>مدينة الملك عبد الله</t>
+        </is>
+      </c>
+      <c r="C26" s="121" t="inlineStr">
+        <is>
+          <t>MK045</t>
+        </is>
+      </c>
+      <c r="D26" s="121" t="inlineStr">
+        <is>
+          <t>رابغ</t>
+        </is>
+      </c>
+      <c r="E26" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F26" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G26" s="132" t="n">
+        <v>41</v>
+      </c>
+      <c r="H26" s="132" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="132" t="n">
+        <v>39</v>
+      </c>
+      <c r="J26" s="133" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="K26" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" s="107">
+      <c r="A27" s="121" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="122" t="inlineStr">
+        <is>
+          <t>القنفذة</t>
+        </is>
+      </c>
+      <c r="C27" s="121" t="inlineStr">
+        <is>
+          <t>MK044</t>
+        </is>
+      </c>
+      <c r="D27" s="121" t="inlineStr">
+        <is>
+          <t>القنفذة</t>
+        </is>
+      </c>
+      <c r="E27" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F27" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G27" s="132" t="n">
+        <v>65</v>
+      </c>
+      <c r="H27" s="132" t="n">
+        <v>27</v>
+      </c>
+      <c r="I27" s="132" t="n">
+        <v>38</v>
+      </c>
+      <c r="J27" s="133" t="n">
+        <v>0.4153846153846154</v>
+      </c>
+      <c r="K27" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="107">
+      <c r="A28" s="121" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="122" t="inlineStr">
+        <is>
+          <t>المدينة عين الخيف</t>
+        </is>
+      </c>
+      <c r="C28" s="121" t="inlineStr">
+        <is>
+          <t>MD297</t>
+        </is>
+      </c>
+      <c r="D28" s="121" t="inlineStr">
+        <is>
+          <t>المدينة المنورة</t>
+        </is>
+      </c>
+      <c r="E28" s="121" t="inlineStr">
+        <is>
+          <t>امتياز</t>
+        </is>
+      </c>
+      <c r="F28" s="121" t="inlineStr">
+        <is>
+          <t>امتياز</t>
+        </is>
+      </c>
+      <c r="G28" s="132" t="n">
+        <v>38</v>
+      </c>
+      <c r="H28" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="132" t="n">
+        <v>38</v>
+      </c>
+      <c r="J28" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="107">
+      <c r="A29" s="121" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="122" t="inlineStr">
+        <is>
+          <t>محطة الظبية</t>
+        </is>
+      </c>
+      <c r="C29" s="121" t="inlineStr">
+        <is>
+          <t>JA070</t>
+        </is>
+      </c>
+      <c r="D29" s="121" t="inlineStr"/>
+      <c r="E29" s="121" t="inlineStr">
+        <is>
+          <t>امتياز</t>
+        </is>
+      </c>
+      <c r="F29" s="121" t="inlineStr">
+        <is>
+          <t>امتياز</t>
+        </is>
+      </c>
+      <c r="G29" s="132" t="n">
+        <v>31</v>
+      </c>
+      <c r="H29" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="132" t="n">
+        <v>31</v>
+      </c>
+      <c r="J29" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="107">
+      <c r="A30" s="121" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="122" t="inlineStr">
+        <is>
+          <t>وادي وج</t>
+        </is>
+      </c>
+      <c r="C30" s="121" t="inlineStr">
+        <is>
+          <t>MK317</t>
+        </is>
+      </c>
+      <c r="D30" s="121" t="inlineStr">
+        <is>
+          <t>الطائف</t>
+        </is>
+      </c>
+      <c r="E30" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F30" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G30" s="132" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="132" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="107">
+      <c r="A31" s="121" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="122" t="inlineStr">
+        <is>
+          <t>ابيار</t>
+        </is>
+      </c>
+      <c r="C31" s="121" t="inlineStr">
+        <is>
+          <t>MD011</t>
+        </is>
+      </c>
+      <c r="D31" s="121" t="inlineStr">
+        <is>
+          <t>المدينة المنورة</t>
+        </is>
+      </c>
+      <c r="E31" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F31" s="121" t="inlineStr">
+        <is>
+          <t>ايجار</t>
+        </is>
+      </c>
+      <c r="G31" s="132" t="n">
+        <v>27</v>
+      </c>
+      <c r="H31" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="132" t="n">
+        <v>27</v>
+      </c>
+      <c r="J31" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="224" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="107">
+      <c r="A32" s="121" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" s="122" t="inlineStr">
+        <is>
+          <t>القادسية</t>
+        </is>
+      </c>
+      <c r="C32" s="121" t="inlineStr">
+        <is>
+          <t>TB146</t>
+        </is>
+      </c>
+      <c r="D32" s="121" t="inlineStr">
+        <is>
+          <t>تبوك</t>
+        </is>
+      </c>
+      <c r="E32" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F32" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G32" s="132" t="n">
+        <v>29</v>
+      </c>
+      <c r="H32" s="132" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="132" t="n">
+        <v>26</v>
+      </c>
+      <c r="J32" s="133" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="K32" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="107">
+      <c r="A33" s="121" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="122" t="inlineStr">
+        <is>
+          <t>صناعية محايل</t>
+        </is>
+      </c>
+      <c r="C33" s="121" t="inlineStr">
+        <is>
+          <t>AS286</t>
+        </is>
+      </c>
+      <c r="D33" s="121" t="inlineStr">
+        <is>
+          <t>محايل عسير</t>
+        </is>
+      </c>
+      <c r="E33" s="121" t="inlineStr">
+        <is>
+          <t>تحت التنفيذ</t>
+        </is>
+      </c>
+      <c r="F33" s="121" t="inlineStr">
+        <is>
+          <t>تشغيل</t>
+        </is>
+      </c>
+      <c r="G33" s="132" t="n">
+        <v>24</v>
+      </c>
+      <c r="H33" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="132" t="n">
+        <v>24</v>
+      </c>
+      <c r="J33" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="224" t="inlineStr">
+        <is>
+          <t>شواغر محل بالأساس</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="109" t="n"/>
+      <c r="B34" s="109" t="n"/>
+      <c r="C34" s="109" t="n"/>
+      <c r="D34" s="109" t="n"/>
+      <c r="E34" s="109" t="n"/>
+      <c r="F34" s="109" t="n"/>
+      <c r="G34" s="109" t="n"/>
+      <c r="H34" s="109" t="n"/>
+      <c r="I34" s="109" t="n"/>
+      <c r="J34" s="109" t="n"/>
+      <c r="K34" s="109" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="109" t="n"/>
+      <c r="B35" s="128" t="inlineStr">
+        <is>
+          <t>ما يصححه هذا السجل</t>
+        </is>
+      </c>
+      <c r="C35" s="109" t="n"/>
+      <c r="D35" s="109" t="n"/>
+      <c r="E35" s="109" t="n"/>
+      <c r="F35" s="109" t="n"/>
+      <c r="G35" s="109" t="n"/>
+      <c r="H35" s="109" t="n"/>
+      <c r="I35" s="109" t="n"/>
+      <c r="J35" s="109" t="n"/>
+      <c r="K35" s="109" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1" s="107">
+      <c r="A36" s="109" t="n"/>
+      <c r="B36" s="109" t="n"/>
+      <c r="C36" s="129" t="inlineStr">
+        <is>
+          <t>•  الشبكة العاملة إشغالها ٧٩٪ لا ٢٥٪ — لا توجد أزمة شغور في المحطات المفتوحة</t>
+        </is>
+      </c>
+      <c r="D36" s="109" t="n"/>
+      <c r="E36" s="109" t="n"/>
+      <c r="F36" s="109" t="n"/>
+      <c r="G36" s="109" t="n"/>
+      <c r="H36" s="109" t="n"/>
+      <c r="I36" s="109" t="n"/>
+      <c r="J36" s="109" t="n"/>
+      <c r="K36" s="109" t="n"/>
+    </row>
+    <row r="37" ht="16" customHeight="1" s="107">
+      <c r="A37" s="109" t="n"/>
+      <c r="B37" s="109" t="n"/>
+      <c r="C37" s="129" t="inlineStr">
+        <is>
+          <t>•  الشغور الحقيقي في مكانين: تحت التنفيذ (٦٨٩ وحدة) والامتياز (٢٦٩ وحدة)</t>
+        </is>
+      </c>
+      <c r="D37" s="109" t="n"/>
+      <c r="E37" s="109" t="n"/>
+      <c r="F37" s="109" t="n"/>
+      <c r="G37" s="109" t="n"/>
+      <c r="H37" s="109" t="n"/>
+      <c r="I37" s="109" t="n"/>
+      <c r="J37" s="109" t="n"/>
+      <c r="K37" s="109" t="n"/>
+    </row>
+    <row r="38" ht="16" customHeight="1" s="107">
+      <c r="A38" s="109" t="n"/>
+      <c r="B38" s="109" t="n"/>
+      <c r="C38" s="129" t="inlineStr">
+        <is>
+          <t>•  المحل هو المنتج العالق: 764 وحدة و192 مؤجرة فقط (25٪) — وكل نوع آخر فوق ٤٥٪</t>
+        </is>
+      </c>
+      <c r="D38" s="109" t="n"/>
+      <c r="E38" s="109" t="n"/>
+      <c r="F38" s="109" t="n"/>
+      <c r="G38" s="109" t="n"/>
+      <c r="H38" s="109" t="n"/>
+      <c r="I38" s="109" t="n"/>
+      <c r="J38" s="109" t="n"/>
+      <c r="K38" s="109" t="n"/>
+    </row>
+    <row r="39" ht="16" customHeight="1" s="107">
+      <c r="A39" s="109" t="n"/>
+      <c r="B39" s="109" t="n"/>
+      <c r="C39" s="129" t="inlineStr">
+        <is>
+          <t>•  محلات الامتياز ١٤٦ وحدة و٥ مؤجرة (٣٪) — أسوأ رقم في السجل كله</t>
+        </is>
+      </c>
+      <c r="D39" s="109" t="n"/>
+      <c r="E39" s="109" t="n"/>
+      <c r="F39" s="109" t="n"/>
+      <c r="G39" s="109" t="n"/>
+      <c r="H39" s="109" t="n"/>
+      <c r="I39" s="109" t="n"/>
+      <c r="J39" s="109" t="n"/>
+      <c r="K39" s="109" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="109" t="n"/>
+      <c r="B40" s="109" t="n"/>
+      <c r="C40" s="109" t="n"/>
+      <c r="D40" s="109" t="n"/>
+      <c r="E40" s="109" t="n"/>
+      <c r="F40" s="109" t="n"/>
+      <c r="G40" s="109" t="n"/>
+      <c r="H40" s="109" t="n"/>
+      <c r="I40" s="109" t="n"/>
+      <c r="J40" s="109" t="n"/>
+      <c r="K40" s="109" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="109" t="n"/>
+      <c r="B41" s="128" t="inlineStr">
+        <is>
+          <t>ما يعنيه للخطة</t>
+        </is>
+      </c>
+      <c r="C41" s="109" t="n"/>
+      <c r="D41" s="109" t="n"/>
+      <c r="E41" s="109" t="n"/>
+      <c r="F41" s="109" t="n"/>
+      <c r="G41" s="109" t="n"/>
+      <c r="H41" s="109" t="n"/>
+      <c r="I41" s="109" t="n"/>
+      <c r="J41" s="109" t="n"/>
+      <c r="K41" s="109" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1" s="107">
+      <c r="A42" s="109" t="n"/>
+      <c r="B42" s="109" t="n"/>
+      <c r="C42" s="129" t="inlineStr">
+        <is>
+          <t>•  التأجير المسبق قبل الافتتاح هو الفرصة الأكبر — ٦٨٩ وحدة في ٤٣ محطة</t>
+        </is>
+      </c>
+      <c r="D42" s="109" t="n"/>
+      <c r="E42" s="109" t="n"/>
+      <c r="F42" s="109" t="n"/>
+      <c r="G42" s="109" t="n"/>
+      <c r="H42" s="109" t="n"/>
+      <c r="I42" s="109" t="n"/>
+      <c r="J42" s="109" t="n"/>
+      <c r="K42" s="109" t="n"/>
+    </row>
+    <row r="43" ht="16" customHeight="1" s="107">
+      <c r="A43" s="109" t="n"/>
+      <c r="B43" s="109" t="n"/>
+      <c r="C43" s="129" t="inlineStr">
+        <is>
+          <t>•  ٥٧٢ محلاً شاغراً هي بالضبط مخزون خطة الإكسسوارات (مساحة مقابل نسبة)</t>
+        </is>
+      </c>
+      <c r="D43" s="109" t="n"/>
+      <c r="E43" s="109" t="n"/>
+      <c r="F43" s="109" t="n"/>
+      <c r="G43" s="109" t="n"/>
+      <c r="H43" s="109" t="n"/>
+      <c r="I43" s="109" t="n"/>
+      <c r="J43" s="109" t="n"/>
+      <c r="K43" s="109" t="n"/>
+    </row>
+    <row r="44" ht="16" customHeight="1" s="107">
+      <c r="A44" s="109" t="n"/>
+      <c r="B44" s="109" t="n"/>
+      <c r="C44" s="129" t="inlineStr">
+        <is>
+          <t>•  شبكة الوسطاء تُوجَّه للامتياز وتحت التنفيذ لا للمحطات العاملة</t>
+        </is>
+      </c>
+      <c r="D44" s="109" t="n"/>
+      <c r="E44" s="109" t="n"/>
+      <c r="F44" s="109" t="n"/>
+      <c r="G44" s="109" t="n"/>
+      <c r="H44" s="109" t="n"/>
+      <c r="I44" s="109" t="n"/>
+      <c r="J44" s="109" t="n"/>
+      <c r="K44" s="109" t="n"/>
+    </row>
+    <row r="45" ht="16" customHeight="1" s="107">
+      <c r="A45" s="109" t="n"/>
+      <c r="B45" s="109" t="n"/>
+      <c r="C45" s="129" t="inlineStr">
+        <is>
+          <t>•  معيار الافتتاح (مغسلة وسوبرماركت) مسنود: إشغالهما ٧٦٪ و٨٥٪ حيث تعمل المحطة</t>
+        </is>
+      </c>
+      <c r="D45" s="109" t="n"/>
+      <c r="E45" s="109" t="n"/>
+      <c r="F45" s="109" t="n"/>
+      <c r="G45" s="109" t="n"/>
+      <c r="H45" s="109" t="n"/>
+      <c r="I45" s="109" t="n"/>
+      <c r="J45" s="109" t="n"/>
+      <c r="K45" s="109" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="109" t="n"/>
+      <c r="B46" s="109" t="n"/>
+      <c r="C46" s="109" t="n"/>
+      <c r="D46" s="109" t="n"/>
+      <c r="E46" s="109" t="n"/>
+      <c r="F46" s="109" t="n"/>
+      <c r="G46" s="109" t="n"/>
+      <c r="H46" s="109" t="n"/>
+      <c r="I46" s="109" t="n"/>
+      <c r="J46" s="109" t="n"/>
+      <c r="K46" s="109" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="109" t="n"/>
+      <c r="B47" s="117" t="inlineStr">
+        <is>
+          <t>حدود السجل</t>
+        </is>
+      </c>
+      <c r="C47" s="109" t="n"/>
+      <c r="D47" s="109" t="n"/>
+      <c r="E47" s="109" t="n"/>
+      <c r="F47" s="109" t="n"/>
+      <c r="G47" s="109" t="n"/>
+      <c r="H47" s="109" t="n"/>
+      <c r="I47" s="109" t="n"/>
+      <c r="J47" s="109" t="n"/>
+      <c r="K47" s="109" t="n"/>
+    </row>
+    <row r="48" ht="16" customHeight="1" s="107">
+      <c r="A48" s="109" t="n"/>
+      <c r="B48" s="109" t="n"/>
+      <c r="C48" s="129" t="inlineStr">
+        <is>
+          <t>•  لا يحمل قيمة إيجارية لكل وحدة — فلا يمكن تسعير الفرصة بالريال منه وحده</t>
+        </is>
+      </c>
+      <c r="D48" s="109" t="n"/>
+      <c r="E48" s="109" t="n"/>
+      <c r="F48" s="109" t="n"/>
+      <c r="G48" s="109" t="n"/>
+      <c r="H48" s="109" t="n"/>
+      <c r="I48" s="109" t="n"/>
+      <c r="J48" s="109" t="n"/>
+      <c r="K48" s="109" t="n"/>
+    </row>
+    <row r="49" ht="16" customHeight="1" s="107">
+      <c r="A49" s="109" t="n"/>
+      <c r="B49" s="109" t="n"/>
+      <c r="C49" s="129" t="inlineStr">
+        <is>
+          <t>•  «المحجوز» غير معرَّف: هل هو تفاوض قائم أم عقد لم يُوقَّع؟</t>
+        </is>
+      </c>
+      <c r="D49" s="109" t="n"/>
+      <c r="E49" s="109" t="n"/>
+      <c r="F49" s="109" t="n"/>
+      <c r="G49" s="109" t="n"/>
+      <c r="H49" s="109" t="n"/>
+      <c r="I49" s="109" t="n"/>
+      <c r="J49" s="109" t="n"/>
+      <c r="K49" s="109" t="n"/>
+    </row>
+    <row r="50" ht="16" customHeight="1" s="107">
+      <c r="A50" s="109" t="n"/>
+      <c r="B50" s="109" t="n"/>
+      <c r="C50" s="129" t="inlineStr">
+        <is>
+          <t>•  ٩١ محطة امتياز هنا مقابل ٩٢ في تقرير يوليو — فرق محطة واحدة غير مُفسَّر</t>
+        </is>
+      </c>
+      <c r="D50" s="109" t="n"/>
+      <c r="E50" s="109" t="n"/>
+      <c r="F50" s="109" t="n"/>
+      <c r="G50" s="109" t="n"/>
+      <c r="H50" s="109" t="n"/>
+      <c r="I50" s="109" t="n"/>
+      <c r="J50" s="109" t="n"/>
+      <c r="K50" s="109" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="C38:K38"/>
+    <mergeCell ref="C49:K49"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C37:K37"/>
+    <mergeCell ref="C36:K36"/>
+    <mergeCell ref="C50:K50"/>
+    <mergeCell ref="C44:K44"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="C45:K45"/>
+    <mergeCell ref="C48:K48"/>
+    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H6:H8">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="8">
+      <formula>0.7</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="7">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13:I18">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="7">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13:H18">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00F5831F"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I33">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00F5831F"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -18113,464 +20130,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="4" customWidth="1" style="106" min="1" max="1"/>
-    <col width="30" customWidth="1" style="106" min="2" max="2"/>
-    <col width="15" customWidth="1" style="106" min="3" max="4"/>
-    <col width="13" customWidth="1" style="106" min="5" max="5"/>
-    <col width="40" customWidth="1" style="106" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="107">
-      <c r="A1" s="118" t="inlineStr">
-        <is>
-          <t>اقتصاديات اللتر</t>
-        </is>
-      </c>
-      <c r="B1" s="109" t="n"/>
-      <c r="C1" s="109" t="n"/>
-      <c r="D1" s="109" t="n"/>
-      <c r="E1" s="109" t="n"/>
-      <c r="F1" s="109" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="107">
-      <c r="A2" s="119" t="inlineStr">
-        <is>
-          <t>أرقام محققة من قائمة الدخل — النصف الأول 2026 · الوحدة: هللة</t>
-        </is>
-      </c>
-      <c r="B2" s="109" t="n"/>
-      <c r="C2" s="109" t="n"/>
-      <c r="D2" s="109" t="n"/>
-      <c r="E2" s="109" t="n"/>
-      <c r="F2" s="109" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="107">
-      <c r="A3" s="111" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="111" t="inlineStr">
-        <is>
-          <t>البند</t>
-        </is>
-      </c>
-      <c r="C3" s="111" t="inlineStr">
-        <is>
-          <t>MK007 العمرة</t>
-        </is>
-      </c>
-      <c r="D3" s="111" t="inlineStr">
-        <is>
-          <t>MK019 الشرايع</t>
-        </is>
-      </c>
-      <c r="E3" s="111" t="inlineStr">
-        <is>
-          <t>الفارق</t>
-        </is>
-      </c>
-      <c r="F3" s="111" t="inlineStr">
-        <is>
-          <t>الدلالة</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21.75" customHeight="1" s="107">
-      <c r="A4" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="148" t="inlineStr">
-        <is>
-          <t>الإيراد لكل لتر</t>
-        </is>
-      </c>
-      <c r="C4" s="155" t="n">
-        <v>182.51</v>
-      </c>
-      <c r="D4" s="155" t="n">
-        <v>196.77</v>
-      </c>
-      <c r="E4" s="163">
-        <f>C4-D4</f>
-        <v/>
-      </c>
-      <c r="F4" s="114" t="inlineStr">
-        <is>
-          <t>قسمة الإيراد على اللترات</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21.75" customHeight="1" s="107">
-      <c r="A5" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="148" t="inlineStr">
-        <is>
-          <t>تكلفة البضاعة</t>
-        </is>
-      </c>
-      <c r="C5" s="155" t="n">
-        <v>-170</v>
-      </c>
-      <c r="D5" s="155" t="n">
-        <v>-180.67</v>
-      </c>
-      <c r="E5" s="163">
-        <f>C5-D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="114" t="inlineStr">
-        <is>
-          <t>93% من الإيراد — خارج سيطرتنا</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="107">
-      <c r="A6" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="148" t="inlineStr">
-        <is>
-          <t>النقل</t>
-        </is>
-      </c>
-      <c r="C6" s="155" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="D6" s="155" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="E6" s="163">
-        <f>C6-D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="114" t="inlineStr">
-        <is>
-          <t>أجرة الرحلة الفعلية 623 ريال</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" s="107">
-      <c r="A7" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="148" t="inlineStr">
-        <is>
-          <t>التبخّر</t>
-        </is>
-      </c>
-      <c r="C7" s="155" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="D7" s="155" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="E7" s="163">
-        <f>C7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="114" t="inlineStr">
-        <is>
-          <t>0.32% من التكلفة</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="21.75" customHeight="1" s="107">
-      <c r="A8" s="164" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="165" t="inlineStr">
-        <is>
-          <t>هامش مساهمة الوقود</t>
-        </is>
-      </c>
-      <c r="C8" s="166" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="D8" s="166" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="E8" s="167">
-        <f>C8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="168" t="inlineStr">
-        <is>
-          <t>الهدف 15 هللة</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="107">
-      <c r="A9" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="148" t="inlineStr">
-        <is>
-          <t>صافي التأجير</t>
-        </is>
-      </c>
-      <c r="C9" s="155" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D9" s="155" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="E9" s="163">
-        <f>C9-D9</f>
-        <v/>
-      </c>
-      <c r="F9" s="114" t="inlineStr">
-        <is>
-          <t>سالب في الشرايع</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" s="107">
-      <c r="A10" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="148" t="inlineStr">
-        <is>
-          <t>المصاريف التشغيلية</t>
-        </is>
-      </c>
-      <c r="C10" s="155" t="n">
-        <v>-10.23</v>
-      </c>
-      <c r="D10" s="155" t="n">
-        <v>-7.21</v>
-      </c>
-      <c r="E10" s="163">
-        <f>C10-D10</f>
-        <v/>
-      </c>
-      <c r="F10" s="114" t="inlineStr">
-        <is>
-          <t>88% منها إهلاك غير نقدي</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21.75" customHeight="1" s="107">
-      <c r="A11" s="164" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="165" t="inlineStr">
-        <is>
-          <t>صافي الربح</t>
-        </is>
-      </c>
-      <c r="C11" s="166" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="D11" s="166" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="E11" s="167">
-        <f>C11-D11</f>
-        <v/>
-      </c>
-      <c r="F11" s="168" t="inlineStr">
-        <is>
-          <t>الفجوة عن الهدف 9.9 و11.1 هللة</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="109" t="n"/>
-      <c r="B12" s="109" t="n"/>
-      <c r="C12" s="109" t="n"/>
-      <c r="D12" s="109" t="n"/>
-      <c r="E12" s="109" t="n"/>
-      <c r="F12" s="109" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="107">
-      <c r="A13" s="109" t="n"/>
-      <c r="B13" s="117" t="inlineStr">
-        <is>
-          <t>لماذا لا يمرّ الحل عبر التكلفة</t>
-        </is>
-      </c>
-      <c r="C13" s="109" t="n"/>
-      <c r="D13" s="109" t="n"/>
-      <c r="E13" s="109" t="n"/>
-      <c r="F13" s="109" t="n"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="107">
-      <c r="A14" s="109" t="n"/>
-      <c r="B14" s="109" t="n"/>
-      <c r="C14" s="129" t="inlineStr">
-        <is>
-          <t>•  المصاريف النقدية 0.94 هللة لكل لتر فقط</t>
-        </is>
-      </c>
-      <c r="D14" s="109" t="n"/>
-      <c r="E14" s="109" t="n"/>
-      <c r="F14" s="109" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="107">
-      <c r="A15" s="109" t="n"/>
-      <c r="B15" s="109" t="n"/>
-      <c r="C15" s="129" t="inlineStr">
-        <is>
-          <t>•  الإهلاك 88% من المصاريف — غير نقدي وغير قابل للخفض</t>
-        </is>
-      </c>
-      <c r="D15" s="109" t="n"/>
-      <c r="E15" s="109" t="n"/>
-      <c r="F15" s="109" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="107">
-      <c r="A16" s="109" t="n"/>
-      <c r="B16" s="109" t="n"/>
-      <c r="C16" s="129" t="inlineStr">
-        <is>
-          <t>•  فرفع الحجم 5% يعطي أضعاف ما يعطيه أي خفض ممكن</t>
-        </is>
-      </c>
-      <c r="D16" s="109" t="n"/>
-      <c r="E16" s="109" t="n"/>
-      <c r="F16" s="109" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="109" t="n"/>
-      <c r="B17" s="109" t="n"/>
-      <c r="C17" s="109" t="n"/>
-      <c r="D17" s="109" t="n"/>
-      <c r="E17" s="109" t="n"/>
-      <c r="F17" s="109" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="107">
-      <c r="A18" s="109" t="n"/>
-      <c r="B18" s="128" t="inlineStr">
-        <is>
-          <t>الديزل يسحب الهامش</t>
-        </is>
-      </c>
-      <c r="C18" s="109" t="n"/>
-      <c r="D18" s="109" t="n"/>
-      <c r="E18" s="109" t="n"/>
-      <c r="F18" s="109" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="107">
-      <c r="A19" s="109" t="n"/>
-      <c r="B19" s="109" t="n"/>
-      <c r="C19" s="129" t="inlineStr">
-        <is>
-          <t>•  العمرة ديزلها 28% وهامشها 10.07 هللة</t>
-        </is>
-      </c>
-      <c r="D19" s="109" t="n"/>
-      <c r="E19" s="109" t="n"/>
-      <c r="F19" s="109" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="107">
-      <c r="A20" s="109" t="n"/>
-      <c r="B20" s="109" t="n"/>
-      <c r="C20" s="129" t="inlineStr">
-        <is>
-          <t>•  الشرايع بلا ديزل وهامشها 13.36 هللة</t>
-        </is>
-      </c>
-      <c r="D20" s="109" t="n"/>
-      <c r="E20" s="109" t="n"/>
-      <c r="F20" s="109" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="107">
-      <c r="A21" s="109" t="n"/>
-      <c r="B21" s="109" t="n"/>
-      <c r="C21" s="129" t="inlineStr">
-        <is>
-          <t>•  ورفع حصة البنزين رفع مباشر للهامش لا مجرد زيادة إيراد</t>
-        </is>
-      </c>
-      <c r="D21" s="109" t="n"/>
-      <c r="E21" s="109" t="n"/>
-      <c r="F21" s="109" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="109" t="n"/>
-      <c r="B22" s="109" t="n"/>
-      <c r="C22" s="109" t="n"/>
-      <c r="D22" s="109" t="n"/>
-      <c r="E22" s="109" t="n"/>
-      <c r="F22" s="109" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="107">
-      <c r="A23" s="109" t="n"/>
-      <c r="B23" s="117" t="inlineStr">
-        <is>
-          <t>التأجير رافعة الربح</t>
-        </is>
-      </c>
-      <c r="C23" s="109" t="n"/>
-      <c r="D23" s="109" t="n"/>
-      <c r="E23" s="109" t="n"/>
-      <c r="F23" s="109" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="107">
-      <c r="A24" s="109" t="n"/>
-      <c r="B24" s="109" t="n"/>
-      <c r="C24" s="129" t="inlineStr">
-        <is>
-          <t>•  التمويل وإهلاك حق الاستخدام ثابتان ومدفوعان</t>
-        </is>
-      </c>
-      <c r="D24" s="109" t="n"/>
-      <c r="E24" s="109" t="n"/>
-      <c r="F24" s="109" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="107">
-      <c r="A25" s="109" t="n"/>
-      <c r="B25" s="109" t="n"/>
-      <c r="C25" s="129" t="inlineStr">
-        <is>
-          <t>•  يلتهمان 63% من دخل الإيجار في العمرة و106% في الشرايع</t>
-        </is>
-      </c>
-      <c r="D25" s="109" t="n"/>
-      <c r="E25" s="109" t="n"/>
-      <c r="F25" s="109" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="107">
-      <c r="A26" s="109" t="n"/>
-      <c r="B26" s="109" t="n"/>
-      <c r="C26" s="129" t="inlineStr">
-        <is>
-          <t>•  فكل إيجار إضافي ربح شبه صافٍ</t>
-        </is>
-      </c>
-      <c r="D26" s="109" t="n"/>
-      <c r="E26" s="109" t="n"/>
-      <c r="F26" s="109" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C14:F14"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>